--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/08-tabela-de-precos.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/08-tabela-de-precos.xlsx
@@ -167,7 +167,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -189,44 +189,11 @@
         <color rgb="00DCD2EC"/>
       </bottom>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00DCD2EC"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00DCD2EC"/>
-      </right>
-      <top style="thin">
-        <color rgb="00DCD2EC"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00DCD2EC"/>
-      </right>
-      <top style="thin">
-        <color rgb="00DCD2EC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00DCD2EC"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -256,26 +223,22 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="10" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="10" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="12" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -507,7 +470,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Tabela'!C24</f>
+              <f>'Tabela'!C26</f>
             </strRef>
           </tx>
           <spPr>
@@ -520,12 +483,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Tabela'!$A$25:$A$31</f>
+              <f>'Tabela'!$A$27:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Tabela'!$C$25:$C$31</f>
+              <f>'Tabela'!$C$27:$C$33</f>
             </numRef>
           </val>
         </ser>
@@ -534,7 +497,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Tabela'!D24</f>
+              <f>'Tabela'!D26</f>
             </strRef>
           </tx>
           <spPr>
@@ -547,12 +510,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Tabela'!$A$25:$A$31</f>
+              <f>'Tabela'!$A$27:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Tabela'!$D$25:$D$31</f>
+              <f>'Tabela'!$D$27:$D$33</f>
             </numRef>
           </val>
         </ser>
@@ -561,7 +524,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Tabela'!E24</f>
+              <f>'Tabela'!E26</f>
             </strRef>
           </tx>
           <spPr>
@@ -574,12 +537,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Tabela'!$A$25:$A$31</f>
+              <f>'Tabela'!$A$27:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Tabela'!$E$25:$E$31</f>
+              <f>'Tabela'!$E$27:$E$33</f>
             </numRef>
           </val>
         </ser>
@@ -588,7 +551,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Tabela'!F24</f>
+              <f>'Tabela'!F26</f>
             </strRef>
           </tx>
           <spPr>
@@ -601,12 +564,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Tabela'!$A$25:$A$31</f>
+              <f>'Tabela'!$A$27:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Tabela'!$F$25:$F$31</f>
+              <f>'Tabela'!$F$27:$F$33</f>
             </numRef>
           </val>
         </ser>
@@ -652,7 +615,7 @@
     <from>
       <col>11</col>
       <colOff>0</colOff>
-      <row>22</row>
+      <row>24</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2880000"/>
@@ -962,7 +925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1015,7 +978,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Em Tabela, uma linha por procedimento: minutos, se gera retorno, material e o valor de cada pagador. A tabela de preços da agenda (01, Config) deve ser esta.</t>
+          <t>Em Tabela, uma linha por procedimento: minutos, se gera retorno, material e o valor de cada pagador. Esta é a tabela oficial da clínica: a Config da planilha 01 (agenda), a 06 e a 07 copiam daqui.</t>
         </is>
       </c>
     </row>
@@ -1046,106 +1009,118 @@
     <row r="9" ht="46" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Rotina</t>
+          <t>Ordem de atualização</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Revise quando o custo-hora mudar (05) ou ao renegociar um convênio. Se pesquisar preços da região, anote na coluna "Referência de mercado"; a divulgação de preços segue as regras do CFM.</t>
+          <t>Mudou um preço? Atualize sempre nesta ordem: 08 (aqui) → 06 · Precificação → 07 · Simulador → 01 · Config (a tabela que a Agenda busca). Procedimento novo: 01 e 02 (Config), 08, 06 e 07. Convênio novo: 01, 02, 06, 07, 08, 09 (categorias de entrada) e 13 (Config, com prazo e dia de envio).</t>
         </is>
       </c>
     </row>
     <row r="10" ht="46" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Com a IA</t>
+          <t>Rotina</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Copie a Tabela e use o prompt "Preço 04 · Revisar a tabela de preços" da biblioteca do kit, ou "Preço 03 · Vale a pena este convênio?" para um convênio específico.</t>
+          <t>Revise quando o custo-hora mudar (05) ou ao renegociar um convênio. Se pesquisar preços da região, anote na coluna "Referência de mercado"; a divulgação de preços segue as regras do CFM.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="46" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Legenda</t>
+          <t>Com a IA</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Células amarelas: você preenche. Brancas: calculadas. Não é preciso mexer em nada fora do amarelo.</t>
+          <t>Copie a Tabela e use o prompt "Preço 04 · Revisar a tabela de preços" da biblioteca do kit, ou "Preço 03 · Vale a pena este convênio?" para um convênio específico.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="46" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Proteção</t>
+          <t>Legenda</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Fórmulas protegidas sem senha. Para editar: Revisar &gt; Desproteger planilha (Excel) ou Dados &gt; Proteger intervalos (Google Sheets).</t>
+          <t>Células amarelas: você preenche. Brancas: calculadas. Não é preciso mexer em nada fora do amarelo.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="46" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Requisitos</t>
+          <t>Proteção</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Excel 2016 ou mais novo, Microsoft 365 ou Google Sheets (só funções do Excel 2007+; nada de MÍNIMOSES, MÁXIMOSES ou UNIRTEXTO). No celular abre nos aplicativos; para preencher, use o computador.</t>
+          <t>Fórmulas protegidas sem senha. Para editar: Revisar &gt; Desproteger planilha (Excel) ou Dados &gt; Proteger intervalos (Google Sheets).</t>
         </is>
       </c>
     </row>
     <row r="14" ht="46" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Dados de pacientes</t>
+          <t>Requisitos</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Guarde só o que a gestão precisa (nome, contato, valor, data). Nada de diagnóstico, prontuário ou exame nestas planilhas: o kit é gestão, não é prontuário. Veja o guia LGPD do kit antes de colar qualquer tabela em uma IA.</t>
+          <t>Excel 2016 ou mais novo, Microsoft 365 ou Google Sheets (só funções do Excel 2007+; nada de MÍNIMOSES, MÁXIMOSES ou UNIRTEXTO). No celular abre nos aplicativos; para preencher, use o computador.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="46" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Google Sheets</t>
+          <t>Dados de pacientes</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
+          <t>Guarde só o que a gestão precisa (nome, contato, valor, data). Nada de diagnóstico, prontuário ou exame nestas planilhas: o kit é gestão, não é prontuário. Veja o guia LGPD do kit antes de colar qualquer tabela em uma IA.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="46" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Exemplos</t>
+          <t>Google Sheets</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Clínica Vida Plena é uma clínica fictícia. Pacientes, convênios, nomes, contatos e valores são inventados; não há nenhum dado clínico. Apague o exemplo antes de começar. Agenda futura e vencimentos em aberto do exemplo são relativos a hoje.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="46" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
+          <t>Exemplos</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Clínica Vida Plena é uma clínica fictícia. Pacientes, convênios, nomes, contatos e valores são inventados; não há nenhum dado clínico. Apague o exemplo antes de começar. Agenda futura e vencimentos em aberto do exemplo são relativos a hoje.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="46" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
           <t>Suporte</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>suporte@seusociogestor.com.br · resposta em até 5 dias úteis · reembolso em até 7 dias pelo mesmo canal.</t>
         </is>
@@ -1163,7 +1138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T37"/>
+  <dimension ref="A1:T39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1217,7 +1192,7 @@
       <c r="D4" s="10" t="n"/>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>Tabelas de convênio abaixo do custo</t>
+          <t>Tabelas de convênio abaixo do custo cheio + imposto</t>
         </is>
       </c>
       <c r="F4" s="10" t="n"/>
@@ -1245,1334 +1220,1392 @@
         <f>Config!$B$13</f>
         <v>338.983050847458</v>
       </c>
-      <c r="B5" s="16" t="n"/>
-      <c r="C5" s="17" t="str">
-        <f>COUNTIF($N$6:$N$17,"Abaixo do mínimo")&amp;" de "&amp;COUNTA($A$6:$A$17)</f>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="16" t="str">
+        <f>COUNTIF($N$8:$N$19,"Abaixo do mínimo")&amp;" de "&amp;COUNTA($A$8:$A$19)</f>
         <v>0 de 7</v>
       </c>
-      <c r="D5" s="18" t="n"/>
-      <c r="E5" s="19">
-        <f>SUM($O$6:$O$17)</f>
-        <v>11</v>
-      </c>
-      <c r="F5" s="18" t="n"/>
-      <c r="G5" s="20">
-        <f>SUM($Q$6:$Q$17)</f>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="17">
+        <f>SUM($O$8:$O$19)</f>
+        <v>14</v>
+      </c>
+      <c r="F5" s="10" t="n"/>
+      <c r="G5" s="18">
+        <f>SUM($Q$8:$Q$19)</f>
         <v>48631</v>
       </c>
-      <c r="H5" s="21" t="n"/>
-      <c r="I5" s="22">
-        <f>IFERROR(SUM($Q$6:$Q$17)/(SUMPRODUCT($P$6:$P$17,$B$6:$B$17)/60),0)</f>
+      <c r="H5" s="12" t="n"/>
+      <c r="I5" s="19">
+        <f>IFERROR(SUM($Q$8:$Q$19)/(SUMPRODUCT($P$8:$P$19,$B$8:$B$19)/60),0)</f>
         <v>410.966197183099</v>
       </c>
-      <c r="J5" s="23" t="n"/>
-      <c r="K5" s="24">
+      <c r="J5" s="14" t="n"/>
+      <c r="K5" s="20">
         <f>IFERROR(I5/Config!$B$13-1,0)</f>
         <v>0.212350281690141</v>
       </c>
-      <c r="L5" s="16" t="n"/>
-      <c r="M5" s="25">
+      <c r="L5" s="8" t="n"/>
+    </row>
+    <row r="6"/>
+    <row r="7" ht="44" customHeight="1">
+      <c r="A7" s="21" t="inlineStr">
+        <is>
+          <t>Procedimento</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>Gera retorno?</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>Material (R$)</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>Custo cheio (R$)</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>Preço mínimo (R$)</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>Preço alvo (R$)</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="str">
+        <f>IF(Config!$B$17="","",Config!$B$17)</f>
+        <v>Particular</v>
+      </c>
+      <c r="I7" s="21" t="str">
+        <f>IF(Config!$B$18="","",Config!$B$18)</f>
+        <v>Saúde Total</v>
+      </c>
+      <c r="J7" s="21" t="str">
+        <f>IF(Config!$B$19="","",Config!$B$19)</f>
+        <v>MediPlan</v>
+      </c>
+      <c r="K7" s="21" t="str">
+        <f>IF(Config!$B$20="","",Config!$B$20)</f>
+        <v>Vida Care</v>
+      </c>
+      <c r="L7" s="21">
+        <f>IF(Config!$B$21="","",Config!$B$21)</f>
+        <v/>
+      </c>
+      <c r="M7" s="21">
         <f>IF(Config!$B$22="","",Config!$B$22)</f>
         <v/>
       </c>
-      <c r="N5" s="25" t="inlineStr">
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t>Situação do particular</t>
         </is>
       </c>
-      <c r="O5" s="25" t="inlineStr">
-        <is>
-          <t>Tabelas abaixo do custo cheio</t>
-        </is>
-      </c>
-      <c r="P5" s="25" t="inlineStr">
+      <c r="O7" s="21" t="inlineStr">
+        <is>
+          <t>Tabelas abaixo do custo cheio + imposto</t>
+        </is>
+      </c>
+      <c r="P7" s="21" t="inlineStr">
         <is>
           <t>Realizados no mês</t>
         </is>
       </c>
-      <c r="Q5" s="25" t="inlineStr">
+      <c r="Q7" s="21" t="inlineStr">
         <is>
           <t>Produção no mês (R$)</t>
         </is>
       </c>
-      <c r="R5" s="25" t="inlineStr">
+      <c r="R7" s="21" t="inlineStr">
         <is>
           <t>Valor médio praticado (R$)</t>
         </is>
       </c>
-      <c r="S5" s="25" t="inlineStr">
+      <c r="S7" s="21" t="inlineStr">
         <is>
           <t>Valor médio contra o mínimo</t>
         </is>
       </c>
-      <c r="T5" s="25" t="inlineStr">
+      <c r="T7" s="21" t="inlineStr">
         <is>
           <t>Referência de mercado (opcional)</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="26" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="22" t="inlineStr">
         <is>
           <t>Consulta</t>
         </is>
       </c>
-      <c r="B6" s="27" t="n">
+      <c r="B8" s="23" t="n">
         <v>30</v>
       </c>
-      <c r="C6" s="28" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D8" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="E6" s="30">
-        <f>IF(A6="","",(B6+IF(C6="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D6)</f>
+      <c r="E8" s="26">
+        <f>IF(A8="","",(B8+IF(C8="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D8)</f>
         <v>130.666666666667</v>
       </c>
-      <c r="F6" s="31">
-        <f>IF(A6="","",IFERROR(E6/(1-Config!$B$8-Config!$B$9),""))</f>
+      <c r="F8" s="27">
+        <f>IF(A8="","",IFERROR(E8/(1-Config!$B$8-Config!$B$9),""))</f>
         <v>221.468926553672</v>
       </c>
-      <c r="G6" s="30">
-        <f>IF(A6="","",IFERROR(E6/(1-Config!$B$8-Config!$B$10),""))</f>
+      <c r="G8" s="26">
+        <f>IF(A8="","",IFERROR(E8/(1-Config!$B$8-Config!$B$10),""))</f>
         <v>296.969696969697</v>
       </c>
-      <c r="H6" s="32" t="n">
+      <c r="H8" s="28" t="n">
         <v>380</v>
       </c>
-      <c r="I6" s="32" t="n">
+      <c r="I8" s="28" t="n">
         <v>120</v>
       </c>
-      <c r="J6" s="32" t="n">
+      <c r="J8" s="28" t="n">
         <v>100</v>
       </c>
-      <c r="K6" s="32" t="n">
+      <c r="K8" s="28" t="n">
         <v>90</v>
       </c>
-      <c r="L6" s="32" t="n"/>
-      <c r="M6" s="32" t="n"/>
-      <c r="N6" s="33" t="str">
-        <f>IF(OR(A6="",H6=""),"",IF(H6=0,"Sem cobrança",IF(H6&lt;F6,"Abaixo do mínimo",IF(H6&lt;G6,"Entre mínimo e alvo","No alvo ou acima"))))</f>
+      <c r="L8" s="28" t="n"/>
+      <c r="M8" s="28" t="n"/>
+      <c r="N8" s="29" t="str">
+        <f>IF(OR(A8="",H8=""),"",IF(H8=0,"Sem cobrança",IF(H8&lt;F8,"Abaixo do mínimo",IF(H8&lt;G8,"Entre mínimo e alvo","No alvo ou acima"))))</f>
         <v>No alvo ou acima</v>
       </c>
-      <c r="O6" s="34">
-        <f>IF(A6="","",SUMPRODUCT((I6:M6&lt;&gt;"")*(I6:M6&gt;0)*(I6:M6&lt;E6)))</f>
+      <c r="O8" s="30">
+        <f>IF(A8="","",SUMPRODUCT((I8:M8&lt;&gt;"")*(I8:M8&gt;0)*(I8:M8*(1-Config!$B$8)&lt;E8)))</f>
         <v>3</v>
       </c>
-      <c r="P6" s="27" t="n">
+      <c r="P8" s="23" t="n">
         <v>130</v>
       </c>
-      <c r="Q6" s="32" t="n">
+      <c r="Q8" s="28" t="n">
         <v>30730</v>
       </c>
-      <c r="R6" s="30">
-        <f>IF(OR(A6="",P6="",P6=0),"",Q6/P6)</f>
+      <c r="R8" s="26">
+        <f>IF(OR(A8="",P8="",P8=0),"",Q8/P8)</f>
         <v>236.384615384615</v>
       </c>
-      <c r="S6" s="35">
-        <f>IF(OR(R6="",F6="",H6=0),"",R6/F6-1)</f>
+      <c r="S8" s="31">
+        <f>IF(OR(R8="",F8="",H8=0),"",R8/F8-1)</f>
         <v>0.0673489010989012</v>
       </c>
-      <c r="T6" s="26" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="T8" s="22" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="inlineStr">
         <is>
           <t>Retorno</t>
         </is>
       </c>
-      <c r="B7" s="27" t="n">
+      <c r="B9" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="C7" s="28" t="inlineStr">
+      <c r="C9" s="24" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D9" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="E7" s="30">
-        <f>IF(A7="","",(B7+IF(C7="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D7)</f>
+      <c r="E9" s="26">
+        <f>IF(A9="","",(B9+IF(C9="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D9)</f>
         <v>68.6666666666667</v>
       </c>
-      <c r="F7" s="31">
-        <f>IF(A7="","",IFERROR(E7/(1-Config!$B$8-Config!$B$9),""))</f>
+      <c r="F9" s="27">
+        <f>IF(A9="","",IFERROR(E9/(1-Config!$B$8-Config!$B$9),""))</f>
         <v>116.38418079096</v>
       </c>
-      <c r="G7" s="30">
-        <f>IF(A7="","",IFERROR(E7/(1-Config!$B$8-Config!$B$10),""))</f>
+      <c r="G9" s="26">
+        <f>IF(A9="","",IFERROR(E9/(1-Config!$B$8-Config!$B$10),""))</f>
         <v>156.060606060606</v>
       </c>
-      <c r="H7" s="32" t="n">
+      <c r="H9" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="32" t="n">
+      <c r="I9" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="32" t="n">
+      <c r="J9" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="K7" s="32" t="n">
+      <c r="K9" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="32" t="n"/>
-      <c r="M7" s="32" t="n"/>
-      <c r="N7" s="33" t="str">
-        <f>IF(OR(A7="",H7=""),"",IF(H7=0,"Sem cobrança",IF(H7&lt;F7,"Abaixo do mínimo",IF(H7&lt;G7,"Entre mínimo e alvo","No alvo ou acima"))))</f>
+      <c r="L9" s="28" t="n"/>
+      <c r="M9" s="28" t="n"/>
+      <c r="N9" s="29" t="str">
+        <f>IF(OR(A9="",H9=""),"",IF(H9=0,"Sem cobrança",IF(H9&lt;F9,"Abaixo do mínimo",IF(H9&lt;G9,"Entre mínimo e alvo","No alvo ou acima"))))</f>
         <v>Sem cobrança</v>
       </c>
-      <c r="O7" s="34">
-        <f>IF(A7="","",SUMPRODUCT((I7:M7&lt;&gt;"")*(I7:M7&gt;0)*(I7:M7&lt;E7)))</f>
+      <c r="O9" s="30">
+        <f>IF(A9="","",SUMPRODUCT((I9:M9&lt;&gt;"")*(I9:M9&gt;0)*(I9:M9*(1-Config!$B$8)&lt;E9)))</f>
         <v>0</v>
       </c>
-      <c r="P7" s="27" t="n">
+      <c r="P9" s="23" t="n">
         <v>48</v>
       </c>
-      <c r="Q7" s="32" t="n">
+      <c r="Q9" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="R7" s="30">
-        <f>IF(OR(A7="",P7="",P7=0),"",Q7/P7)</f>
+      <c r="R9" s="26">
+        <f>IF(OR(A9="",P9="",P9=0),"",Q9/P9)</f>
         <v>0</v>
       </c>
-      <c r="S7" s="35">
-        <f>IF(OR(R7="",F7="",H7=0),"",R7/F7-1)</f>
-        <v/>
-      </c>
-      <c r="T7" s="26" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="S9" s="31">
+        <f>IF(OR(R9="",F9="",H9=0),"",R9/F9-1)</f>
+        <v/>
+      </c>
+      <c r="T9" s="22" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>ECG</t>
         </is>
       </c>
-      <c r="B8" s="27" t="n">
+      <c r="B10" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="C8" s="28" t="inlineStr">
+      <c r="C10" s="24" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D10" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="E8" s="30">
-        <f>IF(A8="","",(B8+IF(C8="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D8)</f>
+      <c r="E10" s="26">
+        <f>IF(A10="","",(B10+IF(C10="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D10)</f>
         <v>74.6666666666667</v>
       </c>
-      <c r="F8" s="31">
-        <f>IF(A8="","",IFERROR(E8/(1-Config!$B$8-Config!$B$9),""))</f>
+      <c r="F10" s="27">
+        <f>IF(A10="","",IFERROR(E10/(1-Config!$B$8-Config!$B$9),""))</f>
         <v>126.553672316384</v>
       </c>
-      <c r="G8" s="30">
-        <f>IF(A8="","",IFERROR(E8/(1-Config!$B$8-Config!$B$10),""))</f>
+      <c r="G10" s="26">
+        <f>IF(A10="","",IFERROR(E10/(1-Config!$B$8-Config!$B$10),""))</f>
         <v>169.69696969697</v>
       </c>
-      <c r="H8" s="32" t="n">
+      <c r="H10" s="28" t="n">
         <v>130</v>
       </c>
-      <c r="I8" s="32" t="n">
+      <c r="I10" s="28" t="n">
         <v>40</v>
       </c>
-      <c r="J8" s="32" t="n">
+      <c r="J10" s="28" t="n">
         <v>35</v>
       </c>
-      <c r="K8" s="32" t="n">
+      <c r="K10" s="28" t="n">
         <v>32</v>
       </c>
-      <c r="L8" s="32" t="n"/>
-      <c r="M8" s="32" t="n"/>
-      <c r="N8" s="33" t="str">
-        <f>IF(OR(A8="",H8=""),"",IF(H8=0,"Sem cobrança",IF(H8&lt;F8,"Abaixo do mínimo",IF(H8&lt;G8,"Entre mínimo e alvo","No alvo ou acima"))))</f>
+      <c r="L10" s="28" t="n"/>
+      <c r="M10" s="28" t="n"/>
+      <c r="N10" s="29" t="str">
+        <f>IF(OR(A10="",H10=""),"",IF(H10=0,"Sem cobrança",IF(H10&lt;F10,"Abaixo do mínimo",IF(H10&lt;G10,"Entre mínimo e alvo","No alvo ou acima"))))</f>
         <v>Entre mínimo e alvo</v>
       </c>
-      <c r="O8" s="34">
-        <f>IF(A8="","",SUMPRODUCT((I8:M8&lt;&gt;"")*(I8:M8&gt;0)*(I8:M8&lt;E8)))</f>
+      <c r="O10" s="30">
+        <f>IF(A10="","",SUMPRODUCT((I10:M10&lt;&gt;"")*(I10:M10&gt;0)*(I10:M10*(1-Config!$B$8)&lt;E10)))</f>
         <v>3</v>
       </c>
-      <c r="P8" s="27" t="n">
+      <c r="P10" s="23" t="n">
         <v>18</v>
       </c>
-      <c r="Q8" s="32" t="n">
+      <c r="Q10" s="28" t="n">
         <v>1416</v>
       </c>
-      <c r="R8" s="30">
-        <f>IF(OR(A8="",P8="",P8=0),"",Q8/P8)</f>
+      <c r="R10" s="26">
+        <f>IF(OR(A10="",P10="",P10=0),"",Q10/P10)</f>
         <v>78.6666666666667</v>
       </c>
-      <c r="S8" s="35">
-        <f>IF(OR(R8="",F8="",H8=0),"",R8/F8-1)</f>
+      <c r="S10" s="31">
+        <f>IF(OR(R10="",F10="",H10=0),"",R10/F10-1)</f>
         <v>-0.378392857142857</v>
       </c>
-      <c r="T8" s="26" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="26" t="inlineStr">
+      <c r="T10" s="22" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>MAPA</t>
         </is>
       </c>
-      <c r="B9" s="27" t="n">
+      <c r="B11" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="C9" s="28" t="inlineStr">
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D11" s="25" t="n">
         <v>15</v>
       </c>
-      <c r="E9" s="30">
-        <f>IF(A9="","",(B9+IF(C9="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D9)</f>
+      <c r="E11" s="26">
+        <f>IF(A11="","",(B11+IF(C11="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D11)</f>
         <v>81.6666666666667</v>
       </c>
-      <c r="F9" s="31">
-        <f>IF(A9="","",IFERROR(E9/(1-Config!$B$8-Config!$B$9),""))</f>
+      <c r="F11" s="27">
+        <f>IF(A11="","",IFERROR(E11/(1-Config!$B$8-Config!$B$9),""))</f>
         <v>138.418079096045</v>
       </c>
-      <c r="G9" s="30">
-        <f>IF(A9="","",IFERROR(E9/(1-Config!$B$8-Config!$B$10),""))</f>
+      <c r="G11" s="26">
+        <f>IF(A11="","",IFERROR(E11/(1-Config!$B$8-Config!$B$10),""))</f>
         <v>185.606060606061</v>
       </c>
-      <c r="H9" s="32" t="n">
+      <c r="H11" s="28" t="n">
         <v>300</v>
       </c>
-      <c r="I9" s="32" t="n">
+      <c r="I11" s="28" t="n">
         <v>95</v>
       </c>
-      <c r="J9" s="32" t="n">
+      <c r="J11" s="28" t="n">
         <v>85</v>
       </c>
-      <c r="K9" s="32" t="n">
+      <c r="K11" s="28" t="n">
         <v>75</v>
       </c>
-      <c r="L9" s="32" t="n"/>
-      <c r="M9" s="32" t="n"/>
-      <c r="N9" s="33" t="str">
-        <f>IF(OR(A9="",H9=""),"",IF(H9=0,"Sem cobrança",IF(H9&lt;F9,"Abaixo do mínimo",IF(H9&lt;G9,"Entre mínimo e alvo","No alvo ou acima"))))</f>
-        <v>No alvo ou acima</v>
-      </c>
-      <c r="O9" s="34">
-        <f>IF(A9="","",SUMPRODUCT((I9:M9&lt;&gt;"")*(I9:M9&gt;0)*(I9:M9&lt;E9)))</f>
-        <v>1</v>
-      </c>
-      <c r="P9" s="27" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q9" s="32" t="n">
-        <v>1345</v>
-      </c>
-      <c r="R9" s="30">
-        <f>IF(OR(A9="",P9="",P9=0),"",Q9/P9)</f>
-        <v>168.125</v>
-      </c>
-      <c r="S9" s="35">
-        <f>IF(OR(R9="",F9="",H9=0),"",R9/F9-1)</f>
-        <v>0.214617346938776</v>
-      </c>
-      <c r="T9" s="26" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="26" t="inlineStr">
-        <is>
-          <t>Holter</t>
-        </is>
-      </c>
-      <c r="B10" s="27" t="n">
-        <v>20</v>
-      </c>
-      <c r="C10" s="28" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="D10" s="29" t="n">
-        <v>18</v>
-      </c>
-      <c r="E10" s="30">
-        <f>IF(A10="","",(B10+IF(C10="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D10)</f>
-        <v>84.6666666666667</v>
-      </c>
-      <c r="F10" s="31">
-        <f>IF(A10="","",IFERROR(E10/(1-Config!$B$8-Config!$B$9),""))</f>
-        <v>143.502824858757</v>
-      </c>
-      <c r="G10" s="30">
-        <f>IF(A10="","",IFERROR(E10/(1-Config!$B$8-Config!$B$10),""))</f>
-        <v>192.424242424242</v>
-      </c>
-      <c r="H10" s="32" t="n">
-        <v>350</v>
-      </c>
-      <c r="I10" s="32" t="n">
-        <v>105</v>
-      </c>
-      <c r="J10" s="32" t="n">
-        <v>95</v>
-      </c>
-      <c r="K10" s="32" t="n">
-        <v>85</v>
-      </c>
-      <c r="L10" s="32" t="n"/>
-      <c r="M10" s="32" t="n"/>
-      <c r="N10" s="33" t="str">
-        <f>IF(OR(A10="",H10=""),"",IF(H10=0,"Sem cobrança",IF(H10&lt;F10,"Abaixo do mínimo",IF(H10&lt;G10,"Entre mínimo e alvo","No alvo ou acima"))))</f>
-        <v>No alvo ou acima</v>
-      </c>
-      <c r="O10" s="34">
-        <f>IF(A10="","",SUMPRODUCT((I10:M10&lt;&gt;"")*(I10:M10&gt;0)*(I10:M10&lt;E10)))</f>
-        <v>0</v>
-      </c>
-      <c r="P10" s="27" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q10" s="32" t="n">
-        <v>2490</v>
-      </c>
-      <c r="R10" s="30">
-        <f>IF(OR(A10="",P10="",P10=0),"",Q10/P10)</f>
-        <v>249</v>
-      </c>
-      <c r="S10" s="35">
-        <f>IF(OR(R10="",F10="",H10=0),"",R10/F10-1)</f>
-        <v>0.735157480314961</v>
-      </c>
-      <c r="T10" s="26" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="26" t="inlineStr">
-        <is>
-          <t>Teste ergométrico</t>
-        </is>
-      </c>
-      <c r="B11" s="27" t="n">
-        <v>40</v>
-      </c>
-      <c r="C11" s="28" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="D11" s="29" t="n">
-        <v>25</v>
-      </c>
-      <c r="E11" s="30">
-        <f>IF(A11="","",(B11+IF(C11="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D11)</f>
-        <v>158.333333333333</v>
-      </c>
-      <c r="F11" s="31">
-        <f>IF(A11="","",IFERROR(E11/(1-Config!$B$8-Config!$B$9),""))</f>
-        <v>268.361581920904</v>
-      </c>
-      <c r="G11" s="30">
-        <f>IF(A11="","",IFERROR(E11/(1-Config!$B$8-Config!$B$10),""))</f>
-        <v>359.848484848485</v>
-      </c>
-      <c r="H11" s="32" t="n">
-        <v>450</v>
-      </c>
-      <c r="I11" s="32" t="n">
-        <v>140</v>
-      </c>
-      <c r="J11" s="32" t="n">
-        <v>125</v>
-      </c>
-      <c r="K11" s="32" t="n">
-        <v>110</v>
-      </c>
-      <c r="L11" s="32" t="n"/>
-      <c r="M11" s="32" t="n"/>
-      <c r="N11" s="33" t="str">
+      <c r="L11" s="28" t="n"/>
+      <c r="M11" s="28" t="n"/>
+      <c r="N11" s="29" t="str">
         <f>IF(OR(A11="",H11=""),"",IF(H11=0,"Sem cobrança",IF(H11&lt;F11,"Abaixo do mínimo",IF(H11&lt;G11,"Entre mínimo e alvo","No alvo ou acima"))))</f>
         <v>No alvo ou acima</v>
       </c>
-      <c r="O11" s="34">
-        <f>IF(A11="","",SUMPRODUCT((I11:M11&lt;&gt;"")*(I11:M11&gt;0)*(I11:M11&lt;E11)))</f>
-        <v>3</v>
-      </c>
-      <c r="P11" s="27" t="n">
+      <c r="O11" s="30">
+        <f>IF(A11="","",SUMPRODUCT((I11:M11&lt;&gt;"")*(I11:M11&gt;0)*(I11:M11*(1-Config!$B$8)&lt;E11)))</f>
+        <v>2</v>
+      </c>
+      <c r="P11" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="Q11" s="32" t="n">
-        <v>2270</v>
-      </c>
-      <c r="R11" s="30">
+      <c r="Q11" s="28" t="n">
+        <v>1345</v>
+      </c>
+      <c r="R11" s="26">
         <f>IF(OR(A11="",P11="",P11=0),"",Q11/P11)</f>
-        <v>283.75</v>
-      </c>
-      <c r="S11" s="35">
+        <v>168.125</v>
+      </c>
+      <c r="S11" s="31">
         <f>IF(OR(R11="",F11="",H11=0),"",R11/F11-1)</f>
-        <v>0.0573421052631582</v>
-      </c>
-      <c r="T11" s="26" t="n"/>
+        <v>0.214617346938776</v>
+      </c>
+      <c r="T11" s="22" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="26" t="inlineStr">
-        <is>
-          <t>Avaliação endócrina</t>
-        </is>
-      </c>
-      <c r="B12" s="27" t="n">
-        <v>40</v>
-      </c>
-      <c r="C12" s="28" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="D12" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="E12" s="30">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>Holter</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D12" s="25" t="n">
+        <v>18</v>
+      </c>
+      <c r="E12" s="26">
         <f>IF(A12="","",(B12+IF(C12="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D12)</f>
-        <v>164</v>
-      </c>
-      <c r="F12" s="31">
+        <v>84.6666666666667</v>
+      </c>
+      <c r="F12" s="27">
         <f>IF(A12="","",IFERROR(E12/(1-Config!$B$8-Config!$B$9),""))</f>
-        <v>277.966101694915</v>
-      </c>
-      <c r="G12" s="30">
+        <v>143.502824858757</v>
+      </c>
+      <c r="G12" s="26">
         <f>IF(A12="","",IFERROR(E12/(1-Config!$B$8-Config!$B$10),""))</f>
-        <v>372.727272727273</v>
-      </c>
-      <c r="H12" s="32" t="n">
-        <v>400</v>
-      </c>
-      <c r="I12" s="32" t="n">
-        <v>130</v>
-      </c>
-      <c r="J12" s="32" t="n"/>
-      <c r="K12" s="32" t="n"/>
-      <c r="L12" s="32" t="n"/>
-      <c r="M12" s="32" t="n"/>
-      <c r="N12" s="33" t="str">
+        <v>192.424242424242</v>
+      </c>
+      <c r="H12" s="28" t="n">
+        <v>350</v>
+      </c>
+      <c r="I12" s="28" t="n">
+        <v>105</v>
+      </c>
+      <c r="J12" s="28" t="n">
+        <v>95</v>
+      </c>
+      <c r="K12" s="28" t="n">
+        <v>85</v>
+      </c>
+      <c r="L12" s="28" t="n"/>
+      <c r="M12" s="28" t="n"/>
+      <c r="N12" s="29" t="str">
         <f>IF(OR(A12="",H12=""),"",IF(H12=0,"Sem cobrança",IF(H12&lt;F12,"Abaixo do mínimo",IF(H12&lt;G12,"Entre mínimo e alvo","No alvo ou acima"))))</f>
         <v>No alvo ou acima</v>
       </c>
-      <c r="O12" s="34">
-        <f>IF(A12="","",SUMPRODUCT((I12:M12&lt;&gt;"")*(I12:M12&gt;0)*(I12:M12&lt;E12)))</f>
+      <c r="O12" s="30">
+        <f>IF(A12="","",SUMPRODUCT((I12:M12&lt;&gt;"")*(I12:M12&gt;0)*(I12:M12*(1-Config!$B$8)&lt;E12)))</f>
+        <v>2</v>
+      </c>
+      <c r="P12" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q12" s="28" t="n">
+        <v>2490</v>
+      </c>
+      <c r="R12" s="26">
+        <f>IF(OR(A12="",P12="",P12=0),"",Q12/P12)</f>
+        <v>249</v>
+      </c>
+      <c r="S12" s="31">
+        <f>IF(OR(R12="",F12="",H12=0),"",R12/F12-1)</f>
+        <v>0.735157480314961</v>
+      </c>
+      <c r="T12" s="22" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>Teste ergométrico</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="n">
+        <v>40</v>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D13" s="25" t="n">
+        <v>25</v>
+      </c>
+      <c r="E13" s="26">
+        <f>IF(A13="","",(B13+IF(C13="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D13)</f>
+        <v>158.333333333333</v>
+      </c>
+      <c r="F13" s="27">
+        <f>IF(A13="","",IFERROR(E13/(1-Config!$B$8-Config!$B$9),""))</f>
+        <v>268.361581920904</v>
+      </c>
+      <c r="G13" s="26">
+        <f>IF(A13="","",IFERROR(E13/(1-Config!$B$8-Config!$B$10),""))</f>
+        <v>359.848484848485</v>
+      </c>
+      <c r="H13" s="28" t="n">
+        <v>450</v>
+      </c>
+      <c r="I13" s="28" t="n">
+        <v>140</v>
+      </c>
+      <c r="J13" s="28" t="n">
+        <v>125</v>
+      </c>
+      <c r="K13" s="28" t="n">
+        <v>110</v>
+      </c>
+      <c r="L13" s="28" t="n"/>
+      <c r="M13" s="28" t="n"/>
+      <c r="N13" s="29" t="str">
+        <f>IF(OR(A13="",H13=""),"",IF(H13=0,"Sem cobrança",IF(H13&lt;F13,"Abaixo do mínimo",IF(H13&lt;G13,"Entre mínimo e alvo","No alvo ou acima"))))</f>
+        <v>No alvo ou acima</v>
+      </c>
+      <c r="O13" s="30">
+        <f>IF(A13="","",SUMPRODUCT((I13:M13&lt;&gt;"")*(I13:M13&gt;0)*(I13:M13*(1-Config!$B$8)&lt;E13)))</f>
+        <v>3</v>
+      </c>
+      <c r="P13" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q13" s="28" t="n">
+        <v>2270</v>
+      </c>
+      <c r="R13" s="26">
+        <f>IF(OR(A13="",P13="",P13=0),"",Q13/P13)</f>
+        <v>283.75</v>
+      </c>
+      <c r="S13" s="31">
+        <f>IF(OR(R13="",F13="",H13=0),"",R13/F13-1)</f>
+        <v>0.0573421052631582</v>
+      </c>
+      <c r="T13" s="22" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>Avaliação endócrina</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="n">
+        <v>40</v>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D14" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" s="26">
+        <f>IF(A14="","",(B14+IF(C14="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D14)</f>
+        <v>164</v>
+      </c>
+      <c r="F14" s="27">
+        <f>IF(A14="","",IFERROR(E14/(1-Config!$B$8-Config!$B$9),""))</f>
+        <v>277.966101694915</v>
+      </c>
+      <c r="G14" s="26">
+        <f>IF(A14="","",IFERROR(E14/(1-Config!$B$8-Config!$B$10),""))</f>
+        <v>372.727272727273</v>
+      </c>
+      <c r="H14" s="28" t="n">
+        <v>400</v>
+      </c>
+      <c r="I14" s="28" t="n">
+        <v>130</v>
+      </c>
+      <c r="J14" s="28" t="n"/>
+      <c r="K14" s="28" t="n"/>
+      <c r="L14" s="28" t="n"/>
+      <c r="M14" s="28" t="n"/>
+      <c r="N14" s="29" t="str">
+        <f>IF(OR(A14="",H14=""),"",IF(H14=0,"Sem cobrança",IF(H14&lt;F14,"Abaixo do mínimo",IF(H14&lt;G14,"Entre mínimo e alvo","No alvo ou acima"))))</f>
+        <v>No alvo ou acima</v>
+      </c>
+      <c r="O14" s="30">
+        <f>IF(A14="","",SUMPRODUCT((I14:M14&lt;&gt;"")*(I14:M14&gt;0)*(I14:M14*(1-Config!$B$8)&lt;E14)))</f>
         <v>1</v>
       </c>
-      <c r="P12" s="27" t="n">
+      <c r="P14" s="23" t="n">
         <v>30</v>
       </c>
-      <c r="Q12" s="32" t="n">
+      <c r="Q14" s="28" t="n">
         <v>10380</v>
       </c>
-      <c r="R12" s="30">
-        <f>IF(OR(A12="",P12="",P12=0),"",Q12/P12)</f>
+      <c r="R14" s="26">
+        <f>IF(OR(A14="",P14="",P14=0),"",Q14/P14)</f>
         <v>346</v>
       </c>
-      <c r="S12" s="35">
-        <f>IF(OR(R12="",F12="",H12=0),"",R12/F12-1)</f>
+      <c r="S14" s="31">
+        <f>IF(OR(R14="",F14="",H14=0),"",R14/F14-1)</f>
         <v>0.244756097560976</v>
       </c>
-      <c r="T12" s="26" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="26" t="n"/>
-      <c r="B13" s="27" t="n"/>
-      <c r="C13" s="28" t="n"/>
-      <c r="D13" s="29" t="n"/>
-      <c r="E13" s="30">
-        <f>IF(A13="","",(B13+IF(C13="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D13)</f>
-        <v/>
-      </c>
-      <c r="F13" s="31">
-        <f>IF(A13="","",IFERROR(E13/(1-Config!$B$8-Config!$B$9),""))</f>
-        <v/>
-      </c>
-      <c r="G13" s="30">
-        <f>IF(A13="","",IFERROR(E13/(1-Config!$B$8-Config!$B$10),""))</f>
-        <v/>
-      </c>
-      <c r="H13" s="32" t="n"/>
-      <c r="I13" s="32" t="n"/>
-      <c r="J13" s="32" t="n"/>
-      <c r="K13" s="32" t="n"/>
-      <c r="L13" s="32" t="n"/>
-      <c r="M13" s="32" t="n"/>
-      <c r="N13" s="33">
-        <f>IF(OR(A13="",H13=""),"",IF(H13=0,"Sem cobrança",IF(H13&lt;F13,"Abaixo do mínimo",IF(H13&lt;G13,"Entre mínimo e alvo","No alvo ou acima"))))</f>
-        <v/>
-      </c>
-      <c r="O13" s="34">
-        <f>IF(A13="","",SUMPRODUCT((I13:M13&lt;&gt;"")*(I13:M13&gt;0)*(I13:M13&lt;E13)))</f>
-        <v/>
-      </c>
-      <c r="P13" s="27" t="n"/>
-      <c r="Q13" s="32" t="n"/>
-      <c r="R13" s="30">
-        <f>IF(OR(A13="",P13="",P13=0),"",Q13/P13)</f>
-        <v/>
-      </c>
-      <c r="S13" s="35">
-        <f>IF(OR(R13="",F13="",H13=0),"",R13/F13-1)</f>
-        <v/>
-      </c>
-      <c r="T13" s="26" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="26" t="n"/>
-      <c r="B14" s="27" t="n"/>
-      <c r="C14" s="28" t="n"/>
-      <c r="D14" s="29" t="n"/>
-      <c r="E14" s="30">
-        <f>IF(A14="","",(B14+IF(C14="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D14)</f>
-        <v/>
-      </c>
-      <c r="F14" s="31">
-        <f>IF(A14="","",IFERROR(E14/(1-Config!$B$8-Config!$B$9),""))</f>
-        <v/>
-      </c>
-      <c r="G14" s="30">
-        <f>IF(A14="","",IFERROR(E14/(1-Config!$B$8-Config!$B$10),""))</f>
-        <v/>
-      </c>
-      <c r="H14" s="32" t="n"/>
-      <c r="I14" s="32" t="n"/>
-      <c r="J14" s="32" t="n"/>
-      <c r="K14" s="32" t="n"/>
-      <c r="L14" s="32" t="n"/>
-      <c r="M14" s="32" t="n"/>
-      <c r="N14" s="33">
-        <f>IF(OR(A14="",H14=""),"",IF(H14=0,"Sem cobrança",IF(H14&lt;F14,"Abaixo do mínimo",IF(H14&lt;G14,"Entre mínimo e alvo","No alvo ou acima"))))</f>
-        <v/>
-      </c>
-      <c r="O14" s="34">
-        <f>IF(A14="","",SUMPRODUCT((I14:M14&lt;&gt;"")*(I14:M14&gt;0)*(I14:M14&lt;E14)))</f>
-        <v/>
-      </c>
-      <c r="P14" s="27" t="n"/>
-      <c r="Q14" s="32" t="n"/>
-      <c r="R14" s="30">
-        <f>IF(OR(A14="",P14="",P14=0),"",Q14/P14)</f>
-        <v/>
-      </c>
-      <c r="S14" s="35">
-        <f>IF(OR(R14="",F14="",H14=0),"",R14/F14-1)</f>
-        <v/>
-      </c>
-      <c r="T14" s="26" t="n"/>
+      <c r="T14" s="22" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="26" t="n"/>
-      <c r="B15" s="27" t="n"/>
-      <c r="C15" s="28" t="n"/>
-      <c r="D15" s="29" t="n"/>
-      <c r="E15" s="30">
+      <c r="A15" s="22" t="n"/>
+      <c r="B15" s="23" t="n"/>
+      <c r="C15" s="24" t="n"/>
+      <c r="D15" s="25" t="n"/>
+      <c r="E15" s="26">
         <f>IF(A15="","",(B15+IF(C15="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D15)</f>
         <v/>
       </c>
-      <c r="F15" s="31">
+      <c r="F15" s="27">
         <f>IF(A15="","",IFERROR(E15/(1-Config!$B$8-Config!$B$9),""))</f>
         <v/>
       </c>
-      <c r="G15" s="30">
+      <c r="G15" s="26">
         <f>IF(A15="","",IFERROR(E15/(1-Config!$B$8-Config!$B$10),""))</f>
         <v/>
       </c>
-      <c r="H15" s="32" t="n"/>
-      <c r="I15" s="32" t="n"/>
-      <c r="J15" s="32" t="n"/>
-      <c r="K15" s="32" t="n"/>
-      <c r="L15" s="32" t="n"/>
-      <c r="M15" s="32" t="n"/>
-      <c r="N15" s="33">
+      <c r="H15" s="28" t="n"/>
+      <c r="I15" s="28" t="n"/>
+      <c r="J15" s="28" t="n"/>
+      <c r="K15" s="28" t="n"/>
+      <c r="L15" s="28" t="n"/>
+      <c r="M15" s="28" t="n"/>
+      <c r="N15" s="29">
         <f>IF(OR(A15="",H15=""),"",IF(H15=0,"Sem cobrança",IF(H15&lt;F15,"Abaixo do mínimo",IF(H15&lt;G15,"Entre mínimo e alvo","No alvo ou acima"))))</f>
         <v/>
       </c>
-      <c r="O15" s="34">
-        <f>IF(A15="","",SUMPRODUCT((I15:M15&lt;&gt;"")*(I15:M15&gt;0)*(I15:M15&lt;E15)))</f>
-        <v/>
-      </c>
-      <c r="P15" s="27" t="n"/>
-      <c r="Q15" s="32" t="n"/>
-      <c r="R15" s="30">
+      <c r="O15" s="30">
+        <f>IF(A15="","",SUMPRODUCT((I15:M15&lt;&gt;"")*(I15:M15&gt;0)*(I15:M15*(1-Config!$B$8)&lt;E15)))</f>
+        <v/>
+      </c>
+      <c r="P15" s="23" t="n"/>
+      <c r="Q15" s="28" t="n"/>
+      <c r="R15" s="26">
         <f>IF(OR(A15="",P15="",P15=0),"",Q15/P15)</f>
         <v/>
       </c>
-      <c r="S15" s="35">
+      <c r="S15" s="31">
         <f>IF(OR(R15="",F15="",H15=0),"",R15/F15-1)</f>
         <v/>
       </c>
-      <c r="T15" s="26" t="n"/>
+      <c r="T15" s="22" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="26" t="n"/>
-      <c r="B16" s="27" t="n"/>
-      <c r="C16" s="28" t="n"/>
-      <c r="D16" s="29" t="n"/>
-      <c r="E16" s="30">
+      <c r="A16" s="22" t="n"/>
+      <c r="B16" s="23" t="n"/>
+      <c r="C16" s="24" t="n"/>
+      <c r="D16" s="25" t="n"/>
+      <c r="E16" s="26">
         <f>IF(A16="","",(B16+IF(C16="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D16)</f>
         <v/>
       </c>
-      <c r="F16" s="31">
+      <c r="F16" s="27">
         <f>IF(A16="","",IFERROR(E16/(1-Config!$B$8-Config!$B$9),""))</f>
         <v/>
       </c>
-      <c r="G16" s="30">
+      <c r="G16" s="26">
         <f>IF(A16="","",IFERROR(E16/(1-Config!$B$8-Config!$B$10),""))</f>
         <v/>
       </c>
-      <c r="H16" s="32" t="n"/>
-      <c r="I16" s="32" t="n"/>
-      <c r="J16" s="32" t="n"/>
-      <c r="K16" s="32" t="n"/>
-      <c r="L16" s="32" t="n"/>
-      <c r="M16" s="32" t="n"/>
-      <c r="N16" s="33">
+      <c r="H16" s="28" t="n"/>
+      <c r="I16" s="28" t="n"/>
+      <c r="J16" s="28" t="n"/>
+      <c r="K16" s="28" t="n"/>
+      <c r="L16" s="28" t="n"/>
+      <c r="M16" s="28" t="n"/>
+      <c r="N16" s="29">
         <f>IF(OR(A16="",H16=""),"",IF(H16=0,"Sem cobrança",IF(H16&lt;F16,"Abaixo do mínimo",IF(H16&lt;G16,"Entre mínimo e alvo","No alvo ou acima"))))</f>
         <v/>
       </c>
-      <c r="O16" s="34">
-        <f>IF(A16="","",SUMPRODUCT((I16:M16&lt;&gt;"")*(I16:M16&gt;0)*(I16:M16&lt;E16)))</f>
-        <v/>
-      </c>
-      <c r="P16" s="27" t="n"/>
-      <c r="Q16" s="32" t="n"/>
-      <c r="R16" s="30">
+      <c r="O16" s="30">
+        <f>IF(A16="","",SUMPRODUCT((I16:M16&lt;&gt;"")*(I16:M16&gt;0)*(I16:M16*(1-Config!$B$8)&lt;E16)))</f>
+        <v/>
+      </c>
+      <c r="P16" s="23" t="n"/>
+      <c r="Q16" s="28" t="n"/>
+      <c r="R16" s="26">
         <f>IF(OR(A16="",P16="",P16=0),"",Q16/P16)</f>
         <v/>
       </c>
-      <c r="S16" s="35">
+      <c r="S16" s="31">
         <f>IF(OR(R16="",F16="",H16=0),"",R16/F16-1)</f>
         <v/>
       </c>
-      <c r="T16" s="26" t="n"/>
+      <c r="T16" s="22" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="26" t="n"/>
-      <c r="B17" s="27" t="n"/>
-      <c r="C17" s="28" t="n"/>
-      <c r="D17" s="29" t="n"/>
-      <c r="E17" s="30">
+      <c r="A17" s="22" t="n"/>
+      <c r="B17" s="23" t="n"/>
+      <c r="C17" s="24" t="n"/>
+      <c r="D17" s="25" t="n"/>
+      <c r="E17" s="26">
         <f>IF(A17="","",(B17+IF(C17="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D17)</f>
         <v/>
       </c>
-      <c r="F17" s="31">
+      <c r="F17" s="27">
         <f>IF(A17="","",IFERROR(E17/(1-Config!$B$8-Config!$B$9),""))</f>
         <v/>
       </c>
-      <c r="G17" s="30">
+      <c r="G17" s="26">
         <f>IF(A17="","",IFERROR(E17/(1-Config!$B$8-Config!$B$10),""))</f>
         <v/>
       </c>
-      <c r="H17" s="32" t="n"/>
-      <c r="I17" s="32" t="n"/>
-      <c r="J17" s="32" t="n"/>
-      <c r="K17" s="32" t="n"/>
-      <c r="L17" s="32" t="n"/>
-      <c r="M17" s="32" t="n"/>
-      <c r="N17" s="33">
+      <c r="H17" s="28" t="n"/>
+      <c r="I17" s="28" t="n"/>
+      <c r="J17" s="28" t="n"/>
+      <c r="K17" s="28" t="n"/>
+      <c r="L17" s="28" t="n"/>
+      <c r="M17" s="28" t="n"/>
+      <c r="N17" s="29">
         <f>IF(OR(A17="",H17=""),"",IF(H17=0,"Sem cobrança",IF(H17&lt;F17,"Abaixo do mínimo",IF(H17&lt;G17,"Entre mínimo e alvo","No alvo ou acima"))))</f>
         <v/>
       </c>
-      <c r="O17" s="34">
-        <f>IF(A17="","",SUMPRODUCT((I17:M17&lt;&gt;"")*(I17:M17&gt;0)*(I17:M17&lt;E17)))</f>
-        <v/>
-      </c>
-      <c r="P17" s="27" t="n"/>
-      <c r="Q17" s="32" t="n"/>
-      <c r="R17" s="30">
+      <c r="O17" s="30">
+        <f>IF(A17="","",SUMPRODUCT((I17:M17&lt;&gt;"")*(I17:M17&gt;0)*(I17:M17*(1-Config!$B$8)&lt;E17)))</f>
+        <v/>
+      </c>
+      <c r="P17" s="23" t="n"/>
+      <c r="Q17" s="28" t="n"/>
+      <c r="R17" s="26">
         <f>IF(OR(A17="",P17="",P17=0),"",Q17/P17)</f>
         <v/>
       </c>
-      <c r="S17" s="35">
+      <c r="S17" s="31">
         <f>IF(OR(R17="",F17="",H17=0),"",R17/F17-1)</f>
         <v/>
       </c>
-      <c r="T17" s="26" t="n"/>
-    </row>
-    <row r="18"/>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="36" t="inlineStr">
-        <is>
-          <t>Custo cheio, preço mínimo e preço alvo: a mesma conta da planilha 06 (tempo com retorno × custo-hora + material; ÷ (1 − impostos − margem)). Tabela de convênio em vermelho: abaixo do custo cheio; amarela: cobre o custo, mas não a margem mínima.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="36" t="inlineStr">
+      <c r="T17" s="22" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="n"/>
+      <c r="B18" s="23" t="n"/>
+      <c r="C18" s="24" t="n"/>
+      <c r="D18" s="25" t="n"/>
+      <c r="E18" s="26">
+        <f>IF(A18="","",(B18+IF(C18="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D18)</f>
+        <v/>
+      </c>
+      <c r="F18" s="27">
+        <f>IF(A18="","",IFERROR(E18/(1-Config!$B$8-Config!$B$9),""))</f>
+        <v/>
+      </c>
+      <c r="G18" s="26">
+        <f>IF(A18="","",IFERROR(E18/(1-Config!$B$8-Config!$B$10),""))</f>
+        <v/>
+      </c>
+      <c r="H18" s="28" t="n"/>
+      <c r="I18" s="28" t="n"/>
+      <c r="J18" s="28" t="n"/>
+      <c r="K18" s="28" t="n"/>
+      <c r="L18" s="28" t="n"/>
+      <c r="M18" s="28" t="n"/>
+      <c r="N18" s="29">
+        <f>IF(OR(A18="",H18=""),"",IF(H18=0,"Sem cobrança",IF(H18&lt;F18,"Abaixo do mínimo",IF(H18&lt;G18,"Entre mínimo e alvo","No alvo ou acima"))))</f>
+        <v/>
+      </c>
+      <c r="O18" s="30">
+        <f>IF(A18="","",SUMPRODUCT((I18:M18&lt;&gt;"")*(I18:M18&gt;0)*(I18:M18*(1-Config!$B$8)&lt;E18)))</f>
+        <v/>
+      </c>
+      <c r="P18" s="23" t="n"/>
+      <c r="Q18" s="28" t="n"/>
+      <c r="R18" s="26">
+        <f>IF(OR(A18="",P18="",P18=0),"",Q18/P18)</f>
+        <v/>
+      </c>
+      <c r="S18" s="31">
+        <f>IF(OR(R18="",F18="",H18=0),"",R18/F18-1)</f>
+        <v/>
+      </c>
+      <c r="T18" s="22" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="n"/>
+      <c r="B19" s="23" t="n"/>
+      <c r="C19" s="24" t="n"/>
+      <c r="D19" s="25" t="n"/>
+      <c r="E19" s="26">
+        <f>IF(A19="","",(B19+IF(C19="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D19)</f>
+        <v/>
+      </c>
+      <c r="F19" s="27">
+        <f>IF(A19="","",IFERROR(E19/(1-Config!$B$8-Config!$B$9),""))</f>
+        <v/>
+      </c>
+      <c r="G19" s="26">
+        <f>IF(A19="","",IFERROR(E19/(1-Config!$B$8-Config!$B$10),""))</f>
+        <v/>
+      </c>
+      <c r="H19" s="28" t="n"/>
+      <c r="I19" s="28" t="n"/>
+      <c r="J19" s="28" t="n"/>
+      <c r="K19" s="28" t="n"/>
+      <c r="L19" s="28" t="n"/>
+      <c r="M19" s="28" t="n"/>
+      <c r="N19" s="29">
+        <f>IF(OR(A19="",H19=""),"",IF(H19=0,"Sem cobrança",IF(H19&lt;F19,"Abaixo do mínimo",IF(H19&lt;G19,"Entre mínimo e alvo","No alvo ou acima"))))</f>
+        <v/>
+      </c>
+      <c r="O19" s="30">
+        <f>IF(A19="","",SUMPRODUCT((I19:M19&lt;&gt;"")*(I19:M19&gt;0)*(I19:M19*(1-Config!$B$8)&lt;E19)))</f>
+        <v/>
+      </c>
+      <c r="P19" s="23" t="n"/>
+      <c r="Q19" s="28" t="n"/>
+      <c r="R19" s="26">
+        <f>IF(OR(A19="",P19="",P19=0),"",Q19/P19)</f>
+        <v/>
+      </c>
+      <c r="S19" s="31">
+        <f>IF(OR(R19="",F19="",H19=0),"",R19/F19-1)</f>
+        <v/>
+      </c>
+      <c r="T19" s="22" t="n"/>
+    </row>
+    <row r="20"/>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="32" t="inlineStr">
+        <is>
+          <t>Custo cheio, preço mínimo e preço alvo: a mesma conta da planilha 06 (tempo com retorno × custo-hora + material; ÷ (1 − impostos − margem)). Tabela de convênio em vermelho: depois dos impostos não cobre o custo cheio (margem negativa) — é a mesma conta e o mesmo número do KPI "Tabelas de convênio abaixo do custo cheio + imposto" e do Resumo da planilha 06. Amarela: cobre o custo, mas não a margem mínima.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="32" t="inlineStr">
         <is>
           <t>Realizados e Produção no mês: copie de "Por procedimento" no Painel da planilha 01 com o mês fechado escolhido em Config (no exemplo, agosto de 2026). Valor médio praticado = produção ÷ realizados: mistura particular e convênio, por isso fica abaixo do preço particular.</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="36" t="inlineStr">
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="32" t="inlineStr">
         <is>
           <t>Referência de mercado é opcional e sua: pesquise a faixa da sua região e anote; a planilha não afirma preço de mercado. A tabela de preços e a divulgação de valores seguem as regras do CFM: revise antes de publicar.</t>
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" s="37" t="inlineStr">
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="33" t="inlineStr">
         <is>
           <t>Valor por hora de atendimento, por pagador (tabela ÷ tempo com retorno)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="32" customHeight="1">
-      <c r="A24" s="25" t="inlineStr">
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="21" t="inlineStr">
         <is>
           <t>Procedimento</t>
         </is>
       </c>
-      <c r="B24" s="25" t="inlineStr">
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>Minutos com retorno</t>
         </is>
       </c>
-      <c r="C24" s="25" t="str">
+      <c r="C26" s="21" t="str">
         <f>IF(Config!$B$17="","",Config!$B$17)</f>
         <v>Particular</v>
       </c>
-      <c r="D24" s="25" t="str">
+      <c r="D26" s="21" t="str">
         <f>IF(Config!$B$18="","",Config!$B$18)</f>
         <v>Saúde Total</v>
       </c>
-      <c r="E24" s="25" t="str">
+      <c r="E26" s="21" t="str">
         <f>IF(Config!$B$19="","",Config!$B$19)</f>
         <v>MediPlan</v>
       </c>
-      <c r="F24" s="25" t="str">
+      <c r="F26" s="21" t="str">
         <f>IF(Config!$B$20="","",Config!$B$20)</f>
         <v>Vida Care</v>
       </c>
-      <c r="G24" s="25">
+      <c r="G26" s="21">
         <f>IF(Config!$B$21="","",Config!$B$21)</f>
         <v/>
       </c>
-      <c r="H24" s="25">
+      <c r="H26" s="21">
         <f>IF(Config!$B$22="","",Config!$B$22)</f>
         <v/>
       </c>
-      <c r="I24" s="25" t="inlineStr">
+      <c r="I26" s="21" t="inlineStr">
         <is>
           <t>Hora mínima</t>
         </is>
       </c>
-      <c r="J24" s="25" t="inlineStr">
+      <c r="J26" s="21" t="inlineStr">
         <is>
           <t>Hora alvo</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="38" t="str">
-        <f>IF($A6="","",$A6)</f>
+    <row r="27">
+      <c r="A27" s="34" t="str">
+        <f>IF($A8="","",$A8)</f>
         <v>Consulta</v>
       </c>
-      <c r="B25" s="39">
-        <f>IF($A6="","",B6+IF(C6="Sim",Config!$B$11*Config!$B$12,0))</f>
+      <c r="B27" s="35">
+        <f>IF($A8="","",B8+IF(C8="Sim",Config!$B$11*Config!$B$12,0))</f>
         <v>38</v>
       </c>
-      <c r="C25" s="40">
-        <f>IF(OR($A6="",H6="",$B25=0),"",H6/($B25/60))</f>
+      <c r="C27" s="36">
+        <f>IF(OR($A8="",H8="",$B27=0),"",H8/($B27/60))</f>
         <v>600</v>
       </c>
-      <c r="D25" s="40">
-        <f>IF(OR($A6="",I6="",$B25=0),"",I6/($B25/60))</f>
+      <c r="D27" s="36">
+        <f>IF(OR($A8="",I8="",$B27=0),"",I8/($B27/60))</f>
         <v>189.473684210526</v>
       </c>
-      <c r="E25" s="40">
-        <f>IF(OR($A6="",J6="",$B25=0),"",J6/($B25/60))</f>
+      <c r="E27" s="36">
+        <f>IF(OR($A8="",J8="",$B27=0),"",J8/($B27/60))</f>
         <v>157.894736842105</v>
       </c>
-      <c r="F25" s="40">
-        <f>IF(OR($A6="",K6="",$B25=0),"",K6/($B25/60))</f>
+      <c r="F27" s="36">
+        <f>IF(OR($A8="",K8="",$B27=0),"",K8/($B27/60))</f>
         <v>142.105263157895</v>
       </c>
-      <c r="G25" s="40">
-        <f>IF(OR($A6="",L6="",$B25=0),"",L6/($B25/60))</f>
-        <v/>
-      </c>
-      <c r="H25" s="40">
-        <f>IF(OR($A6="",M6="",$B25=0),"",M6/($B25/60))</f>
-        <v/>
-      </c>
-      <c r="I25" s="40">
-        <f>IF($A6="","",Config!$B$13)</f>
-        <v>338.983050847458</v>
-      </c>
-      <c r="J25" s="40">
-        <f>IF($A6="","",Config!$B$14)</f>
-        <v>454.545454545455</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="38" t="str">
-        <f>IF($A7="","",$A7)</f>
-        <v>Retorno</v>
-      </c>
-      <c r="B26" s="39">
-        <f>IF($A7="","",B7+IF(C7="Sim",Config!$B$11*Config!$B$12,0))</f>
-        <v>20</v>
-      </c>
-      <c r="C26" s="40">
-        <f>IF(OR($A7="",H7="",$B26=0),"",H7/($B26/60))</f>
-        <v>0</v>
-      </c>
-      <c r="D26" s="40">
-        <f>IF(OR($A7="",I7="",$B26=0),"",I7/($B26/60))</f>
-        <v>0</v>
-      </c>
-      <c r="E26" s="40">
-        <f>IF(OR($A7="",J7="",$B26=0),"",J7/($B26/60))</f>
-        <v>0</v>
-      </c>
-      <c r="F26" s="40">
-        <f>IF(OR($A7="",K7="",$B26=0),"",K7/($B26/60))</f>
-        <v>0</v>
-      </c>
-      <c r="G26" s="40">
-        <f>IF(OR($A7="",L7="",$B26=0),"",L7/($B26/60))</f>
-        <v/>
-      </c>
-      <c r="H26" s="40">
-        <f>IF(OR($A7="",M7="",$B26=0),"",M7/($B26/60))</f>
-        <v/>
-      </c>
-      <c r="I26" s="40">
-        <f>IF($A7="","",Config!$B$13)</f>
-        <v>338.983050847458</v>
-      </c>
-      <c r="J26" s="40">
-        <f>IF($A7="","",Config!$B$14)</f>
-        <v>454.545454545455</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="38" t="str">
-        <f>IF($A8="","",$A8)</f>
-        <v>ECG</v>
-      </c>
-      <c r="B27" s="39">
-        <f>IF($A8="","",B8+IF(C8="Sim",Config!$B$11*Config!$B$12,0))</f>
-        <v>20</v>
-      </c>
-      <c r="C27" s="40">
-        <f>IF(OR($A8="",H8="",$B27=0),"",H8/($B27/60))</f>
-        <v>390</v>
-      </c>
-      <c r="D27" s="40">
-        <f>IF(OR($A8="",I8="",$B27=0),"",I8/($B27/60))</f>
-        <v>120</v>
-      </c>
-      <c r="E27" s="40">
-        <f>IF(OR($A8="",J8="",$B27=0),"",J8/($B27/60))</f>
-        <v>105</v>
-      </c>
-      <c r="F27" s="40">
-        <f>IF(OR($A8="",K8="",$B27=0),"",K8/($B27/60))</f>
-        <v>96</v>
-      </c>
-      <c r="G27" s="40">
+      <c r="G27" s="36">
         <f>IF(OR($A8="",L8="",$B27=0),"",L8/($B27/60))</f>
         <v/>
       </c>
-      <c r="H27" s="40">
+      <c r="H27" s="36">
         <f>IF(OR($A8="",M8="",$B27=0),"",M8/($B27/60))</f>
         <v/>
       </c>
-      <c r="I27" s="40">
+      <c r="I27" s="36">
         <f>IF($A8="","",Config!$B$13)</f>
         <v>338.983050847458</v>
       </c>
-      <c r="J27" s="40">
+      <c r="J27" s="36">
         <f>IF($A8="","",Config!$B$14)</f>
         <v>454.545454545455</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="38" t="str">
+      <c r="A28" s="34" t="str">
         <f>IF($A9="","",$A9)</f>
-        <v>MAPA</v>
-      </c>
-      <c r="B28" s="39">
+        <v>Retorno</v>
+      </c>
+      <c r="B28" s="35">
         <f>IF($A9="","",B9+IF(C9="Sim",Config!$B$11*Config!$B$12,0))</f>
         <v>20</v>
       </c>
-      <c r="C28" s="40">
+      <c r="C28" s="36">
         <f>IF(OR($A9="",H9="",$B28=0),"",H9/($B28/60))</f>
-        <v>900</v>
-      </c>
-      <c r="D28" s="40">
+        <v>0</v>
+      </c>
+      <c r="D28" s="36">
         <f>IF(OR($A9="",I9="",$B28=0),"",I9/($B28/60))</f>
-        <v>285</v>
-      </c>
-      <c r="E28" s="40">
+        <v>0</v>
+      </c>
+      <c r="E28" s="36">
         <f>IF(OR($A9="",J9="",$B28=0),"",J9/($B28/60))</f>
-        <v>255</v>
-      </c>
-      <c r="F28" s="40">
+        <v>0</v>
+      </c>
+      <c r="F28" s="36">
         <f>IF(OR($A9="",K9="",$B28=0),"",K9/($B28/60))</f>
-        <v>225</v>
-      </c>
-      <c r="G28" s="40">
+        <v>0</v>
+      </c>
+      <c r="G28" s="36">
         <f>IF(OR($A9="",L9="",$B28=0),"",L9/($B28/60))</f>
         <v/>
       </c>
-      <c r="H28" s="40">
+      <c r="H28" s="36">
         <f>IF(OR($A9="",M9="",$B28=0),"",M9/($B28/60))</f>
         <v/>
       </c>
-      <c r="I28" s="40">
+      <c r="I28" s="36">
         <f>IF($A9="","",Config!$B$13)</f>
         <v>338.983050847458</v>
       </c>
-      <c r="J28" s="40">
+      <c r="J28" s="36">
         <f>IF($A9="","",Config!$B$14)</f>
         <v>454.545454545455</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="38" t="str">
+      <c r="A29" s="34" t="str">
         <f>IF($A10="","",$A10)</f>
-        <v>Holter</v>
-      </c>
-      <c r="B29" s="39">
+        <v>ECG</v>
+      </c>
+      <c r="B29" s="35">
         <f>IF($A10="","",B10+IF(C10="Sim",Config!$B$11*Config!$B$12,0))</f>
         <v>20</v>
       </c>
-      <c r="C29" s="40">
+      <c r="C29" s="36">
         <f>IF(OR($A10="",H10="",$B29=0),"",H10/($B29/60))</f>
-        <v>1050</v>
-      </c>
-      <c r="D29" s="40">
+        <v>390</v>
+      </c>
+      <c r="D29" s="36">
         <f>IF(OR($A10="",I10="",$B29=0),"",I10/($B29/60))</f>
-        <v>315</v>
-      </c>
-      <c r="E29" s="40">
+        <v>120</v>
+      </c>
+      <c r="E29" s="36">
         <f>IF(OR($A10="",J10="",$B29=0),"",J10/($B29/60))</f>
-        <v>285</v>
-      </c>
-      <c r="F29" s="40">
+        <v>105</v>
+      </c>
+      <c r="F29" s="36">
         <f>IF(OR($A10="",K10="",$B29=0),"",K10/($B29/60))</f>
-        <v>255</v>
-      </c>
-      <c r="G29" s="40">
+        <v>96</v>
+      </c>
+      <c r="G29" s="36">
         <f>IF(OR($A10="",L10="",$B29=0),"",L10/($B29/60))</f>
         <v/>
       </c>
-      <c r="H29" s="40">
+      <c r="H29" s="36">
         <f>IF(OR($A10="",M10="",$B29=0),"",M10/($B29/60))</f>
         <v/>
       </c>
-      <c r="I29" s="40">
+      <c r="I29" s="36">
         <f>IF($A10="","",Config!$B$13)</f>
         <v>338.983050847458</v>
       </c>
-      <c r="J29" s="40">
+      <c r="J29" s="36">
         <f>IF($A10="","",Config!$B$14)</f>
         <v>454.545454545455</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="38" t="str">
+      <c r="A30" s="34" t="str">
         <f>IF($A11="","",$A11)</f>
-        <v>Teste ergométrico</v>
-      </c>
-      <c r="B30" s="39">
+        <v>MAPA</v>
+      </c>
+      <c r="B30" s="35">
         <f>IF($A11="","",B11+IF(C11="Sim",Config!$B$11*Config!$B$12,0))</f>
-        <v>40</v>
-      </c>
-      <c r="C30" s="40">
+        <v>20</v>
+      </c>
+      <c r="C30" s="36">
         <f>IF(OR($A11="",H11="",$B30=0),"",H11/($B30/60))</f>
-        <v>675</v>
-      </c>
-      <c r="D30" s="40">
+        <v>900</v>
+      </c>
+      <c r="D30" s="36">
         <f>IF(OR($A11="",I11="",$B30=0),"",I11/($B30/60))</f>
-        <v>210</v>
-      </c>
-      <c r="E30" s="40">
+        <v>285</v>
+      </c>
+      <c r="E30" s="36">
         <f>IF(OR($A11="",J11="",$B30=0),"",J11/($B30/60))</f>
-        <v>187.5</v>
-      </c>
-      <c r="F30" s="40">
+        <v>255</v>
+      </c>
+      <c r="F30" s="36">
         <f>IF(OR($A11="",K11="",$B30=0),"",K11/($B30/60))</f>
-        <v>165</v>
-      </c>
-      <c r="G30" s="40">
+        <v>225</v>
+      </c>
+      <c r="G30" s="36">
         <f>IF(OR($A11="",L11="",$B30=0),"",L11/($B30/60))</f>
         <v/>
       </c>
-      <c r="H30" s="40">
+      <c r="H30" s="36">
         <f>IF(OR($A11="",M11="",$B30=0),"",M11/($B30/60))</f>
         <v/>
       </c>
-      <c r="I30" s="40">
+      <c r="I30" s="36">
         <f>IF($A11="","",Config!$B$13)</f>
         <v>338.983050847458</v>
       </c>
-      <c r="J30" s="40">
+      <c r="J30" s="36">
         <f>IF($A11="","",Config!$B$14)</f>
         <v>454.545454545455</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="38" t="str">
+      <c r="A31" s="34" t="str">
         <f>IF($A12="","",$A12)</f>
-        <v>Avaliação endócrina</v>
-      </c>
-      <c r="B31" s="39">
+        <v>Holter</v>
+      </c>
+      <c r="B31" s="35">
         <f>IF($A12="","",B12+IF(C12="Sim",Config!$B$11*Config!$B$12,0))</f>
-        <v>48</v>
-      </c>
-      <c r="C31" s="40">
+        <v>20</v>
+      </c>
+      <c r="C31" s="36">
         <f>IF(OR($A12="",H12="",$B31=0),"",H12/($B31/60))</f>
-        <v>500</v>
-      </c>
-      <c r="D31" s="40">
+        <v>1050</v>
+      </c>
+      <c r="D31" s="36">
         <f>IF(OR($A12="",I12="",$B31=0),"",I12/($B31/60))</f>
-        <v>162.5</v>
-      </c>
-      <c r="E31" s="40">
+        <v>315</v>
+      </c>
+      <c r="E31" s="36">
         <f>IF(OR($A12="",J12="",$B31=0),"",J12/($B31/60))</f>
-        <v/>
-      </c>
-      <c r="F31" s="40">
+        <v>285</v>
+      </c>
+      <c r="F31" s="36">
         <f>IF(OR($A12="",K12="",$B31=0),"",K12/($B31/60))</f>
-        <v/>
-      </c>
-      <c r="G31" s="40">
+        <v>255</v>
+      </c>
+      <c r="G31" s="36">
         <f>IF(OR($A12="",L12="",$B31=0),"",L12/($B31/60))</f>
         <v/>
       </c>
-      <c r="H31" s="40">
+      <c r="H31" s="36">
         <f>IF(OR($A12="",M12="",$B31=0),"",M12/($B31/60))</f>
         <v/>
       </c>
-      <c r="I31" s="40">
+      <c r="I31" s="36">
         <f>IF($A12="","",Config!$B$13)</f>
         <v>338.983050847458</v>
       </c>
-      <c r="J31" s="40">
+      <c r="J31" s="36">
         <f>IF($A12="","",Config!$B$14)</f>
         <v>454.545454545455</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="38">
+      <c r="A32" s="34" t="str">
         <f>IF($A13="","",$A13)</f>
-        <v/>
-      </c>
-      <c r="B32" s="39">
+        <v>Teste ergométrico</v>
+      </c>
+      <c r="B32" s="35">
         <f>IF($A13="","",B13+IF(C13="Sim",Config!$B$11*Config!$B$12,0))</f>
-        <v/>
-      </c>
-      <c r="C32" s="40">
+        <v>40</v>
+      </c>
+      <c r="C32" s="36">
         <f>IF(OR($A13="",H13="",$B32=0),"",H13/($B32/60))</f>
-        <v/>
-      </c>
-      <c r="D32" s="40">
+        <v>675</v>
+      </c>
+      <c r="D32" s="36">
         <f>IF(OR($A13="",I13="",$B32=0),"",I13/($B32/60))</f>
-        <v/>
-      </c>
-      <c r="E32" s="40">
+        <v>210</v>
+      </c>
+      <c r="E32" s="36">
         <f>IF(OR($A13="",J13="",$B32=0),"",J13/($B32/60))</f>
-        <v/>
-      </c>
-      <c r="F32" s="40">
+        <v>187.5</v>
+      </c>
+      <c r="F32" s="36">
         <f>IF(OR($A13="",K13="",$B32=0),"",K13/($B32/60))</f>
-        <v/>
-      </c>
-      <c r="G32" s="40">
+        <v>165</v>
+      </c>
+      <c r="G32" s="36">
         <f>IF(OR($A13="",L13="",$B32=0),"",L13/($B32/60))</f>
         <v/>
       </c>
-      <c r="H32" s="40">
+      <c r="H32" s="36">
         <f>IF(OR($A13="",M13="",$B32=0),"",M13/($B32/60))</f>
         <v/>
       </c>
-      <c r="I32" s="40">
+      <c r="I32" s="36">
         <f>IF($A13="","",Config!$B$13)</f>
-        <v/>
-      </c>
-      <c r="J32" s="40">
+        <v>338.983050847458</v>
+      </c>
+      <c r="J32" s="36">
         <f>IF($A13="","",Config!$B$14)</f>
-        <v/>
+        <v>454.545454545455</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="38">
+      <c r="A33" s="34" t="str">
         <f>IF($A14="","",$A14)</f>
-        <v/>
-      </c>
-      <c r="B33" s="39">
+        <v>Avaliação endócrina</v>
+      </c>
+      <c r="B33" s="35">
         <f>IF($A14="","",B14+IF(C14="Sim",Config!$B$11*Config!$B$12,0))</f>
-        <v/>
-      </c>
-      <c r="C33" s="40">
+        <v>48</v>
+      </c>
+      <c r="C33" s="36">
         <f>IF(OR($A14="",H14="",$B33=0),"",H14/($B33/60))</f>
-        <v/>
-      </c>
-      <c r="D33" s="40">
+        <v>500</v>
+      </c>
+      <c r="D33" s="36">
         <f>IF(OR($A14="",I14="",$B33=0),"",I14/($B33/60))</f>
-        <v/>
-      </c>
-      <c r="E33" s="40">
+        <v>162.5</v>
+      </c>
+      <c r="E33" s="36">
         <f>IF(OR($A14="",J14="",$B33=0),"",J14/($B33/60))</f>
         <v/>
       </c>
-      <c r="F33" s="40">
+      <c r="F33" s="36">
         <f>IF(OR($A14="",K14="",$B33=0),"",K14/($B33/60))</f>
         <v/>
       </c>
-      <c r="G33" s="40">
+      <c r="G33" s="36">
         <f>IF(OR($A14="",L14="",$B33=0),"",L14/($B33/60))</f>
         <v/>
       </c>
-      <c r="H33" s="40">
+      <c r="H33" s="36">
         <f>IF(OR($A14="",M14="",$B33=0),"",M14/($B33/60))</f>
         <v/>
       </c>
-      <c r="I33" s="40">
+      <c r="I33" s="36">
         <f>IF($A14="","",Config!$B$13)</f>
-        <v/>
-      </c>
-      <c r="J33" s="40">
+        <v>338.983050847458</v>
+      </c>
+      <c r="J33" s="36">
         <f>IF($A14="","",Config!$B$14)</f>
-        <v/>
+        <v>454.545454545455</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="38">
+      <c r="A34" s="34">
         <f>IF($A15="","",$A15)</f>
         <v/>
       </c>
-      <c r="B34" s="39">
+      <c r="B34" s="35">
         <f>IF($A15="","",B15+IF(C15="Sim",Config!$B$11*Config!$B$12,0))</f>
         <v/>
       </c>
-      <c r="C34" s="40">
+      <c r="C34" s="36">
         <f>IF(OR($A15="",H15="",$B34=0),"",H15/($B34/60))</f>
         <v/>
       </c>
-      <c r="D34" s="40">
+      <c r="D34" s="36">
         <f>IF(OR($A15="",I15="",$B34=0),"",I15/($B34/60))</f>
         <v/>
       </c>
-      <c r="E34" s="40">
+      <c r="E34" s="36">
         <f>IF(OR($A15="",J15="",$B34=0),"",J15/($B34/60))</f>
         <v/>
       </c>
-      <c r="F34" s="40">
+      <c r="F34" s="36">
         <f>IF(OR($A15="",K15="",$B34=0),"",K15/($B34/60))</f>
         <v/>
       </c>
-      <c r="G34" s="40">
+      <c r="G34" s="36">
         <f>IF(OR($A15="",L15="",$B34=0),"",L15/($B34/60))</f>
         <v/>
       </c>
-      <c r="H34" s="40">
+      <c r="H34" s="36">
         <f>IF(OR($A15="",M15="",$B34=0),"",M15/($B34/60))</f>
         <v/>
       </c>
-      <c r="I34" s="40">
+      <c r="I34" s="36">
         <f>IF($A15="","",Config!$B$13)</f>
         <v/>
       </c>
-      <c r="J34" s="40">
+      <c r="J34" s="36">
         <f>IF($A15="","",Config!$B$14)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="38">
+      <c r="A35" s="34">
         <f>IF($A16="","",$A16)</f>
         <v/>
       </c>
-      <c r="B35" s="39">
+      <c r="B35" s="35">
         <f>IF($A16="","",B16+IF(C16="Sim",Config!$B$11*Config!$B$12,0))</f>
         <v/>
       </c>
-      <c r="C35" s="40">
+      <c r="C35" s="36">
         <f>IF(OR($A16="",H16="",$B35=0),"",H16/($B35/60))</f>
         <v/>
       </c>
-      <c r="D35" s="40">
+      <c r="D35" s="36">
         <f>IF(OR($A16="",I16="",$B35=0),"",I16/($B35/60))</f>
         <v/>
       </c>
-      <c r="E35" s="40">
+      <c r="E35" s="36">
         <f>IF(OR($A16="",J16="",$B35=0),"",J16/($B35/60))</f>
         <v/>
       </c>
-      <c r="F35" s="40">
+      <c r="F35" s="36">
         <f>IF(OR($A16="",K16="",$B35=0),"",K16/($B35/60))</f>
         <v/>
       </c>
-      <c r="G35" s="40">
+      <c r="G35" s="36">
         <f>IF(OR($A16="",L16="",$B35=0),"",L16/($B35/60))</f>
         <v/>
       </c>
-      <c r="H35" s="40">
+      <c r="H35" s="36">
         <f>IF(OR($A16="",M16="",$B35=0),"",M16/($B35/60))</f>
         <v/>
       </c>
-      <c r="I35" s="40">
+      <c r="I35" s="36">
         <f>IF($A16="","",Config!$B$13)</f>
         <v/>
       </c>
-      <c r="J35" s="40">
+      <c r="J35" s="36">
         <f>IF($A16="","",Config!$B$14)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="38">
+      <c r="A36" s="34">
         <f>IF($A17="","",$A17)</f>
         <v/>
       </c>
-      <c r="B36" s="39">
+      <c r="B36" s="35">
         <f>IF($A17="","",B17+IF(C17="Sim",Config!$B$11*Config!$B$12,0))</f>
         <v/>
       </c>
-      <c r="C36" s="40">
+      <c r="C36" s="36">
         <f>IF(OR($A17="",H17="",$B36=0),"",H17/($B36/60))</f>
         <v/>
       </c>
-      <c r="D36" s="40">
+      <c r="D36" s="36">
         <f>IF(OR($A17="",I17="",$B36=0),"",I17/($B36/60))</f>
         <v/>
       </c>
-      <c r="E36" s="40">
+      <c r="E36" s="36">
         <f>IF(OR($A17="",J17="",$B36=0),"",J17/($B36/60))</f>
         <v/>
       </c>
-      <c r="F36" s="40">
+      <c r="F36" s="36">
         <f>IF(OR($A17="",K17="",$B36=0),"",K17/($B36/60))</f>
         <v/>
       </c>
-      <c r="G36" s="40">
+      <c r="G36" s="36">
         <f>IF(OR($A17="",L17="",$B36=0),"",L17/($B36/60))</f>
         <v/>
       </c>
-      <c r="H36" s="40">
+      <c r="H36" s="36">
         <f>IF(OR($A17="",M17="",$B36=0),"",M17/($B36/60))</f>
         <v/>
       </c>
-      <c r="I36" s="40">
+      <c r="I36" s="36">
         <f>IF($A17="","",Config!$B$13)</f>
         <v/>
       </c>
-      <c r="J36" s="40">
+      <c r="J36" s="36">
         <f>IF($A17="","",Config!$B$14)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="41" t="inlineStr">
+      <c r="A37" s="34">
+        <f>IF($A18="","",$A18)</f>
+        <v/>
+      </c>
+      <c r="B37" s="35">
+        <f>IF($A18="","",B18+IF(C18="Sim",Config!$B$11*Config!$B$12,0))</f>
+        <v/>
+      </c>
+      <c r="C37" s="36">
+        <f>IF(OR($A18="",H18="",$B37=0),"",H18/($B37/60))</f>
+        <v/>
+      </c>
+      <c r="D37" s="36">
+        <f>IF(OR($A18="",I18="",$B37=0),"",I18/($B37/60))</f>
+        <v/>
+      </c>
+      <c r="E37" s="36">
+        <f>IF(OR($A18="",J18="",$B37=0),"",J18/($B37/60))</f>
+        <v/>
+      </c>
+      <c r="F37" s="36">
+        <f>IF(OR($A18="",K18="",$B37=0),"",K18/($B37/60))</f>
+        <v/>
+      </c>
+      <c r="G37" s="36">
+        <f>IF(OR($A18="",L18="",$B37=0),"",L18/($B37/60))</f>
+        <v/>
+      </c>
+      <c r="H37" s="36">
+        <f>IF(OR($A18="",M18="",$B37=0),"",M18/($B37/60))</f>
+        <v/>
+      </c>
+      <c r="I37" s="36">
+        <f>IF($A18="","",Config!$B$13)</f>
+        <v/>
+      </c>
+      <c r="J37" s="36">
+        <f>IF($A18="","",Config!$B$14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="34">
+        <f>IF($A19="","",$A19)</f>
+        <v/>
+      </c>
+      <c r="B38" s="35">
+        <f>IF($A19="","",B19+IF(C19="Sim",Config!$B$11*Config!$B$12,0))</f>
+        <v/>
+      </c>
+      <c r="C38" s="36">
+        <f>IF(OR($A19="",H19="",$B38=0),"",H19/($B38/60))</f>
+        <v/>
+      </c>
+      <c r="D38" s="36">
+        <f>IF(OR($A19="",I19="",$B38=0),"",I19/($B38/60))</f>
+        <v/>
+      </c>
+      <c r="E38" s="36">
+        <f>IF(OR($A19="",J19="",$B38=0),"",J19/($B38/60))</f>
+        <v/>
+      </c>
+      <c r="F38" s="36">
+        <f>IF(OR($A19="",K19="",$B38=0),"",K19/($B38/60))</f>
+        <v/>
+      </c>
+      <c r="G38" s="36">
+        <f>IF(OR($A19="",L19="",$B38=0),"",L19/($B38/60))</f>
+        <v/>
+      </c>
+      <c r="H38" s="36">
+        <f>IF(OR($A19="",M19="",$B38=0),"",M19/($B38/60))</f>
+        <v/>
+      </c>
+      <c r="I38" s="36">
+        <f>IF($A19="","",Config!$B$13)</f>
+        <v/>
+      </c>
+      <c r="J38" s="36">
+        <f>IF($A19="","",Config!$B$14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="37" t="inlineStr">
         <is>
           <t>Vermelho: abaixo da hora mínima. Verde: na hora alvo ou acima. Retorno aparece vazio (valor zero). Este quadro é o argumento na negociação de tabela: quanto cada convênio paga pela hora da clínica.</t>
         </is>
@@ -2581,68 +2614,68 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="19">
-    <mergeCell ref="A23:J23"/>
     <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A39:T39"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="K5:L5"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="A1:T1"/>
     <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A37:T37"/>
     <mergeCell ref="A21:T21"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="A2:T2"/>
+    <mergeCell ref="A25:J25"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
+    <mergeCell ref="A23:T23"/>
     <mergeCell ref="I4:J4"/>
-    <mergeCell ref="A20:T20"/>
+    <mergeCell ref="A22:T22"/>
     <mergeCell ref="K4:L4"/>
-    <mergeCell ref="A19:T19"/>
   </mergeCells>
-  <conditionalFormatting sqref="N6:N17">
+  <conditionalFormatting sqref="N8:N19">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>N6="Abaixo do mínimo"</formula>
+      <formula>N8="Abaixo do mínimo"</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1">
-      <formula>N6="Entre mínimo e alvo"</formula>
+      <formula>N8="Entre mínimo e alvo"</formula>
     </cfRule>
     <cfRule type="expression" priority="3" dxfId="2">
-      <formula>N6="No alvo ou acima"</formula>
+      <formula>N8="No alvo ou acima"</formula>
     </cfRule>
     <cfRule type="expression" priority="6" dxfId="3">
-      <formula>N6="Sem cobrança"</formula>
+      <formula>N8="Sem cobrança"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I6:M17">
+  <conditionalFormatting sqref="I8:M19">
     <cfRule type="expression" priority="4" dxfId="4">
-      <formula>AND(ISNUMBER(I6),I6&gt;0,I6&lt;$E6)</formula>
+      <formula>AND(ISNUMBER(I8),I8&gt;0,I8*(1-Config!$B$8)&lt;$E8)</formula>
     </cfRule>
     <cfRule type="expression" priority="5" dxfId="1">
-      <formula>AND(ISNUMBER(I6),I6&gt;=$E6,I6&lt;$F6)</formula>
+      <formula>AND(ISNUMBER(I8),I8*(1-Config!$B$8)&gt;=$E8,I8&lt;$F8)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O6:O17">
+  <conditionalFormatting sqref="O8:O19">
     <cfRule type="expression" priority="7" dxfId="5">
-      <formula>AND(ISNUMBER(O6),O6&gt;0)</formula>
+      <formula>AND(ISNUMBER(O8),O8&gt;0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S6:S17">
+  <conditionalFormatting sqref="S8:S19">
     <cfRule type="expression" priority="8" dxfId="5">
-      <formula>AND(ISNUMBER(S6),S6&lt;0)</formula>
+      <formula>AND(ISNUMBER(S8),S8&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C25:H36">
+  <conditionalFormatting sqref="C27:H38">
     <cfRule type="expression" priority="9" dxfId="4">
-      <formula>AND(ISNUMBER(C25),C25&gt;0,C25&lt;Config!$B$13)</formula>
+      <formula>AND(ISNUMBER(C27),C27&gt;0,C27&lt;Config!$B$13)</formula>
     </cfRule>
     <cfRule type="expression" priority="10" dxfId="2">
-      <formula>AND(ISNUMBER(C25),C25&gt;=Config!$B$14)</formula>
+      <formula>AND(ISNUMBER(C27),C27&gt;=Config!$B$14)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="C6:C17" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="C8:C19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2657,7 +2690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -2680,207 +2713,221 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="42" t="inlineStr">
+      <c r="A4" s="38" t="inlineStr">
         <is>
           <t>Nome da clínica</t>
         </is>
       </c>
-      <c r="B4" s="26" t="inlineStr">
+      <c r="B4" s="22" t="inlineStr">
         <is>
           <t>Clínica Vida Plena (exemplo fictício)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="42" t="inlineStr">
+      <c r="A5" s="38" t="inlineStr">
         <is>
           <t>Mês do volume (mês fechado)</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>Agosto de 2026</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="42" t="inlineStr">
+      <c r="A6" s="38" t="inlineStr">
         <is>
           <t>Data de referência</t>
         </is>
       </c>
-      <c r="B6" s="43">
+      <c r="B6" s="39">
         <f>TODAY()</f>
         <v>46279.0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="42" t="inlineStr">
+      <c r="A7" s="38" t="inlineStr">
         <is>
           <t>Custo da hora de atendimento (R$)</t>
         </is>
       </c>
-      <c r="B7" s="29" t="n">
+      <c r="B7" s="25" t="n">
         <v>200</v>
       </c>
-      <c r="C7" s="41" t="inlineStr">
+      <c r="C7" s="37" t="inlineStr">
         <is>
           <t>Copie do Painel da planilha 05 ("Custo da hora de atendimento"). No exemplo, R$ 200,00.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="42" t="inlineStr">
-        <is>
-          <t>Impostos e taxas sobre o que entra (%)</t>
-        </is>
-      </c>
-      <c r="B8" s="44" t="n">
+      <c r="A8" s="38" t="inlineStr">
+        <is>
+          <t>Impostos sobre o que entra (%)</t>
+        </is>
+      </c>
+      <c r="B8" s="40" t="n">
         <v>0.11</v>
       </c>
-      <c r="C8" s="41" t="inlineStr">
-        <is>
-          <t>A mesma alíquota das planilhas 05, 06 e 07 (exemplo: 11 %).</t>
+      <c r="C8" s="37" t="inlineStr">
+        <is>
+          <t>A mesma alíquota efetiva das planilhas 05, 06 e 07 (exemplo: 11 %). Só imposto: a taxa da maquininha não entra aqui (fica na 16 e no resultado 18).</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="42" t="inlineStr">
+      <c r="A9" s="38" t="inlineStr">
         <is>
           <t>Margem mínima sobre o preço (%)</t>
         </is>
       </c>
-      <c r="B9" s="44" t="n">
+      <c r="B9" s="40" t="n">
         <v>0.3</v>
       </c>
-      <c r="C9" s="41" t="inlineStr">
+      <c r="C9" s="37" t="inlineStr">
         <is>
           <t>Piso da faixa (a mesma margem da 05 e da 06).</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="42" t="inlineStr">
+      <c r="A10" s="38" t="inlineStr">
         <is>
           <t>Margem alvo sobre o preço (%)</t>
         </is>
       </c>
-      <c r="B10" s="44" t="n">
+      <c r="B10" s="40" t="n">
         <v>0.45</v>
       </c>
-      <c r="C10" s="41" t="inlineStr">
+      <c r="C10" s="37" t="inlineStr">
         <is>
           <t>Teto da faixa (a mesma da 06).</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="42" t="inlineStr">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>Retornos por consulta (média)</t>
         </is>
       </c>
-      <c r="B11" s="45" t="n">
+      <c r="B11" s="41" t="n">
         <v>0.4</v>
       </c>
-      <c r="C11" s="41" t="inlineStr">
+      <c r="C11" s="37" t="inlineStr">
         <is>
           <t>Iguais à 06: o tempo do retorno entra no custo da consulta.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="42" t="inlineStr">
+      <c r="A12" s="38" t="inlineStr">
         <is>
           <t>Duração do retorno (minutos)</t>
         </is>
       </c>
-      <c r="B12" s="27" t="n">
+      <c r="B12" s="23" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="42" t="inlineStr">
+      <c r="A13" s="38" t="inlineStr">
         <is>
           <t>Hora mínima a cobrar (R$)</t>
         </is>
       </c>
-      <c r="B13" s="31">
+      <c r="B13" s="27">
         <f>IFERROR(B7/(1-B8-B9),"")</f>
         <v>338.983050847458</v>
       </c>
-      <c r="C13" s="41" t="inlineStr">
+      <c r="C13" s="37" t="inlineStr">
         <is>
           <t>Custo-hora ÷ (1 − impostos − margem mínima) = R$ 338,98 no exemplo (a 05 arredonda para R$ 340).</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="42" t="inlineStr">
+      <c r="A14" s="38" t="inlineStr">
         <is>
           <t>Hora alvo (R$)</t>
         </is>
       </c>
-      <c r="B14" s="31">
+      <c r="B14" s="27">
         <f>IFERROR(B7/(1-B8-B10),"")</f>
         <v>454.545454545455</v>
       </c>
-      <c r="C14" s="41" t="inlineStr">
+      <c r="C14" s="37" t="inlineStr">
         <is>
           <t>Custo-hora ÷ (1 − impostos − margem alvo).</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="42" t="inlineStr">
+      <c r="A16" s="38" t="inlineStr">
         <is>
           <t>Pagadores (até 6, na ordem das colunas da Tabela; o primeiro é o particular)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="46" t="inlineStr">
+      <c r="A17" s="42" t="inlineStr">
         <is>
           <t>Nomes</t>
         </is>
       </c>
-      <c r="B17" s="26" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>Particular</t>
         </is>
       </c>
-      <c r="C17" s="41" t="inlineStr">
+      <c r="C17" s="37" t="inlineStr">
         <is>
           <t>Preencha de cima para baixo, sem pular linha. Os mesmos da Config da planilha 01.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="26" t="inlineStr">
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>Saúde Total</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="26" t="inlineStr">
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>MediPlan</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="26" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>Vida Care</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="26" t="n"/>
+      <c r="B21" s="22" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="26" t="n"/>
+      <c r="B22" s="22" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="37" t="inlineStr">
+        <is>
+          <t>Esta planilha é a FONTE ÚNICA da tabela de preços do kit. A aba Tabela é onde o preço é decidido; 06 (precificação), 07 (simulador) e a Config da planilha 01 (agenda) copiam daqui.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="37" t="inlineStr">
+        <is>
+          <t>Ordem de atualização quando um preço muda: 1) aqui, na aba Tabela; 2) planilha 06 · Precificação (colunas do particular e dos convênios); 3) planilha 07 · Simulador (quadro 2, valor de tabela); 4) planilha 01 · Config (tabela de preços por pagador, que é o que a Agenda busca). Procedimentos novos: cadastre na 01 (Config), na 02, aqui, na 06 e na 07. Convênio novo: 01, 02, 06, 07, aqui, 09 (categorias de entrada) e 13 (Config).</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/08-tabela-de-precos.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/08-tabela-de-precos.xlsx
@@ -18,12 +18,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="165" formatCode="&quot;R$&quot; #,##0.00;[Red]-&quot;R$&quot; #,##0.00"/>
-    <numFmt numFmtId="166" formatCode="&quot;R$&quot; #,##0;[Red]-&quot;R$&quot; #,##0"/>
-    <numFmt numFmtId="167" formatCode="+0%;-0%;0%"/>
-    <numFmt numFmtId="168" formatCode="0.0"/>
+  <numFmts count="6">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="166" formatCode="&quot;R$&quot; #,##0.00;[Red]-&quot;R$&quot; #,##0.00"/>
+    <numFmt numFmtId="167" formatCode="&quot;R$&quot; #,##0;[Red]-&quot;R$&quot; #,##0"/>
+    <numFmt numFmtId="168" formatCode="+0%;-0%;0%"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
   </numFmts>
   <fonts count="18">
     <font>
@@ -223,7 +224,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="10" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -232,13 +233,13 @@
     <xf numFmtId="1" fontId="10" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="12" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -255,45 +256,45 @@
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="166" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -925,7 +926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1110,17 +1111,29 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Clínica Vida Plena é uma clínica fictícia. Pacientes, convênios, nomes, contatos e valores são inventados; não há nenhum dado clínico. Apague o exemplo antes de começar. Agenda futura e vencimentos em aberto do exemplo são relativos a hoje.</t>
+          <t>Clínica Vida Plena é uma clínica fictícia. Pacientes, convênios, nomes, contatos e valores são inventados; não há nenhum dado clínico. Apague o exemplo antes de começar.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="46" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
+          <t>Data de referência</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="46" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
           <t>Suporte</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>suporte@seusociogestor.com.br · resposta em até 5 dias úteis · reembolso em até 7 dias pelo mesmo canal.</t>
         </is>
@@ -2742,9 +2755,8 @@
           <t>Data de referência</t>
         </is>
       </c>
-      <c r="B6" s="39">
-        <f>TODAY()</f>
-        <v>46279.0</v>
+      <c r="B6" s="39" t="n">
+        <v>46279</v>
       </c>
     </row>
     <row r="7">

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/08-tabela-de-precos.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/08-tabela-de-precos.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores, semáforos e gráficos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os SEUS dados, troque em Config: a data de referência por =HOJE(), o ano, o mês do painel, o trimestre (onde houver) e a lista de feriados. Trocar só a data de referência deixa o resto apontando para 2026.</t>
         </is>
       </c>
     </row>
@@ -2663,10 +2663,10 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="I8:M19">
     <cfRule type="expression" priority="4" dxfId="4">
-      <formula>AND(ISNUMBER(I8),I8&gt;0,I8*(1-Config!$B$8)&lt;$E8)</formula>
+      <formula>AND(ISNUMBER(I8),I8&gt;0,I8*(1-INDIRECT("Config!$B$8"))&lt;$E8)</formula>
     </cfRule>
     <cfRule type="expression" priority="5" dxfId="1">
-      <formula>AND(ISNUMBER(I8),I8*(1-Config!$B$8)&gt;=$E8,I8&lt;$F8)</formula>
+      <formula>AND(ISNUMBER(I8),I8*(1-INDIRECT("Config!$B$8"))&gt;=$E8,I8&lt;$F8)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O8:O19">
@@ -2681,10 +2681,10 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="C27:H38">
     <cfRule type="expression" priority="9" dxfId="4">
-      <formula>AND(ISNUMBER(C27),C27&gt;0,C27&lt;Config!$B$13)</formula>
+      <formula>AND(ISNUMBER(C27),C27&gt;0,C27&lt;INDIRECT("Config!$B$13"))</formula>
     </cfRule>
     <cfRule type="expression" priority="10" dxfId="2">
-      <formula>AND(ISNUMBER(C27),C27&gt;=Config!$B$14)</formula>
+      <formula>AND(ISNUMBER(C27),C27&gt;=INDIRECT("Config!$B$14"))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/08-tabela-de-precos.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/08-tabela-de-precos.xlsx
@@ -1235,12 +1235,12 @@
       </c>
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="16" t="str">
-        <f>COUNTIF($N$8:$N$19,"Abaixo do mínimo")&amp;" de "&amp;COUNTA($A$8:$A$19)</f>
+        <f>IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,COUNTIF($N$8:$N$19,"Abaixo do mínimo")&amp;" de "&amp;COUNTA($A$8:$A$19))</f>
         <v>0 de 7</v>
       </c>
       <c r="D5" s="10" t="n"/>
       <c r="E5" s="17">
-        <f>SUM($O$8:$O$19)</f>
+        <f>IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,SUM($O$8:$O$19))</f>
         <v>14</v>
       </c>
       <c r="F5" s="10" t="n"/>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="J5" s="14" t="n"/>
       <c r="K5" s="20">
-        <f>IFERROR(I5/Config!$B$13-1,0)</f>
+        <f>IF(NOT(ISNUMBER(Config!$B$13)),"",IFERROR(I5/Config!$B$13-1,0))</f>
         <v>0.212350281690141</v>
       </c>
       <c r="L5" s="8" t="n"/>
@@ -1375,15 +1375,15 @@
         <v>4</v>
       </c>
       <c r="E8" s="26">
-        <f>IF(A8="","",(B8+IF(C8="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D8)</f>
+        <f>IF(A8="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",(B8+IF(C8="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D8))</f>
         <v>130.666666666667</v>
       </c>
       <c r="F8" s="27">
-        <f>IF(A8="","",IFERROR(E8/(1-Config!$B$8-Config!$B$9),""))</f>
+        <f>IF(A8="","",IF(NOT(ISNUMBER(E8)),E8,IF((Config!$B$15&lt;&gt;"Sim"),"margens inválidas (Config)",E8/(1-Config!$B$8-Config!$B$9))))</f>
         <v>221.468926553672</v>
       </c>
       <c r="G8" s="26">
-        <f>IF(A8="","",IFERROR(E8/(1-Config!$B$8-Config!$B$10),""))</f>
+        <f>IF(A8="","",IF(NOT(ISNUMBER(E8)),E8,IF((Config!$B$15&lt;&gt;"Sim"),"margens inválidas (Config)",E8/(1-Config!$B$8-Config!$B$10))))</f>
         <v>296.969696969697</v>
       </c>
       <c r="H8" s="28" t="n">
@@ -1401,11 +1401,11 @@
       <c r="L8" s="28" t="n"/>
       <c r="M8" s="28" t="n"/>
       <c r="N8" s="29" t="str">
-        <f>IF(OR(A8="",H8=""),"",IF(H8=0,"Sem cobrança",IF(H8&lt;F8,"Abaixo do mínimo",IF(H8&lt;G8,"Entre mínimo e alvo","No alvo ou acima"))))</f>
+        <f>IF(OR(A8="",H8=""),"",IF(NOT(ISNUMBER(E8)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(F8)),NOT(ISNUMBER(G8))),"Margens inválidas",IF(H8=0,"Sem cobrança",IF(H8&lt;F8,"Abaixo do mínimo",IF(H8&lt;G8,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="O8" s="30">
-        <f>IF(A8="","",SUMPRODUCT((I8:M8&lt;&gt;"")*(I8:M8&gt;0)*(I8:M8*(1-Config!$B$8)&lt;E8)))</f>
+        <f>IF(OR(A8="",NOT(ISNUMBER(F8))),"",SUMPRODUCT((I8:M8&lt;&gt;"")*(I8:M8&gt;0)*(I8:M8*(1-Config!$B$8)&lt;E8)))</f>
         <v>3</v>
       </c>
       <c r="P8" s="23" t="n">
@@ -1419,7 +1419,7 @@
         <v>236.384615384615</v>
       </c>
       <c r="S8" s="31">
-        <f>IF(OR(R8="",F8="",H8=0),"",R8/F8-1)</f>
+        <f>IF(OR(R8="",NOT(ISNUMBER(F8)),N(H8)=0),"",R8/F8-1)</f>
         <v>0.0673489010989012</v>
       </c>
       <c r="T8" s="22" t="n"/>
@@ -1442,15 +1442,15 @@
         <v>2</v>
       </c>
       <c r="E9" s="26">
-        <f>IF(A9="","",(B9+IF(C9="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D9)</f>
+        <f>IF(A9="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",(B9+IF(C9="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D9))</f>
         <v>68.6666666666667</v>
       </c>
       <c r="F9" s="27">
-        <f>IF(A9="","",IFERROR(E9/(1-Config!$B$8-Config!$B$9),""))</f>
+        <f>IF(A9="","",IF(NOT(ISNUMBER(E9)),E9,IF((Config!$B$15&lt;&gt;"Sim"),"margens inválidas (Config)",E9/(1-Config!$B$8-Config!$B$9))))</f>
         <v>116.38418079096</v>
       </c>
       <c r="G9" s="26">
-        <f>IF(A9="","",IFERROR(E9/(1-Config!$B$8-Config!$B$10),""))</f>
+        <f>IF(A9="","",IF(NOT(ISNUMBER(E9)),E9,IF((Config!$B$15&lt;&gt;"Sim"),"margens inválidas (Config)",E9/(1-Config!$B$8-Config!$B$10))))</f>
         <v>156.060606060606</v>
       </c>
       <c r="H9" s="28" t="n">
@@ -1468,11 +1468,11 @@
       <c r="L9" s="28" t="n"/>
       <c r="M9" s="28" t="n"/>
       <c r="N9" s="29" t="str">
-        <f>IF(OR(A9="",H9=""),"",IF(H9=0,"Sem cobrança",IF(H9&lt;F9,"Abaixo do mínimo",IF(H9&lt;G9,"Entre mínimo e alvo","No alvo ou acima"))))</f>
+        <f>IF(OR(A9="",H9=""),"",IF(NOT(ISNUMBER(E9)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(F9)),NOT(ISNUMBER(G9))),"Margens inválidas",IF(H9=0,"Sem cobrança",IF(H9&lt;F9,"Abaixo do mínimo",IF(H9&lt;G9,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
         <v>Sem cobrança</v>
       </c>
       <c r="O9" s="30">
-        <f>IF(A9="","",SUMPRODUCT((I9:M9&lt;&gt;"")*(I9:M9&gt;0)*(I9:M9*(1-Config!$B$8)&lt;E9)))</f>
+        <f>IF(OR(A9="",NOT(ISNUMBER(F9))),"",SUMPRODUCT((I9:M9&lt;&gt;"")*(I9:M9&gt;0)*(I9:M9*(1-Config!$B$8)&lt;E9)))</f>
         <v>0</v>
       </c>
       <c r="P9" s="23" t="n">
@@ -1486,7 +1486,7 @@
         <v>0</v>
       </c>
       <c r="S9" s="31">
-        <f>IF(OR(R9="",F9="",H9=0),"",R9/F9-1)</f>
+        <f>IF(OR(R9="",NOT(ISNUMBER(F9)),N(H9)=0),"",R9/F9-1)</f>
         <v/>
       </c>
       <c r="T9" s="22" t="n"/>
@@ -1509,15 +1509,15 @@
         <v>8</v>
       </c>
       <c r="E10" s="26">
-        <f>IF(A10="","",(B10+IF(C10="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D10)</f>
+        <f>IF(A10="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",(B10+IF(C10="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D10))</f>
         <v>74.6666666666667</v>
       </c>
       <c r="F10" s="27">
-        <f>IF(A10="","",IFERROR(E10/(1-Config!$B$8-Config!$B$9),""))</f>
+        <f>IF(A10="","",IF(NOT(ISNUMBER(E10)),E10,IF((Config!$B$15&lt;&gt;"Sim"),"margens inválidas (Config)",E10/(1-Config!$B$8-Config!$B$9))))</f>
         <v>126.553672316384</v>
       </c>
       <c r="G10" s="26">
-        <f>IF(A10="","",IFERROR(E10/(1-Config!$B$8-Config!$B$10),""))</f>
+        <f>IF(A10="","",IF(NOT(ISNUMBER(E10)),E10,IF((Config!$B$15&lt;&gt;"Sim"),"margens inválidas (Config)",E10/(1-Config!$B$8-Config!$B$10))))</f>
         <v>169.69696969697</v>
       </c>
       <c r="H10" s="28" t="n">
@@ -1535,11 +1535,11 @@
       <c r="L10" s="28" t="n"/>
       <c r="M10" s="28" t="n"/>
       <c r="N10" s="29" t="str">
-        <f>IF(OR(A10="",H10=""),"",IF(H10=0,"Sem cobrança",IF(H10&lt;F10,"Abaixo do mínimo",IF(H10&lt;G10,"Entre mínimo e alvo","No alvo ou acima"))))</f>
+        <f>IF(OR(A10="",H10=""),"",IF(NOT(ISNUMBER(E10)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(F10)),NOT(ISNUMBER(G10))),"Margens inválidas",IF(H10=0,"Sem cobrança",IF(H10&lt;F10,"Abaixo do mínimo",IF(H10&lt;G10,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
         <v>Entre mínimo e alvo</v>
       </c>
       <c r="O10" s="30">
-        <f>IF(A10="","",SUMPRODUCT((I10:M10&lt;&gt;"")*(I10:M10&gt;0)*(I10:M10*(1-Config!$B$8)&lt;E10)))</f>
+        <f>IF(OR(A10="",NOT(ISNUMBER(F10))),"",SUMPRODUCT((I10:M10&lt;&gt;"")*(I10:M10&gt;0)*(I10:M10*(1-Config!$B$8)&lt;E10)))</f>
         <v>3</v>
       </c>
       <c r="P10" s="23" t="n">
@@ -1553,7 +1553,7 @@
         <v>78.6666666666667</v>
       </c>
       <c r="S10" s="31">
-        <f>IF(OR(R10="",F10="",H10=0),"",R10/F10-1)</f>
+        <f>IF(OR(R10="",NOT(ISNUMBER(F10)),N(H10)=0),"",R10/F10-1)</f>
         <v>-0.378392857142857</v>
       </c>
       <c r="T10" s="22" t="n"/>
@@ -1576,15 +1576,15 @@
         <v>15</v>
       </c>
       <c r="E11" s="26">
-        <f>IF(A11="","",(B11+IF(C11="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D11)</f>
+        <f>IF(A11="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",(B11+IF(C11="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D11))</f>
         <v>81.6666666666667</v>
       </c>
       <c r="F11" s="27">
-        <f>IF(A11="","",IFERROR(E11/(1-Config!$B$8-Config!$B$9),""))</f>
+        <f>IF(A11="","",IF(NOT(ISNUMBER(E11)),E11,IF((Config!$B$15&lt;&gt;"Sim"),"margens inválidas (Config)",E11/(1-Config!$B$8-Config!$B$9))))</f>
         <v>138.418079096045</v>
       </c>
       <c r="G11" s="26">
-        <f>IF(A11="","",IFERROR(E11/(1-Config!$B$8-Config!$B$10),""))</f>
+        <f>IF(A11="","",IF(NOT(ISNUMBER(E11)),E11,IF((Config!$B$15&lt;&gt;"Sim"),"margens inválidas (Config)",E11/(1-Config!$B$8-Config!$B$10))))</f>
         <v>185.606060606061</v>
       </c>
       <c r="H11" s="28" t="n">
@@ -1602,11 +1602,11 @@
       <c r="L11" s="28" t="n"/>
       <c r="M11" s="28" t="n"/>
       <c r="N11" s="29" t="str">
-        <f>IF(OR(A11="",H11=""),"",IF(H11=0,"Sem cobrança",IF(H11&lt;F11,"Abaixo do mínimo",IF(H11&lt;G11,"Entre mínimo e alvo","No alvo ou acima"))))</f>
+        <f>IF(OR(A11="",H11=""),"",IF(NOT(ISNUMBER(E11)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(F11)),NOT(ISNUMBER(G11))),"Margens inválidas",IF(H11=0,"Sem cobrança",IF(H11&lt;F11,"Abaixo do mínimo",IF(H11&lt;G11,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="O11" s="30">
-        <f>IF(A11="","",SUMPRODUCT((I11:M11&lt;&gt;"")*(I11:M11&gt;0)*(I11:M11*(1-Config!$B$8)&lt;E11)))</f>
+        <f>IF(OR(A11="",NOT(ISNUMBER(F11))),"",SUMPRODUCT((I11:M11&lt;&gt;"")*(I11:M11&gt;0)*(I11:M11*(1-Config!$B$8)&lt;E11)))</f>
         <v>2</v>
       </c>
       <c r="P11" s="23" t="n">
@@ -1620,7 +1620,7 @@
         <v>168.125</v>
       </c>
       <c r="S11" s="31">
-        <f>IF(OR(R11="",F11="",H11=0),"",R11/F11-1)</f>
+        <f>IF(OR(R11="",NOT(ISNUMBER(F11)),N(H11)=0),"",R11/F11-1)</f>
         <v>0.214617346938776</v>
       </c>
       <c r="T11" s="22" t="n"/>
@@ -1643,15 +1643,15 @@
         <v>18</v>
       </c>
       <c r="E12" s="26">
-        <f>IF(A12="","",(B12+IF(C12="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D12)</f>
+        <f>IF(A12="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",(B12+IF(C12="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D12))</f>
         <v>84.6666666666667</v>
       </c>
       <c r="F12" s="27">
-        <f>IF(A12="","",IFERROR(E12/(1-Config!$B$8-Config!$B$9),""))</f>
+        <f>IF(A12="","",IF(NOT(ISNUMBER(E12)),E12,IF((Config!$B$15&lt;&gt;"Sim"),"margens inválidas (Config)",E12/(1-Config!$B$8-Config!$B$9))))</f>
         <v>143.502824858757</v>
       </c>
       <c r="G12" s="26">
-        <f>IF(A12="","",IFERROR(E12/(1-Config!$B$8-Config!$B$10),""))</f>
+        <f>IF(A12="","",IF(NOT(ISNUMBER(E12)),E12,IF((Config!$B$15&lt;&gt;"Sim"),"margens inválidas (Config)",E12/(1-Config!$B$8-Config!$B$10))))</f>
         <v>192.424242424242</v>
       </c>
       <c r="H12" s="28" t="n">
@@ -1669,11 +1669,11 @@
       <c r="L12" s="28" t="n"/>
       <c r="M12" s="28" t="n"/>
       <c r="N12" s="29" t="str">
-        <f>IF(OR(A12="",H12=""),"",IF(H12=0,"Sem cobrança",IF(H12&lt;F12,"Abaixo do mínimo",IF(H12&lt;G12,"Entre mínimo e alvo","No alvo ou acima"))))</f>
+        <f>IF(OR(A12="",H12=""),"",IF(NOT(ISNUMBER(E12)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(F12)),NOT(ISNUMBER(G12))),"Margens inválidas",IF(H12=0,"Sem cobrança",IF(H12&lt;F12,"Abaixo do mínimo",IF(H12&lt;G12,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="O12" s="30">
-        <f>IF(A12="","",SUMPRODUCT((I12:M12&lt;&gt;"")*(I12:M12&gt;0)*(I12:M12*(1-Config!$B$8)&lt;E12)))</f>
+        <f>IF(OR(A12="",NOT(ISNUMBER(F12))),"",SUMPRODUCT((I12:M12&lt;&gt;"")*(I12:M12&gt;0)*(I12:M12*(1-Config!$B$8)&lt;E12)))</f>
         <v>2</v>
       </c>
       <c r="P12" s="23" t="n">
@@ -1687,7 +1687,7 @@
         <v>249</v>
       </c>
       <c r="S12" s="31">
-        <f>IF(OR(R12="",F12="",H12=0),"",R12/F12-1)</f>
+        <f>IF(OR(R12="",NOT(ISNUMBER(F12)),N(H12)=0),"",R12/F12-1)</f>
         <v>0.735157480314961</v>
       </c>
       <c r="T12" s="22" t="n"/>
@@ -1710,15 +1710,15 @@
         <v>25</v>
       </c>
       <c r="E13" s="26">
-        <f>IF(A13="","",(B13+IF(C13="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D13)</f>
+        <f>IF(A13="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",(B13+IF(C13="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D13))</f>
         <v>158.333333333333</v>
       </c>
       <c r="F13" s="27">
-        <f>IF(A13="","",IFERROR(E13/(1-Config!$B$8-Config!$B$9),""))</f>
+        <f>IF(A13="","",IF(NOT(ISNUMBER(E13)),E13,IF((Config!$B$15&lt;&gt;"Sim"),"margens inválidas (Config)",E13/(1-Config!$B$8-Config!$B$9))))</f>
         <v>268.361581920904</v>
       </c>
       <c r="G13" s="26">
-        <f>IF(A13="","",IFERROR(E13/(1-Config!$B$8-Config!$B$10),""))</f>
+        <f>IF(A13="","",IF(NOT(ISNUMBER(E13)),E13,IF((Config!$B$15&lt;&gt;"Sim"),"margens inválidas (Config)",E13/(1-Config!$B$8-Config!$B$10))))</f>
         <v>359.848484848485</v>
       </c>
       <c r="H13" s="28" t="n">
@@ -1736,11 +1736,11 @@
       <c r="L13" s="28" t="n"/>
       <c r="M13" s="28" t="n"/>
       <c r="N13" s="29" t="str">
-        <f>IF(OR(A13="",H13=""),"",IF(H13=0,"Sem cobrança",IF(H13&lt;F13,"Abaixo do mínimo",IF(H13&lt;G13,"Entre mínimo e alvo","No alvo ou acima"))))</f>
+        <f>IF(OR(A13="",H13=""),"",IF(NOT(ISNUMBER(E13)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(F13)),NOT(ISNUMBER(G13))),"Margens inválidas",IF(H13=0,"Sem cobrança",IF(H13&lt;F13,"Abaixo do mínimo",IF(H13&lt;G13,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="O13" s="30">
-        <f>IF(A13="","",SUMPRODUCT((I13:M13&lt;&gt;"")*(I13:M13&gt;0)*(I13:M13*(1-Config!$B$8)&lt;E13)))</f>
+        <f>IF(OR(A13="",NOT(ISNUMBER(F13))),"",SUMPRODUCT((I13:M13&lt;&gt;"")*(I13:M13&gt;0)*(I13:M13*(1-Config!$B$8)&lt;E13)))</f>
         <v>3</v>
       </c>
       <c r="P13" s="23" t="n">
@@ -1754,7 +1754,7 @@
         <v>283.75</v>
       </c>
       <c r="S13" s="31">
-        <f>IF(OR(R13="",F13="",H13=0),"",R13/F13-1)</f>
+        <f>IF(OR(R13="",NOT(ISNUMBER(F13)),N(H13)=0),"",R13/F13-1)</f>
         <v>0.0573421052631582</v>
       </c>
       <c r="T13" s="22" t="n"/>
@@ -1777,15 +1777,15 @@
         <v>4</v>
       </c>
       <c r="E14" s="26">
-        <f>IF(A14="","",(B14+IF(C14="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D14)</f>
+        <f>IF(A14="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",(B14+IF(C14="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D14))</f>
         <v>164</v>
       </c>
       <c r="F14" s="27">
-        <f>IF(A14="","",IFERROR(E14/(1-Config!$B$8-Config!$B$9),""))</f>
+        <f>IF(A14="","",IF(NOT(ISNUMBER(E14)),E14,IF((Config!$B$15&lt;&gt;"Sim"),"margens inválidas (Config)",E14/(1-Config!$B$8-Config!$B$9))))</f>
         <v>277.966101694915</v>
       </c>
       <c r="G14" s="26">
-        <f>IF(A14="","",IFERROR(E14/(1-Config!$B$8-Config!$B$10),""))</f>
+        <f>IF(A14="","",IF(NOT(ISNUMBER(E14)),E14,IF((Config!$B$15&lt;&gt;"Sim"),"margens inválidas (Config)",E14/(1-Config!$B$8-Config!$B$10))))</f>
         <v>372.727272727273</v>
       </c>
       <c r="H14" s="28" t="n">
@@ -1799,11 +1799,11 @@
       <c r="L14" s="28" t="n"/>
       <c r="M14" s="28" t="n"/>
       <c r="N14" s="29" t="str">
-        <f>IF(OR(A14="",H14=""),"",IF(H14=0,"Sem cobrança",IF(H14&lt;F14,"Abaixo do mínimo",IF(H14&lt;G14,"Entre mínimo e alvo","No alvo ou acima"))))</f>
+        <f>IF(OR(A14="",H14=""),"",IF(NOT(ISNUMBER(E14)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(F14)),NOT(ISNUMBER(G14))),"Margens inválidas",IF(H14=0,"Sem cobrança",IF(H14&lt;F14,"Abaixo do mínimo",IF(H14&lt;G14,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="O14" s="30">
-        <f>IF(A14="","",SUMPRODUCT((I14:M14&lt;&gt;"")*(I14:M14&gt;0)*(I14:M14*(1-Config!$B$8)&lt;E14)))</f>
+        <f>IF(OR(A14="",NOT(ISNUMBER(F14))),"",SUMPRODUCT((I14:M14&lt;&gt;"")*(I14:M14&gt;0)*(I14:M14*(1-Config!$B$8)&lt;E14)))</f>
         <v>1</v>
       </c>
       <c r="P14" s="23" t="n">
@@ -1817,7 +1817,7 @@
         <v>346</v>
       </c>
       <c r="S14" s="31">
-        <f>IF(OR(R14="",F14="",H14=0),"",R14/F14-1)</f>
+        <f>IF(OR(R14="",NOT(ISNUMBER(F14)),N(H14)=0),"",R14/F14-1)</f>
         <v>0.244756097560976</v>
       </c>
       <c r="T14" s="22" t="n"/>
@@ -1828,15 +1828,15 @@
       <c r="C15" s="24" t="n"/>
       <c r="D15" s="25" t="n"/>
       <c r="E15" s="26">
-        <f>IF(A15="","",(B15+IF(C15="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D15)</f>
+        <f>IF(A15="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",(B15+IF(C15="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D15))</f>
         <v/>
       </c>
       <c r="F15" s="27">
-        <f>IF(A15="","",IFERROR(E15/(1-Config!$B$8-Config!$B$9),""))</f>
+        <f>IF(A15="","",IF(NOT(ISNUMBER(E15)),E15,IF((Config!$B$15&lt;&gt;"Sim"),"margens inválidas (Config)",E15/(1-Config!$B$8-Config!$B$9))))</f>
         <v/>
       </c>
       <c r="G15" s="26">
-        <f>IF(A15="","",IFERROR(E15/(1-Config!$B$8-Config!$B$10),""))</f>
+        <f>IF(A15="","",IF(NOT(ISNUMBER(E15)),E15,IF((Config!$B$15&lt;&gt;"Sim"),"margens inválidas (Config)",E15/(1-Config!$B$8-Config!$B$10))))</f>
         <v/>
       </c>
       <c r="H15" s="28" t="n"/>
@@ -1846,11 +1846,11 @@
       <c r="L15" s="28" t="n"/>
       <c r="M15" s="28" t="n"/>
       <c r="N15" s="29">
-        <f>IF(OR(A15="",H15=""),"",IF(H15=0,"Sem cobrança",IF(H15&lt;F15,"Abaixo do mínimo",IF(H15&lt;G15,"Entre mínimo e alvo","No alvo ou acima"))))</f>
+        <f>IF(OR(A15="",H15=""),"",IF(NOT(ISNUMBER(E15)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(F15)),NOT(ISNUMBER(G15))),"Margens inválidas",IF(H15=0,"Sem cobrança",IF(H15&lt;F15,"Abaixo do mínimo",IF(H15&lt;G15,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
         <v/>
       </c>
       <c r="O15" s="30">
-        <f>IF(A15="","",SUMPRODUCT((I15:M15&lt;&gt;"")*(I15:M15&gt;0)*(I15:M15*(1-Config!$B$8)&lt;E15)))</f>
+        <f>IF(OR(A15="",NOT(ISNUMBER(F15))),"",SUMPRODUCT((I15:M15&lt;&gt;"")*(I15:M15&gt;0)*(I15:M15*(1-Config!$B$8)&lt;E15)))</f>
         <v/>
       </c>
       <c r="P15" s="23" t="n"/>
@@ -1860,7 +1860,7 @@
         <v/>
       </c>
       <c r="S15" s="31">
-        <f>IF(OR(R15="",F15="",H15=0),"",R15/F15-1)</f>
+        <f>IF(OR(R15="",NOT(ISNUMBER(F15)),N(H15)=0),"",R15/F15-1)</f>
         <v/>
       </c>
       <c r="T15" s="22" t="n"/>
@@ -1871,15 +1871,15 @@
       <c r="C16" s="24" t="n"/>
       <c r="D16" s="25" t="n"/>
       <c r="E16" s="26">
-        <f>IF(A16="","",(B16+IF(C16="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D16)</f>
+        <f>IF(A16="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",(B16+IF(C16="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D16))</f>
         <v/>
       </c>
       <c r="F16" s="27">
-        <f>IF(A16="","",IFERROR(E16/(1-Config!$B$8-Config!$B$9),""))</f>
+        <f>IF(A16="","",IF(NOT(ISNUMBER(E16)),E16,IF((Config!$B$15&lt;&gt;"Sim"),"margens inválidas (Config)",E16/(1-Config!$B$8-Config!$B$9))))</f>
         <v/>
       </c>
       <c r="G16" s="26">
-        <f>IF(A16="","",IFERROR(E16/(1-Config!$B$8-Config!$B$10),""))</f>
+        <f>IF(A16="","",IF(NOT(ISNUMBER(E16)),E16,IF((Config!$B$15&lt;&gt;"Sim"),"margens inválidas (Config)",E16/(1-Config!$B$8-Config!$B$10))))</f>
         <v/>
       </c>
       <c r="H16" s="28" t="n"/>
@@ -1889,11 +1889,11 @@
       <c r="L16" s="28" t="n"/>
       <c r="M16" s="28" t="n"/>
       <c r="N16" s="29">
-        <f>IF(OR(A16="",H16=""),"",IF(H16=0,"Sem cobrança",IF(H16&lt;F16,"Abaixo do mínimo",IF(H16&lt;G16,"Entre mínimo e alvo","No alvo ou acima"))))</f>
+        <f>IF(OR(A16="",H16=""),"",IF(NOT(ISNUMBER(E16)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(F16)),NOT(ISNUMBER(G16))),"Margens inválidas",IF(H16=0,"Sem cobrança",IF(H16&lt;F16,"Abaixo do mínimo",IF(H16&lt;G16,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
         <v/>
       </c>
       <c r="O16" s="30">
-        <f>IF(A16="","",SUMPRODUCT((I16:M16&lt;&gt;"")*(I16:M16&gt;0)*(I16:M16*(1-Config!$B$8)&lt;E16)))</f>
+        <f>IF(OR(A16="",NOT(ISNUMBER(F16))),"",SUMPRODUCT((I16:M16&lt;&gt;"")*(I16:M16&gt;0)*(I16:M16*(1-Config!$B$8)&lt;E16)))</f>
         <v/>
       </c>
       <c r="P16" s="23" t="n"/>
@@ -1903,7 +1903,7 @@
         <v/>
       </c>
       <c r="S16" s="31">
-        <f>IF(OR(R16="",F16="",H16=0),"",R16/F16-1)</f>
+        <f>IF(OR(R16="",NOT(ISNUMBER(F16)),N(H16)=0),"",R16/F16-1)</f>
         <v/>
       </c>
       <c r="T16" s="22" t="n"/>
@@ -1914,15 +1914,15 @@
       <c r="C17" s="24" t="n"/>
       <c r="D17" s="25" t="n"/>
       <c r="E17" s="26">
-        <f>IF(A17="","",(B17+IF(C17="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D17)</f>
+        <f>IF(A17="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",(B17+IF(C17="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D17))</f>
         <v/>
       </c>
       <c r="F17" s="27">
-        <f>IF(A17="","",IFERROR(E17/(1-Config!$B$8-Config!$B$9),""))</f>
+        <f>IF(A17="","",IF(NOT(ISNUMBER(E17)),E17,IF((Config!$B$15&lt;&gt;"Sim"),"margens inválidas (Config)",E17/(1-Config!$B$8-Config!$B$9))))</f>
         <v/>
       </c>
       <c r="G17" s="26">
-        <f>IF(A17="","",IFERROR(E17/(1-Config!$B$8-Config!$B$10),""))</f>
+        <f>IF(A17="","",IF(NOT(ISNUMBER(E17)),E17,IF((Config!$B$15&lt;&gt;"Sim"),"margens inválidas (Config)",E17/(1-Config!$B$8-Config!$B$10))))</f>
         <v/>
       </c>
       <c r="H17" s="28" t="n"/>
@@ -1932,11 +1932,11 @@
       <c r="L17" s="28" t="n"/>
       <c r="M17" s="28" t="n"/>
       <c r="N17" s="29">
-        <f>IF(OR(A17="",H17=""),"",IF(H17=0,"Sem cobrança",IF(H17&lt;F17,"Abaixo do mínimo",IF(H17&lt;G17,"Entre mínimo e alvo","No alvo ou acima"))))</f>
+        <f>IF(OR(A17="",H17=""),"",IF(NOT(ISNUMBER(E17)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(F17)),NOT(ISNUMBER(G17))),"Margens inválidas",IF(H17=0,"Sem cobrança",IF(H17&lt;F17,"Abaixo do mínimo",IF(H17&lt;G17,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
         <v/>
       </c>
       <c r="O17" s="30">
-        <f>IF(A17="","",SUMPRODUCT((I17:M17&lt;&gt;"")*(I17:M17&gt;0)*(I17:M17*(1-Config!$B$8)&lt;E17)))</f>
+        <f>IF(OR(A17="",NOT(ISNUMBER(F17))),"",SUMPRODUCT((I17:M17&lt;&gt;"")*(I17:M17&gt;0)*(I17:M17*(1-Config!$B$8)&lt;E17)))</f>
         <v/>
       </c>
       <c r="P17" s="23" t="n"/>
@@ -1946,7 +1946,7 @@
         <v/>
       </c>
       <c r="S17" s="31">
-        <f>IF(OR(R17="",F17="",H17=0),"",R17/F17-1)</f>
+        <f>IF(OR(R17="",NOT(ISNUMBER(F17)),N(H17)=0),"",R17/F17-1)</f>
         <v/>
       </c>
       <c r="T17" s="22" t="n"/>
@@ -1957,15 +1957,15 @@
       <c r="C18" s="24" t="n"/>
       <c r="D18" s="25" t="n"/>
       <c r="E18" s="26">
-        <f>IF(A18="","",(B18+IF(C18="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D18)</f>
+        <f>IF(A18="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",(B18+IF(C18="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D18))</f>
         <v/>
       </c>
       <c r="F18" s="27">
-        <f>IF(A18="","",IFERROR(E18/(1-Config!$B$8-Config!$B$9),""))</f>
+        <f>IF(A18="","",IF(NOT(ISNUMBER(E18)),E18,IF((Config!$B$15&lt;&gt;"Sim"),"margens inválidas (Config)",E18/(1-Config!$B$8-Config!$B$9))))</f>
         <v/>
       </c>
       <c r="G18" s="26">
-        <f>IF(A18="","",IFERROR(E18/(1-Config!$B$8-Config!$B$10),""))</f>
+        <f>IF(A18="","",IF(NOT(ISNUMBER(E18)),E18,IF((Config!$B$15&lt;&gt;"Sim"),"margens inválidas (Config)",E18/(1-Config!$B$8-Config!$B$10))))</f>
         <v/>
       </c>
       <c r="H18" s="28" t="n"/>
@@ -1975,11 +1975,11 @@
       <c r="L18" s="28" t="n"/>
       <c r="M18" s="28" t="n"/>
       <c r="N18" s="29">
-        <f>IF(OR(A18="",H18=""),"",IF(H18=0,"Sem cobrança",IF(H18&lt;F18,"Abaixo do mínimo",IF(H18&lt;G18,"Entre mínimo e alvo","No alvo ou acima"))))</f>
+        <f>IF(OR(A18="",H18=""),"",IF(NOT(ISNUMBER(E18)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(F18)),NOT(ISNUMBER(G18))),"Margens inválidas",IF(H18=0,"Sem cobrança",IF(H18&lt;F18,"Abaixo do mínimo",IF(H18&lt;G18,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
         <v/>
       </c>
       <c r="O18" s="30">
-        <f>IF(A18="","",SUMPRODUCT((I18:M18&lt;&gt;"")*(I18:M18&gt;0)*(I18:M18*(1-Config!$B$8)&lt;E18)))</f>
+        <f>IF(OR(A18="",NOT(ISNUMBER(F18))),"",SUMPRODUCT((I18:M18&lt;&gt;"")*(I18:M18&gt;0)*(I18:M18*(1-Config!$B$8)&lt;E18)))</f>
         <v/>
       </c>
       <c r="P18" s="23" t="n"/>
@@ -1989,7 +1989,7 @@
         <v/>
       </c>
       <c r="S18" s="31">
-        <f>IF(OR(R18="",F18="",H18=0),"",R18/F18-1)</f>
+        <f>IF(OR(R18="",NOT(ISNUMBER(F18)),N(H18)=0),"",R18/F18-1)</f>
         <v/>
       </c>
       <c r="T18" s="22" t="n"/>
@@ -2000,15 +2000,15 @@
       <c r="C19" s="24" t="n"/>
       <c r="D19" s="25" t="n"/>
       <c r="E19" s="26">
-        <f>IF(A19="","",(B19+IF(C19="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D19)</f>
+        <f>IF(A19="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",(B19+IF(C19="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D19))</f>
         <v/>
       </c>
       <c r="F19" s="27">
-        <f>IF(A19="","",IFERROR(E19/(1-Config!$B$8-Config!$B$9),""))</f>
+        <f>IF(A19="","",IF(NOT(ISNUMBER(E19)),E19,IF((Config!$B$15&lt;&gt;"Sim"),"margens inválidas (Config)",E19/(1-Config!$B$8-Config!$B$9))))</f>
         <v/>
       </c>
       <c r="G19" s="26">
-        <f>IF(A19="","",IFERROR(E19/(1-Config!$B$8-Config!$B$10),""))</f>
+        <f>IF(A19="","",IF(NOT(ISNUMBER(E19)),E19,IF((Config!$B$15&lt;&gt;"Sim"),"margens inválidas (Config)",E19/(1-Config!$B$8-Config!$B$10))))</f>
         <v/>
       </c>
       <c r="H19" s="28" t="n"/>
@@ -2018,11 +2018,11 @@
       <c r="L19" s="28" t="n"/>
       <c r="M19" s="28" t="n"/>
       <c r="N19" s="29">
-        <f>IF(OR(A19="",H19=""),"",IF(H19=0,"Sem cobrança",IF(H19&lt;F19,"Abaixo do mínimo",IF(H19&lt;G19,"Entre mínimo e alvo","No alvo ou acima"))))</f>
+        <f>IF(OR(A19="",H19=""),"",IF(NOT(ISNUMBER(E19)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(F19)),NOT(ISNUMBER(G19))),"Margens inválidas",IF(H19=0,"Sem cobrança",IF(H19&lt;F19,"Abaixo do mínimo",IF(H19&lt;G19,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
         <v/>
       </c>
       <c r="O19" s="30">
-        <f>IF(A19="","",SUMPRODUCT((I19:M19&lt;&gt;"")*(I19:M19&gt;0)*(I19:M19*(1-Config!$B$8)&lt;E19)))</f>
+        <f>IF(OR(A19="",NOT(ISNUMBER(F19))),"",SUMPRODUCT((I19:M19&lt;&gt;"")*(I19:M19&gt;0)*(I19:M19*(1-Config!$B$8)&lt;E19)))</f>
         <v/>
       </c>
       <c r="P19" s="23" t="n"/>
@@ -2032,7 +2032,7 @@
         <v/>
       </c>
       <c r="S19" s="31">
-        <f>IF(OR(R19="",F19="",H19=0),"",R19/F19-1)</f>
+        <f>IF(OR(R19="",NOT(ISNUMBER(F19)),N(H19)=0),"",R19/F19-1)</f>
         <v/>
       </c>
       <c r="T19" s="22" t="n"/>
@@ -2649,7 +2649,7 @@
   </mergeCells>
   <conditionalFormatting sqref="N8:N19">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>N8="Abaixo do mínimo"</formula>
+      <formula>OR(N8="Abaixo do mínimo",N8="Falta o custo-hora",N8="Margens inválidas")</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1">
       <formula>N8="Entre mínimo e alvo"</formula>
@@ -2663,10 +2663,10 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="I8:M19">
     <cfRule type="expression" priority="4" dxfId="4">
-      <formula>AND(ISNUMBER(I8),I8&gt;0,I8*(1-INDIRECT("Config!$B$8"))&lt;$E8)</formula>
+      <formula>AND(ISNUMBER(I8),I8&gt;0,ISNUMBER($F8),I8*(1-INDIRECT("Config!$B$8"))&lt;$E8)</formula>
     </cfRule>
     <cfRule type="expression" priority="5" dxfId="1">
-      <formula>AND(ISNUMBER(I8),I8*(1-INDIRECT("Config!$B$8"))&gt;=$E8,I8&lt;$F8)</formula>
+      <formula>AND(ISNUMBER(I8),ISNUMBER($F8),I8*(1-INDIRECT("Config!$B$8"))&gt;=$E8,I8&lt;$F8)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O8:O19">
@@ -2681,10 +2681,10 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="C27:H38">
     <cfRule type="expression" priority="9" dxfId="4">
-      <formula>AND(ISNUMBER(C27),C27&gt;0,C27&lt;INDIRECT("Config!$B$13"))</formula>
+      <formula>AND(ISNUMBER(C27),C27&gt;0,ISNUMBER(INDIRECT("Config!$B$13")),C27&lt;INDIRECT("Config!$B$13"))</formula>
     </cfRule>
     <cfRule type="expression" priority="10" dxfId="2">
-      <formula>AND(ISNUMBER(C27),C27&gt;=INDIRECT("Config!$B$14"))</formula>
+      <formula>AND(ISNUMBER(C27),ISNUMBER(INDIRECT("Config!$B$14")),C27&gt;=INDIRECT("Config!$B$14"))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="B13" s="27">
-        <f>IFERROR(B7/(1-B8-B9),"")</f>
+        <f>IF(NOT(ISNUMBER(B7)),"falta o custo-hora",IF(B15&lt;&gt;"Sim","margens inválidas (Config)",B7/(1-B8-B9)))</f>
         <v>338.983050847458</v>
       </c>
       <c r="C13" s="37" t="inlineStr">
@@ -2867,12 +2867,28 @@
         </is>
       </c>
       <c r="B14" s="27">
-        <f>IFERROR(B7/(1-B8-B10),"")</f>
+        <f>IF(NOT(ISNUMBER(B7)),"falta o custo-hora",IF(B15&lt;&gt;"Sim","margens inválidas (Config)",B7/(1-B8-B10)))</f>
         <v>454.545454545455</v>
       </c>
       <c r="C14" s="37" t="inlineStr">
         <is>
           <t>Custo-hora ÷ (1 − impostos − margem alvo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="38" t="inlineStr">
+        <is>
+          <t>Impostos e margens conferem? (calculado)</t>
+        </is>
+      </c>
+      <c r="B15" s="29" t="str">
+        <f>IF(AND(ISNUMBER(B8),ISNUMBER(B9),ISNUMBER(B10)),IF(AND(B8&gt;=0,B8&lt;1,B9&gt;=0,B9&lt;=B10,B10&lt;1,B8+B10&lt;1),"Sim","Não"),"Não")</f>
+        <v>Sim</v>
+      </c>
+      <c r="C15" s="37" t="inlineStr">
+        <is>
+          <t>"Não" suspende preços, situação e contagens: impostos e margens de 0 % a 99 %, mínima ≤ alvo e impostos + margem alvo abaixo de 100 %.</t>
         </is>
       </c>
     </row>
@@ -2947,6 +2963,17 @@
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
+  <dataValidations count="3">
+    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentual" error="Impostos entre 0 % e 99 %, e impostos + margem alvo abaixo de 100 %." type="custom">
+      <formula1>=AND(ISNUMBER(B8),B8&gt;=0,B8&lt;1,B8+N(B10)&lt;1)</formula1>
+    </dataValidation>
+    <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentual" error="Margem mínima entre 0 % e a margem alvo, e impostos + margem abaixo de 100 %." type="custom">
+      <formula1>=AND(ISNUMBER(B9),B9&gt;=0,B9&lt;=N(B10),N(B8)+B9&lt;1)</formula1>
+    </dataValidation>
+    <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentual" error="Margem alvo entre a margem mínima e 99 %, e impostos + margem alvo abaixo de 100 %." type="custom">
+      <formula1>=AND(ISNUMBER(B10),B10&gt;=N(B9),B10&lt;1,N(B8)+B10&lt;1)</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/08-tabela-de-precos.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/08-tabela-de-precos.xlsx
@@ -1255,7 +1255,7 @@
       </c>
       <c r="J5" s="14" t="n"/>
       <c r="K5" s="20">
-        <f>IF(NOT(ISNUMBER(Config!$B$13)),"",IFERROR(I5/Config!$B$13-1,0))</f>
+        <f>IF(NOT(ISNUMBER(Config!$B$13)),"",IF(Config!$B$13=0,"sem base (mínimo zero)",IFERROR(I5/Config!$B$13-1,"")))</f>
         <v>0.212350281690141</v>
       </c>
       <c r="L5" s="8" t="n"/>
@@ -1419,7 +1419,7 @@
         <v>236.384615384615</v>
       </c>
       <c r="S8" s="31">
-        <f>IF(OR(R8="",NOT(ISNUMBER(F8)),N(H8)=0),"",R8/F8-1)</f>
+        <f>IF(OR(R8="",NOT(ISNUMBER(F8)),N(H8)=0),"",IF(F8=0,"sem base (mínimo zero)",R8/F8-1))</f>
         <v>0.0673489010989012</v>
       </c>
       <c r="T8" s="22" t="n"/>
@@ -1486,7 +1486,7 @@
         <v>0</v>
       </c>
       <c r="S9" s="31">
-        <f>IF(OR(R9="",NOT(ISNUMBER(F9)),N(H9)=0),"",R9/F9-1)</f>
+        <f>IF(OR(R9="",NOT(ISNUMBER(F9)),N(H9)=0),"",IF(F9=0,"sem base (mínimo zero)",R9/F9-1))</f>
         <v/>
       </c>
       <c r="T9" s="22" t="n"/>
@@ -1553,7 +1553,7 @@
         <v>78.6666666666667</v>
       </c>
       <c r="S10" s="31">
-        <f>IF(OR(R10="",NOT(ISNUMBER(F10)),N(H10)=0),"",R10/F10-1)</f>
+        <f>IF(OR(R10="",NOT(ISNUMBER(F10)),N(H10)=0),"",IF(F10=0,"sem base (mínimo zero)",R10/F10-1))</f>
         <v>-0.378392857142857</v>
       </c>
       <c r="T10" s="22" t="n"/>
@@ -1620,7 +1620,7 @@
         <v>168.125</v>
       </c>
       <c r="S11" s="31">
-        <f>IF(OR(R11="",NOT(ISNUMBER(F11)),N(H11)=0),"",R11/F11-1)</f>
+        <f>IF(OR(R11="",NOT(ISNUMBER(F11)),N(H11)=0),"",IF(F11=0,"sem base (mínimo zero)",R11/F11-1))</f>
         <v>0.214617346938776</v>
       </c>
       <c r="T11" s="22" t="n"/>
@@ -1687,7 +1687,7 @@
         <v>249</v>
       </c>
       <c r="S12" s="31">
-        <f>IF(OR(R12="",NOT(ISNUMBER(F12)),N(H12)=0),"",R12/F12-1)</f>
+        <f>IF(OR(R12="",NOT(ISNUMBER(F12)),N(H12)=0),"",IF(F12=0,"sem base (mínimo zero)",R12/F12-1))</f>
         <v>0.735157480314961</v>
       </c>
       <c r="T12" s="22" t="n"/>
@@ -1754,7 +1754,7 @@
         <v>283.75</v>
       </c>
       <c r="S13" s="31">
-        <f>IF(OR(R13="",NOT(ISNUMBER(F13)),N(H13)=0),"",R13/F13-1)</f>
+        <f>IF(OR(R13="",NOT(ISNUMBER(F13)),N(H13)=0),"",IF(F13=0,"sem base (mínimo zero)",R13/F13-1))</f>
         <v>0.0573421052631582</v>
       </c>
       <c r="T13" s="22" t="n"/>
@@ -1817,7 +1817,7 @@
         <v>346</v>
       </c>
       <c r="S14" s="31">
-        <f>IF(OR(R14="",NOT(ISNUMBER(F14)),N(H14)=0),"",R14/F14-1)</f>
+        <f>IF(OR(R14="",NOT(ISNUMBER(F14)),N(H14)=0),"",IF(F14=0,"sem base (mínimo zero)",R14/F14-1))</f>
         <v>0.244756097560976</v>
       </c>
       <c r="T14" s="22" t="n"/>
@@ -1860,7 +1860,7 @@
         <v/>
       </c>
       <c r="S15" s="31">
-        <f>IF(OR(R15="",NOT(ISNUMBER(F15)),N(H15)=0),"",R15/F15-1)</f>
+        <f>IF(OR(R15="",NOT(ISNUMBER(F15)),N(H15)=0),"",IF(F15=0,"sem base (mínimo zero)",R15/F15-1))</f>
         <v/>
       </c>
       <c r="T15" s="22" t="n"/>
@@ -1903,7 +1903,7 @@
         <v/>
       </c>
       <c r="S16" s="31">
-        <f>IF(OR(R16="",NOT(ISNUMBER(F16)),N(H16)=0),"",R16/F16-1)</f>
+        <f>IF(OR(R16="",NOT(ISNUMBER(F16)),N(H16)=0),"",IF(F16=0,"sem base (mínimo zero)",R16/F16-1))</f>
         <v/>
       </c>
       <c r="T16" s="22" t="n"/>
@@ -1946,7 +1946,7 @@
         <v/>
       </c>
       <c r="S17" s="31">
-        <f>IF(OR(R17="",NOT(ISNUMBER(F17)),N(H17)=0),"",R17/F17-1)</f>
+        <f>IF(OR(R17="",NOT(ISNUMBER(F17)),N(H17)=0),"",IF(F17=0,"sem base (mínimo zero)",R17/F17-1))</f>
         <v/>
       </c>
       <c r="T17" s="22" t="n"/>
@@ -1989,7 +1989,7 @@
         <v/>
       </c>
       <c r="S18" s="31">
-        <f>IF(OR(R18="",NOT(ISNUMBER(F18)),N(H18)=0),"",R18/F18-1)</f>
+        <f>IF(OR(R18="",NOT(ISNUMBER(F18)),N(H18)=0),"",IF(F18=0,"sem base (mínimo zero)",R18/F18-1))</f>
         <v/>
       </c>
       <c r="T18" s="22" t="n"/>
@@ -2032,7 +2032,7 @@
         <v/>
       </c>
       <c r="S19" s="31">
-        <f>IF(OR(R19="",NOT(ISNUMBER(F19)),N(H19)=0),"",R19/F19-1)</f>
+        <f>IF(OR(R19="",NOT(ISNUMBER(F19)),N(H19)=0),"",IF(F19=0,"sem base (mínimo zero)",R19/F19-1))</f>
         <v/>
       </c>
       <c r="T19" s="22" t="n"/>
@@ -2965,13 +2965,13 @@
   </mergeCells>
   <dataValidations count="3">
     <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentual" error="Impostos entre 0 % e 99 %, e impostos + margem alvo abaixo de 100 %." type="custom">
-      <formula1>=AND(ISNUMBER(B8),B8&gt;=0,B8&lt;1,B8+N(B10)&lt;1)</formula1>
+      <formula1>=IF(ISNUMBER(B8),AND(B8&gt;=0,B8&lt;1,B8+N(B10)&lt;1),FALSE)</formula1>
     </dataValidation>
     <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentual" error="Margem mínima entre 0 % e a margem alvo, e impostos + margem abaixo de 100 %." type="custom">
-      <formula1>=AND(ISNUMBER(B9),B9&gt;=0,B9&lt;=N(B10),N(B8)+B9&lt;1)</formula1>
+      <formula1>=IF(ISNUMBER(B9),AND(B9&gt;=0,B9&lt;=N(B10),N(B8)+B9&lt;1),FALSE)</formula1>
     </dataValidation>
     <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentual" error="Margem alvo entre a margem mínima e 99 %, e impostos + margem alvo abaixo de 100 %." type="custom">
-      <formula1>=AND(ISNUMBER(B10),B10&gt;=N(B9),B10&lt;1,N(B8)+B10&lt;1)</formula1>
+      <formula1>=IF(ISNUMBER(B10),AND(B10&gt;=N(B9),B10&lt;1,N(B8)+B10&lt;1),FALSE)</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/08-tabela-de-precos.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/08-tabela-de-precos.xlsx
@@ -1235,22 +1235,22 @@
       </c>
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="16" t="str">
-        <f>IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,COUNTIF($N$8:$N$19,"Abaixo do mínimo")&amp;" de "&amp;COUNTA($A$8:$A$19))</f>
+        <f>IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF((SUMPRODUCT(($A$8:$A$19&lt;&gt;"")*(ISNUMBER($F$8:$F$19)=FALSE))+SUMPRODUCT(ISTEXT($H$8:$M$19)*1))&gt;0,(SUMPRODUCT(($A$8:$A$19&lt;&gt;"")*(ISNUMBER($F$8:$F$19)=FALSE))+SUMPRODUCT(ISTEXT($H$8:$M$19)*1))&amp;" linha(s) ou preço(s) incompletos",COUNTIF($N$8:$N$19,"Abaixo do mínimo")&amp;" de "&amp;COUNTA($A$8:$A$19)))</f>
         <v>0 de 7</v>
       </c>
       <c r="D5" s="10" t="n"/>
       <c r="E5" s="17">
-        <f>IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,SUM($O$8:$O$19))</f>
+        <f>IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF((SUMPRODUCT(($A$8:$A$19&lt;&gt;"")*(ISNUMBER($F$8:$F$19)=FALSE))+SUMPRODUCT(ISTEXT($H$8:$M$19)*1))&gt;0,(SUMPRODUCT(($A$8:$A$19&lt;&gt;"")*(ISNUMBER($F$8:$F$19)=FALSE))+SUMPRODUCT(ISTEXT($H$8:$M$19)*1))&amp;" linha(s) ou preço(s) incompletos",SUM($O$8:$O$19)))</f>
         <v>14</v>
       </c>
       <c r="F5" s="10" t="n"/>
       <c r="G5" s="18">
-        <f>SUM($Q$8:$Q$19)</f>
+        <f>IF(SUMPRODUCT(ISTEXT($Q$8:$Q$19)*1)&gt;0,"produção com texto",SUM($Q$8:$Q$19))</f>
         <v>48631</v>
       </c>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="19">
-        <f>IFERROR(SUM($Q$8:$Q$19)/(SUMPRODUCT($P$8:$P$19,$B$8:$B$19)/60),0)</f>
+        <f>IF(SUMPRODUCT((($P$8:$P$19&lt;&gt;"")+($Q$8:$Q$19&lt;&gt;"")&gt;0)*((ISNUMBER($P$8:$P$19)=FALSE)+(ISNUMBER($Q$8:$Q$19)=FALSE)+(ISNUMBER($B$8:$B$19)=FALSE)&gt;0))&gt;0,"volume incompleto em "&amp;SUMPRODUCT((($P$8:$P$19&lt;&gt;"")+($Q$8:$Q$19&lt;&gt;"")&gt;0)*((ISNUMBER($P$8:$P$19)=FALSE)+(ISNUMBER($Q$8:$Q$19)=FALSE)+(ISNUMBER($B$8:$B$19)=FALSE)&gt;0))&amp;" linha(s)",IFERROR(SUM($Q$8:$Q$19)/(SUMPRODUCT($P$8:$P$19,$B$8:$B$19)/60),""))</f>
         <v>410.966197183099</v>
       </c>
       <c r="J5" s="14" t="n"/>
@@ -1375,7 +1375,7 @@
         <v>4</v>
       </c>
       <c r="E8" s="26">
-        <f>IF(A8="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",(B8+IF(C8="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D8))</f>
+        <f>IF(A8="","",IF(NOT(ISNUMBER((IF(NOT(IF(ISNUMBER(B8),AND(B8&gt;=0),FALSE)),"faltam os minutos",IF(AND(C8&lt;&gt;"Sim",C8&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C8="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B8+IF(C8="Sim",Config!$B$11*Config!$B$12,0))))))),(IF(NOT(IF(ISNUMBER(B8),AND(B8&gt;=0),FALSE)),"faltam os minutos",IF(AND(C8&lt;&gt;"Sim",C8&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C8="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B8+IF(C8="Sim",Config!$B$11*Config!$B$12,0))))),IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D8),AND(D8&gt;=0),FALSE)),"falta o material",(IF(NOT(IF(ISNUMBER(B8),AND(B8&gt;=0),FALSE)),"faltam os minutos",IF(AND(C8&lt;&gt;"Sim",C8&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C8="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B8+IF(C8="Sim",Config!$B$11*Config!$B$12,0)))))/60*Config!$B$7+D8))))</f>
         <v>130.666666666667</v>
       </c>
       <c r="F8" s="27">
@@ -1401,11 +1401,11 @@
       <c r="L8" s="28" t="n"/>
       <c r="M8" s="28" t="n"/>
       <c r="N8" s="29" t="str">
-        <f>IF(OR(A8="",H8=""),"",IF(NOT(ISNUMBER(E8)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(F8)),NOT(ISNUMBER(G8))),"Margens inválidas",IF(H8=0,"Sem cobrança",IF(H8&lt;F8,"Abaixo do mínimo",IF(H8&lt;G8,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
+        <f>IF(OR(A8="",H8=""),"",IF(NOT(ISNUMBER(H8)),"Preço inválido",IF(NOT(ISNUMBER(E8)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F8)),NOT(ISNUMBER(G8))),"Margens inválidas",IF(H8=0,"Sem cobrança",IF(H8&lt;F8,"Abaixo do mínimo",IF(H8&lt;G8,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="O8" s="30">
-        <f>IF(OR(A8="",NOT(ISNUMBER(F8))),"",SUMPRODUCT((I8:M8&lt;&gt;"")*(I8:M8&gt;0)*(I8:M8*(1-Config!$B$8)&lt;E8)))</f>
+        <f>IF(OR(A8="",NOT(ISNUMBER(F8))),"",IF(SUMPRODUCT(ISTEXT(I8:M8)*1)&gt;0,"tabela com texto",SUMPRODUCT((I8:M8&lt;&gt;"")*(I8:M8&gt;0)*(I8:M8*(1-Config!$B$8)&lt;E8))))</f>
         <v>3</v>
       </c>
       <c r="P8" s="23" t="n">
@@ -1415,11 +1415,11 @@
         <v>30730</v>
       </c>
       <c r="R8" s="26">
-        <f>IF(OR(A8="",P8="",P8=0),"",Q8/P8)</f>
+        <f>IF(OR(A8="",AND(P8="",Q8="")),"",IF(OR(NOT(ISNUMBER(P8)),NOT(ISNUMBER(Q8))),"volume ou produção faltando",IF(P8=0,"",Q8/P8)))</f>
         <v>236.384615384615</v>
       </c>
       <c r="S8" s="31">
-        <f>IF(OR(R8="",NOT(ISNUMBER(F8)),N(H8)=0),"",IF(F8=0,"sem base (mínimo zero)",R8/F8-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(R8)),NOT(ISNUMBER(F8)),N(H8)=0),"",IF(F8=0,"sem base (mínimo zero)",R8/F8-1))</f>
         <v>0.0673489010989012</v>
       </c>
       <c r="T8" s="22" t="n"/>
@@ -1442,7 +1442,7 @@
         <v>2</v>
       </c>
       <c r="E9" s="26">
-        <f>IF(A9="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",(B9+IF(C9="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D9))</f>
+        <f>IF(A9="","",IF(NOT(ISNUMBER((IF(NOT(IF(ISNUMBER(B9),AND(B9&gt;=0),FALSE)),"faltam os minutos",IF(AND(C9&lt;&gt;"Sim",C9&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C9="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B9+IF(C9="Sim",Config!$B$11*Config!$B$12,0))))))),(IF(NOT(IF(ISNUMBER(B9),AND(B9&gt;=0),FALSE)),"faltam os minutos",IF(AND(C9&lt;&gt;"Sim",C9&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C9="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B9+IF(C9="Sim",Config!$B$11*Config!$B$12,0))))),IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D9),AND(D9&gt;=0),FALSE)),"falta o material",(IF(NOT(IF(ISNUMBER(B9),AND(B9&gt;=0),FALSE)),"faltam os minutos",IF(AND(C9&lt;&gt;"Sim",C9&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C9="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B9+IF(C9="Sim",Config!$B$11*Config!$B$12,0)))))/60*Config!$B$7+D9))))</f>
         <v>68.6666666666667</v>
       </c>
       <c r="F9" s="27">
@@ -1468,11 +1468,11 @@
       <c r="L9" s="28" t="n"/>
       <c r="M9" s="28" t="n"/>
       <c r="N9" s="29" t="str">
-        <f>IF(OR(A9="",H9=""),"",IF(NOT(ISNUMBER(E9)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(F9)),NOT(ISNUMBER(G9))),"Margens inválidas",IF(H9=0,"Sem cobrança",IF(H9&lt;F9,"Abaixo do mínimo",IF(H9&lt;G9,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
+        <f>IF(OR(A9="",H9=""),"",IF(NOT(ISNUMBER(H9)),"Preço inválido",IF(NOT(ISNUMBER(E9)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F9)),NOT(ISNUMBER(G9))),"Margens inválidas",IF(H9=0,"Sem cobrança",IF(H9&lt;F9,"Abaixo do mínimo",IF(H9&lt;G9,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v>Sem cobrança</v>
       </c>
       <c r="O9" s="30">
-        <f>IF(OR(A9="",NOT(ISNUMBER(F9))),"",SUMPRODUCT((I9:M9&lt;&gt;"")*(I9:M9&gt;0)*(I9:M9*(1-Config!$B$8)&lt;E9)))</f>
+        <f>IF(OR(A9="",NOT(ISNUMBER(F9))),"",IF(SUMPRODUCT(ISTEXT(I9:M9)*1)&gt;0,"tabela com texto",SUMPRODUCT((I9:M9&lt;&gt;"")*(I9:M9&gt;0)*(I9:M9*(1-Config!$B$8)&lt;E9))))</f>
         <v>0</v>
       </c>
       <c r="P9" s="23" t="n">
@@ -1482,11 +1482,11 @@
         <v>0</v>
       </c>
       <c r="R9" s="26">
-        <f>IF(OR(A9="",P9="",P9=0),"",Q9/P9)</f>
+        <f>IF(OR(A9="",AND(P9="",Q9="")),"",IF(OR(NOT(ISNUMBER(P9)),NOT(ISNUMBER(Q9))),"volume ou produção faltando",IF(P9=0,"",Q9/P9)))</f>
         <v>0</v>
       </c>
       <c r="S9" s="31">
-        <f>IF(OR(R9="",NOT(ISNUMBER(F9)),N(H9)=0),"",IF(F9=0,"sem base (mínimo zero)",R9/F9-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(R9)),NOT(ISNUMBER(F9)),N(H9)=0),"",IF(F9=0,"sem base (mínimo zero)",R9/F9-1))</f>
         <v/>
       </c>
       <c r="T9" s="22" t="n"/>
@@ -1509,7 +1509,7 @@
         <v>8</v>
       </c>
       <c r="E10" s="26">
-        <f>IF(A10="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",(B10+IF(C10="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D10))</f>
+        <f>IF(A10="","",IF(NOT(ISNUMBER((IF(NOT(IF(ISNUMBER(B10),AND(B10&gt;=0),FALSE)),"faltam os minutos",IF(AND(C10&lt;&gt;"Sim",C10&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C10="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B10+IF(C10="Sim",Config!$B$11*Config!$B$12,0))))))),(IF(NOT(IF(ISNUMBER(B10),AND(B10&gt;=0),FALSE)),"faltam os minutos",IF(AND(C10&lt;&gt;"Sim",C10&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C10="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B10+IF(C10="Sim",Config!$B$11*Config!$B$12,0))))),IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D10),AND(D10&gt;=0),FALSE)),"falta o material",(IF(NOT(IF(ISNUMBER(B10),AND(B10&gt;=0),FALSE)),"faltam os minutos",IF(AND(C10&lt;&gt;"Sim",C10&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C10="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B10+IF(C10="Sim",Config!$B$11*Config!$B$12,0)))))/60*Config!$B$7+D10))))</f>
         <v>74.6666666666667</v>
       </c>
       <c r="F10" s="27">
@@ -1535,11 +1535,11 @@
       <c r="L10" s="28" t="n"/>
       <c r="M10" s="28" t="n"/>
       <c r="N10" s="29" t="str">
-        <f>IF(OR(A10="",H10=""),"",IF(NOT(ISNUMBER(E10)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(F10)),NOT(ISNUMBER(G10))),"Margens inválidas",IF(H10=0,"Sem cobrança",IF(H10&lt;F10,"Abaixo do mínimo",IF(H10&lt;G10,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
+        <f>IF(OR(A10="",H10=""),"",IF(NOT(ISNUMBER(H10)),"Preço inválido",IF(NOT(ISNUMBER(E10)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F10)),NOT(ISNUMBER(G10))),"Margens inválidas",IF(H10=0,"Sem cobrança",IF(H10&lt;F10,"Abaixo do mínimo",IF(H10&lt;G10,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v>Entre mínimo e alvo</v>
       </c>
       <c r="O10" s="30">
-        <f>IF(OR(A10="",NOT(ISNUMBER(F10))),"",SUMPRODUCT((I10:M10&lt;&gt;"")*(I10:M10&gt;0)*(I10:M10*(1-Config!$B$8)&lt;E10)))</f>
+        <f>IF(OR(A10="",NOT(ISNUMBER(F10))),"",IF(SUMPRODUCT(ISTEXT(I10:M10)*1)&gt;0,"tabela com texto",SUMPRODUCT((I10:M10&lt;&gt;"")*(I10:M10&gt;0)*(I10:M10*(1-Config!$B$8)&lt;E10))))</f>
         <v>3</v>
       </c>
       <c r="P10" s="23" t="n">
@@ -1549,11 +1549,11 @@
         <v>1416</v>
       </c>
       <c r="R10" s="26">
-        <f>IF(OR(A10="",P10="",P10=0),"",Q10/P10)</f>
+        <f>IF(OR(A10="",AND(P10="",Q10="")),"",IF(OR(NOT(ISNUMBER(P10)),NOT(ISNUMBER(Q10))),"volume ou produção faltando",IF(P10=0,"",Q10/P10)))</f>
         <v>78.6666666666667</v>
       </c>
       <c r="S10" s="31">
-        <f>IF(OR(R10="",NOT(ISNUMBER(F10)),N(H10)=0),"",IF(F10=0,"sem base (mínimo zero)",R10/F10-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(R10)),NOT(ISNUMBER(F10)),N(H10)=0),"",IF(F10=0,"sem base (mínimo zero)",R10/F10-1))</f>
         <v>-0.378392857142857</v>
       </c>
       <c r="T10" s="22" t="n"/>
@@ -1576,7 +1576,7 @@
         <v>15</v>
       </c>
       <c r="E11" s="26">
-        <f>IF(A11="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",(B11+IF(C11="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D11))</f>
+        <f>IF(A11="","",IF(NOT(ISNUMBER((IF(NOT(IF(ISNUMBER(B11),AND(B11&gt;=0),FALSE)),"faltam os minutos",IF(AND(C11&lt;&gt;"Sim",C11&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C11="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B11+IF(C11="Sim",Config!$B$11*Config!$B$12,0))))))),(IF(NOT(IF(ISNUMBER(B11),AND(B11&gt;=0),FALSE)),"faltam os minutos",IF(AND(C11&lt;&gt;"Sim",C11&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C11="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B11+IF(C11="Sim",Config!$B$11*Config!$B$12,0))))),IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D11),AND(D11&gt;=0),FALSE)),"falta o material",(IF(NOT(IF(ISNUMBER(B11),AND(B11&gt;=0),FALSE)),"faltam os minutos",IF(AND(C11&lt;&gt;"Sim",C11&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C11="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B11+IF(C11="Sim",Config!$B$11*Config!$B$12,0)))))/60*Config!$B$7+D11))))</f>
         <v>81.6666666666667</v>
       </c>
       <c r="F11" s="27">
@@ -1602,11 +1602,11 @@
       <c r="L11" s="28" t="n"/>
       <c r="M11" s="28" t="n"/>
       <c r="N11" s="29" t="str">
-        <f>IF(OR(A11="",H11=""),"",IF(NOT(ISNUMBER(E11)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(F11)),NOT(ISNUMBER(G11))),"Margens inválidas",IF(H11=0,"Sem cobrança",IF(H11&lt;F11,"Abaixo do mínimo",IF(H11&lt;G11,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
+        <f>IF(OR(A11="",H11=""),"",IF(NOT(ISNUMBER(H11)),"Preço inválido",IF(NOT(ISNUMBER(E11)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F11)),NOT(ISNUMBER(G11))),"Margens inválidas",IF(H11=0,"Sem cobrança",IF(H11&lt;F11,"Abaixo do mínimo",IF(H11&lt;G11,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="O11" s="30">
-        <f>IF(OR(A11="",NOT(ISNUMBER(F11))),"",SUMPRODUCT((I11:M11&lt;&gt;"")*(I11:M11&gt;0)*(I11:M11*(1-Config!$B$8)&lt;E11)))</f>
+        <f>IF(OR(A11="",NOT(ISNUMBER(F11))),"",IF(SUMPRODUCT(ISTEXT(I11:M11)*1)&gt;0,"tabela com texto",SUMPRODUCT((I11:M11&lt;&gt;"")*(I11:M11&gt;0)*(I11:M11*(1-Config!$B$8)&lt;E11))))</f>
         <v>2</v>
       </c>
       <c r="P11" s="23" t="n">
@@ -1616,11 +1616,11 @@
         <v>1345</v>
       </c>
       <c r="R11" s="26">
-        <f>IF(OR(A11="",P11="",P11=0),"",Q11/P11)</f>
+        <f>IF(OR(A11="",AND(P11="",Q11="")),"",IF(OR(NOT(ISNUMBER(P11)),NOT(ISNUMBER(Q11))),"volume ou produção faltando",IF(P11=0,"",Q11/P11)))</f>
         <v>168.125</v>
       </c>
       <c r="S11" s="31">
-        <f>IF(OR(R11="",NOT(ISNUMBER(F11)),N(H11)=0),"",IF(F11=0,"sem base (mínimo zero)",R11/F11-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(R11)),NOT(ISNUMBER(F11)),N(H11)=0),"",IF(F11=0,"sem base (mínimo zero)",R11/F11-1))</f>
         <v>0.214617346938776</v>
       </c>
       <c r="T11" s="22" t="n"/>
@@ -1643,7 +1643,7 @@
         <v>18</v>
       </c>
       <c r="E12" s="26">
-        <f>IF(A12="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",(B12+IF(C12="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D12))</f>
+        <f>IF(A12="","",IF(NOT(ISNUMBER((IF(NOT(IF(ISNUMBER(B12),AND(B12&gt;=0),FALSE)),"faltam os minutos",IF(AND(C12&lt;&gt;"Sim",C12&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C12="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B12+IF(C12="Sim",Config!$B$11*Config!$B$12,0))))))),(IF(NOT(IF(ISNUMBER(B12),AND(B12&gt;=0),FALSE)),"faltam os minutos",IF(AND(C12&lt;&gt;"Sim",C12&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C12="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B12+IF(C12="Sim",Config!$B$11*Config!$B$12,0))))),IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D12),AND(D12&gt;=0),FALSE)),"falta o material",(IF(NOT(IF(ISNUMBER(B12),AND(B12&gt;=0),FALSE)),"faltam os minutos",IF(AND(C12&lt;&gt;"Sim",C12&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C12="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B12+IF(C12="Sim",Config!$B$11*Config!$B$12,0)))))/60*Config!$B$7+D12))))</f>
         <v>84.6666666666667</v>
       </c>
       <c r="F12" s="27">
@@ -1669,11 +1669,11 @@
       <c r="L12" s="28" t="n"/>
       <c r="M12" s="28" t="n"/>
       <c r="N12" s="29" t="str">
-        <f>IF(OR(A12="",H12=""),"",IF(NOT(ISNUMBER(E12)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(F12)),NOT(ISNUMBER(G12))),"Margens inválidas",IF(H12=0,"Sem cobrança",IF(H12&lt;F12,"Abaixo do mínimo",IF(H12&lt;G12,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
+        <f>IF(OR(A12="",H12=""),"",IF(NOT(ISNUMBER(H12)),"Preço inválido",IF(NOT(ISNUMBER(E12)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F12)),NOT(ISNUMBER(G12))),"Margens inválidas",IF(H12=0,"Sem cobrança",IF(H12&lt;F12,"Abaixo do mínimo",IF(H12&lt;G12,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="O12" s="30">
-        <f>IF(OR(A12="",NOT(ISNUMBER(F12))),"",SUMPRODUCT((I12:M12&lt;&gt;"")*(I12:M12&gt;0)*(I12:M12*(1-Config!$B$8)&lt;E12)))</f>
+        <f>IF(OR(A12="",NOT(ISNUMBER(F12))),"",IF(SUMPRODUCT(ISTEXT(I12:M12)*1)&gt;0,"tabela com texto",SUMPRODUCT((I12:M12&lt;&gt;"")*(I12:M12&gt;0)*(I12:M12*(1-Config!$B$8)&lt;E12))))</f>
         <v>2</v>
       </c>
       <c r="P12" s="23" t="n">
@@ -1683,11 +1683,11 @@
         <v>2490</v>
       </c>
       <c r="R12" s="26">
-        <f>IF(OR(A12="",P12="",P12=0),"",Q12/P12)</f>
+        <f>IF(OR(A12="",AND(P12="",Q12="")),"",IF(OR(NOT(ISNUMBER(P12)),NOT(ISNUMBER(Q12))),"volume ou produção faltando",IF(P12=0,"",Q12/P12)))</f>
         <v>249</v>
       </c>
       <c r="S12" s="31">
-        <f>IF(OR(R12="",NOT(ISNUMBER(F12)),N(H12)=0),"",IF(F12=0,"sem base (mínimo zero)",R12/F12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(R12)),NOT(ISNUMBER(F12)),N(H12)=0),"",IF(F12=0,"sem base (mínimo zero)",R12/F12-1))</f>
         <v>0.735157480314961</v>
       </c>
       <c r="T12" s="22" t="n"/>
@@ -1710,7 +1710,7 @@
         <v>25</v>
       </c>
       <c r="E13" s="26">
-        <f>IF(A13="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",(B13+IF(C13="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D13))</f>
+        <f>IF(A13="","",IF(NOT(ISNUMBER((IF(NOT(IF(ISNUMBER(B13),AND(B13&gt;=0),FALSE)),"faltam os minutos",IF(AND(C13&lt;&gt;"Sim",C13&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C13="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B13+IF(C13="Sim",Config!$B$11*Config!$B$12,0))))))),(IF(NOT(IF(ISNUMBER(B13),AND(B13&gt;=0),FALSE)),"faltam os minutos",IF(AND(C13&lt;&gt;"Sim",C13&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C13="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B13+IF(C13="Sim",Config!$B$11*Config!$B$12,0))))),IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D13),AND(D13&gt;=0),FALSE)),"falta o material",(IF(NOT(IF(ISNUMBER(B13),AND(B13&gt;=0),FALSE)),"faltam os minutos",IF(AND(C13&lt;&gt;"Sim",C13&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C13="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B13+IF(C13="Sim",Config!$B$11*Config!$B$12,0)))))/60*Config!$B$7+D13))))</f>
         <v>158.333333333333</v>
       </c>
       <c r="F13" s="27">
@@ -1736,11 +1736,11 @@
       <c r="L13" s="28" t="n"/>
       <c r="M13" s="28" t="n"/>
       <c r="N13" s="29" t="str">
-        <f>IF(OR(A13="",H13=""),"",IF(NOT(ISNUMBER(E13)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(F13)),NOT(ISNUMBER(G13))),"Margens inválidas",IF(H13=0,"Sem cobrança",IF(H13&lt;F13,"Abaixo do mínimo",IF(H13&lt;G13,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
+        <f>IF(OR(A13="",H13=""),"",IF(NOT(ISNUMBER(H13)),"Preço inválido",IF(NOT(ISNUMBER(E13)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F13)),NOT(ISNUMBER(G13))),"Margens inválidas",IF(H13=0,"Sem cobrança",IF(H13&lt;F13,"Abaixo do mínimo",IF(H13&lt;G13,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="O13" s="30">
-        <f>IF(OR(A13="",NOT(ISNUMBER(F13))),"",SUMPRODUCT((I13:M13&lt;&gt;"")*(I13:M13&gt;0)*(I13:M13*(1-Config!$B$8)&lt;E13)))</f>
+        <f>IF(OR(A13="",NOT(ISNUMBER(F13))),"",IF(SUMPRODUCT(ISTEXT(I13:M13)*1)&gt;0,"tabela com texto",SUMPRODUCT((I13:M13&lt;&gt;"")*(I13:M13&gt;0)*(I13:M13*(1-Config!$B$8)&lt;E13))))</f>
         <v>3</v>
       </c>
       <c r="P13" s="23" t="n">
@@ -1750,11 +1750,11 @@
         <v>2270</v>
       </c>
       <c r="R13" s="26">
-        <f>IF(OR(A13="",P13="",P13=0),"",Q13/P13)</f>
+        <f>IF(OR(A13="",AND(P13="",Q13="")),"",IF(OR(NOT(ISNUMBER(P13)),NOT(ISNUMBER(Q13))),"volume ou produção faltando",IF(P13=0,"",Q13/P13)))</f>
         <v>283.75</v>
       </c>
       <c r="S13" s="31">
-        <f>IF(OR(R13="",NOT(ISNUMBER(F13)),N(H13)=0),"",IF(F13=0,"sem base (mínimo zero)",R13/F13-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(R13)),NOT(ISNUMBER(F13)),N(H13)=0),"",IF(F13=0,"sem base (mínimo zero)",R13/F13-1))</f>
         <v>0.0573421052631582</v>
       </c>
       <c r="T13" s="22" t="n"/>
@@ -1777,7 +1777,7 @@
         <v>4</v>
       </c>
       <c r="E14" s="26">
-        <f>IF(A14="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",(B14+IF(C14="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D14))</f>
+        <f>IF(A14="","",IF(NOT(ISNUMBER((IF(NOT(IF(ISNUMBER(B14),AND(B14&gt;=0),FALSE)),"faltam os minutos",IF(AND(C14&lt;&gt;"Sim",C14&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C14="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B14+IF(C14="Sim",Config!$B$11*Config!$B$12,0))))))),(IF(NOT(IF(ISNUMBER(B14),AND(B14&gt;=0),FALSE)),"faltam os minutos",IF(AND(C14&lt;&gt;"Sim",C14&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C14="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B14+IF(C14="Sim",Config!$B$11*Config!$B$12,0))))),IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D14),AND(D14&gt;=0),FALSE)),"falta o material",(IF(NOT(IF(ISNUMBER(B14),AND(B14&gt;=0),FALSE)),"faltam os minutos",IF(AND(C14&lt;&gt;"Sim",C14&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C14="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B14+IF(C14="Sim",Config!$B$11*Config!$B$12,0)))))/60*Config!$B$7+D14))))</f>
         <v>164</v>
       </c>
       <c r="F14" s="27">
@@ -1799,11 +1799,11 @@
       <c r="L14" s="28" t="n"/>
       <c r="M14" s="28" t="n"/>
       <c r="N14" s="29" t="str">
-        <f>IF(OR(A14="",H14=""),"",IF(NOT(ISNUMBER(E14)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(F14)),NOT(ISNUMBER(G14))),"Margens inválidas",IF(H14=0,"Sem cobrança",IF(H14&lt;F14,"Abaixo do mínimo",IF(H14&lt;G14,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
+        <f>IF(OR(A14="",H14=""),"",IF(NOT(ISNUMBER(H14)),"Preço inválido",IF(NOT(ISNUMBER(E14)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F14)),NOT(ISNUMBER(G14))),"Margens inválidas",IF(H14=0,"Sem cobrança",IF(H14&lt;F14,"Abaixo do mínimo",IF(H14&lt;G14,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="O14" s="30">
-        <f>IF(OR(A14="",NOT(ISNUMBER(F14))),"",SUMPRODUCT((I14:M14&lt;&gt;"")*(I14:M14&gt;0)*(I14:M14*(1-Config!$B$8)&lt;E14)))</f>
+        <f>IF(OR(A14="",NOT(ISNUMBER(F14))),"",IF(SUMPRODUCT(ISTEXT(I14:M14)*1)&gt;0,"tabela com texto",SUMPRODUCT((I14:M14&lt;&gt;"")*(I14:M14&gt;0)*(I14:M14*(1-Config!$B$8)&lt;E14))))</f>
         <v>1</v>
       </c>
       <c r="P14" s="23" t="n">
@@ -1813,11 +1813,11 @@
         <v>10380</v>
       </c>
       <c r="R14" s="26">
-        <f>IF(OR(A14="",P14="",P14=0),"",Q14/P14)</f>
+        <f>IF(OR(A14="",AND(P14="",Q14="")),"",IF(OR(NOT(ISNUMBER(P14)),NOT(ISNUMBER(Q14))),"volume ou produção faltando",IF(P14=0,"",Q14/P14)))</f>
         <v>346</v>
       </c>
       <c r="S14" s="31">
-        <f>IF(OR(R14="",NOT(ISNUMBER(F14)),N(H14)=0),"",IF(F14=0,"sem base (mínimo zero)",R14/F14-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(R14)),NOT(ISNUMBER(F14)),N(H14)=0),"",IF(F14=0,"sem base (mínimo zero)",R14/F14-1))</f>
         <v>0.244756097560976</v>
       </c>
       <c r="T14" s="22" t="n"/>
@@ -1828,7 +1828,7 @@
       <c r="C15" s="24" t="n"/>
       <c r="D15" s="25" t="n"/>
       <c r="E15" s="26">
-        <f>IF(A15="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",(B15+IF(C15="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D15))</f>
+        <f>IF(A15="","",IF(NOT(ISNUMBER((IF(NOT(IF(ISNUMBER(B15),AND(B15&gt;=0),FALSE)),"faltam os minutos",IF(AND(C15&lt;&gt;"Sim",C15&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C15="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B15+IF(C15="Sim",Config!$B$11*Config!$B$12,0))))))),(IF(NOT(IF(ISNUMBER(B15),AND(B15&gt;=0),FALSE)),"faltam os minutos",IF(AND(C15&lt;&gt;"Sim",C15&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C15="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B15+IF(C15="Sim",Config!$B$11*Config!$B$12,0))))),IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D15),AND(D15&gt;=0),FALSE)),"falta o material",(IF(NOT(IF(ISNUMBER(B15),AND(B15&gt;=0),FALSE)),"faltam os minutos",IF(AND(C15&lt;&gt;"Sim",C15&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C15="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B15+IF(C15="Sim",Config!$B$11*Config!$B$12,0)))))/60*Config!$B$7+D15))))</f>
         <v/>
       </c>
       <c r="F15" s="27">
@@ -1846,21 +1846,21 @@
       <c r="L15" s="28" t="n"/>
       <c r="M15" s="28" t="n"/>
       <c r="N15" s="29">
-        <f>IF(OR(A15="",H15=""),"",IF(NOT(ISNUMBER(E15)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(F15)),NOT(ISNUMBER(G15))),"Margens inválidas",IF(H15=0,"Sem cobrança",IF(H15&lt;F15,"Abaixo do mínimo",IF(H15&lt;G15,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
+        <f>IF(OR(A15="",H15=""),"",IF(NOT(ISNUMBER(H15)),"Preço inválido",IF(NOT(ISNUMBER(E15)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F15)),NOT(ISNUMBER(G15))),"Margens inválidas",IF(H15=0,"Sem cobrança",IF(H15&lt;F15,"Abaixo do mínimo",IF(H15&lt;G15,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v/>
       </c>
       <c r="O15" s="30">
-        <f>IF(OR(A15="",NOT(ISNUMBER(F15))),"",SUMPRODUCT((I15:M15&lt;&gt;"")*(I15:M15&gt;0)*(I15:M15*(1-Config!$B$8)&lt;E15)))</f>
+        <f>IF(OR(A15="",NOT(ISNUMBER(F15))),"",IF(SUMPRODUCT(ISTEXT(I15:M15)*1)&gt;0,"tabela com texto",SUMPRODUCT((I15:M15&lt;&gt;"")*(I15:M15&gt;0)*(I15:M15*(1-Config!$B$8)&lt;E15))))</f>
         <v/>
       </c>
       <c r="P15" s="23" t="n"/>
       <c r="Q15" s="28" t="n"/>
       <c r="R15" s="26">
-        <f>IF(OR(A15="",P15="",P15=0),"",Q15/P15)</f>
+        <f>IF(OR(A15="",AND(P15="",Q15="")),"",IF(OR(NOT(ISNUMBER(P15)),NOT(ISNUMBER(Q15))),"volume ou produção faltando",IF(P15=0,"",Q15/P15)))</f>
         <v/>
       </c>
       <c r="S15" s="31">
-        <f>IF(OR(R15="",NOT(ISNUMBER(F15)),N(H15)=0),"",IF(F15=0,"sem base (mínimo zero)",R15/F15-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(R15)),NOT(ISNUMBER(F15)),N(H15)=0),"",IF(F15=0,"sem base (mínimo zero)",R15/F15-1))</f>
         <v/>
       </c>
       <c r="T15" s="22" t="n"/>
@@ -1871,7 +1871,7 @@
       <c r="C16" s="24" t="n"/>
       <c r="D16" s="25" t="n"/>
       <c r="E16" s="26">
-        <f>IF(A16="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",(B16+IF(C16="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D16))</f>
+        <f>IF(A16="","",IF(NOT(ISNUMBER((IF(NOT(IF(ISNUMBER(B16),AND(B16&gt;=0),FALSE)),"faltam os minutos",IF(AND(C16&lt;&gt;"Sim",C16&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C16="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B16+IF(C16="Sim",Config!$B$11*Config!$B$12,0))))))),(IF(NOT(IF(ISNUMBER(B16),AND(B16&gt;=0),FALSE)),"faltam os minutos",IF(AND(C16&lt;&gt;"Sim",C16&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C16="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B16+IF(C16="Sim",Config!$B$11*Config!$B$12,0))))),IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D16),AND(D16&gt;=0),FALSE)),"falta o material",(IF(NOT(IF(ISNUMBER(B16),AND(B16&gt;=0),FALSE)),"faltam os minutos",IF(AND(C16&lt;&gt;"Sim",C16&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C16="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B16+IF(C16="Sim",Config!$B$11*Config!$B$12,0)))))/60*Config!$B$7+D16))))</f>
         <v/>
       </c>
       <c r="F16" s="27">
@@ -1889,21 +1889,21 @@
       <c r="L16" s="28" t="n"/>
       <c r="M16" s="28" t="n"/>
       <c r="N16" s="29">
-        <f>IF(OR(A16="",H16=""),"",IF(NOT(ISNUMBER(E16)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(F16)),NOT(ISNUMBER(G16))),"Margens inválidas",IF(H16=0,"Sem cobrança",IF(H16&lt;F16,"Abaixo do mínimo",IF(H16&lt;G16,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
+        <f>IF(OR(A16="",H16=""),"",IF(NOT(ISNUMBER(H16)),"Preço inválido",IF(NOT(ISNUMBER(E16)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F16)),NOT(ISNUMBER(G16))),"Margens inválidas",IF(H16=0,"Sem cobrança",IF(H16&lt;F16,"Abaixo do mínimo",IF(H16&lt;G16,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v/>
       </c>
       <c r="O16" s="30">
-        <f>IF(OR(A16="",NOT(ISNUMBER(F16))),"",SUMPRODUCT((I16:M16&lt;&gt;"")*(I16:M16&gt;0)*(I16:M16*(1-Config!$B$8)&lt;E16)))</f>
+        <f>IF(OR(A16="",NOT(ISNUMBER(F16))),"",IF(SUMPRODUCT(ISTEXT(I16:M16)*1)&gt;0,"tabela com texto",SUMPRODUCT((I16:M16&lt;&gt;"")*(I16:M16&gt;0)*(I16:M16*(1-Config!$B$8)&lt;E16))))</f>
         <v/>
       </c>
       <c r="P16" s="23" t="n"/>
       <c r="Q16" s="28" t="n"/>
       <c r="R16" s="26">
-        <f>IF(OR(A16="",P16="",P16=0),"",Q16/P16)</f>
+        <f>IF(OR(A16="",AND(P16="",Q16="")),"",IF(OR(NOT(ISNUMBER(P16)),NOT(ISNUMBER(Q16))),"volume ou produção faltando",IF(P16=0,"",Q16/P16)))</f>
         <v/>
       </c>
       <c r="S16" s="31">
-        <f>IF(OR(R16="",NOT(ISNUMBER(F16)),N(H16)=0),"",IF(F16=0,"sem base (mínimo zero)",R16/F16-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(R16)),NOT(ISNUMBER(F16)),N(H16)=0),"",IF(F16=0,"sem base (mínimo zero)",R16/F16-1))</f>
         <v/>
       </c>
       <c r="T16" s="22" t="n"/>
@@ -1914,7 +1914,7 @@
       <c r="C17" s="24" t="n"/>
       <c r="D17" s="25" t="n"/>
       <c r="E17" s="26">
-        <f>IF(A17="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",(B17+IF(C17="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D17))</f>
+        <f>IF(A17="","",IF(NOT(ISNUMBER((IF(NOT(IF(ISNUMBER(B17),AND(B17&gt;=0),FALSE)),"faltam os minutos",IF(AND(C17&lt;&gt;"Sim",C17&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C17="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B17+IF(C17="Sim",Config!$B$11*Config!$B$12,0))))))),(IF(NOT(IF(ISNUMBER(B17),AND(B17&gt;=0),FALSE)),"faltam os minutos",IF(AND(C17&lt;&gt;"Sim",C17&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C17="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B17+IF(C17="Sim",Config!$B$11*Config!$B$12,0))))),IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D17),AND(D17&gt;=0),FALSE)),"falta o material",(IF(NOT(IF(ISNUMBER(B17),AND(B17&gt;=0),FALSE)),"faltam os minutos",IF(AND(C17&lt;&gt;"Sim",C17&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C17="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B17+IF(C17="Sim",Config!$B$11*Config!$B$12,0)))))/60*Config!$B$7+D17))))</f>
         <v/>
       </c>
       <c r="F17" s="27">
@@ -1932,21 +1932,21 @@
       <c r="L17" s="28" t="n"/>
       <c r="M17" s="28" t="n"/>
       <c r="N17" s="29">
-        <f>IF(OR(A17="",H17=""),"",IF(NOT(ISNUMBER(E17)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(F17)),NOT(ISNUMBER(G17))),"Margens inválidas",IF(H17=0,"Sem cobrança",IF(H17&lt;F17,"Abaixo do mínimo",IF(H17&lt;G17,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
+        <f>IF(OR(A17="",H17=""),"",IF(NOT(ISNUMBER(H17)),"Preço inválido",IF(NOT(ISNUMBER(E17)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F17)),NOT(ISNUMBER(G17))),"Margens inválidas",IF(H17=0,"Sem cobrança",IF(H17&lt;F17,"Abaixo do mínimo",IF(H17&lt;G17,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v/>
       </c>
       <c r="O17" s="30">
-        <f>IF(OR(A17="",NOT(ISNUMBER(F17))),"",SUMPRODUCT((I17:M17&lt;&gt;"")*(I17:M17&gt;0)*(I17:M17*(1-Config!$B$8)&lt;E17)))</f>
+        <f>IF(OR(A17="",NOT(ISNUMBER(F17))),"",IF(SUMPRODUCT(ISTEXT(I17:M17)*1)&gt;0,"tabela com texto",SUMPRODUCT((I17:M17&lt;&gt;"")*(I17:M17&gt;0)*(I17:M17*(1-Config!$B$8)&lt;E17))))</f>
         <v/>
       </c>
       <c r="P17" s="23" t="n"/>
       <c r="Q17" s="28" t="n"/>
       <c r="R17" s="26">
-        <f>IF(OR(A17="",P17="",P17=0),"",Q17/P17)</f>
+        <f>IF(OR(A17="",AND(P17="",Q17="")),"",IF(OR(NOT(ISNUMBER(P17)),NOT(ISNUMBER(Q17))),"volume ou produção faltando",IF(P17=0,"",Q17/P17)))</f>
         <v/>
       </c>
       <c r="S17" s="31">
-        <f>IF(OR(R17="",NOT(ISNUMBER(F17)),N(H17)=0),"",IF(F17=0,"sem base (mínimo zero)",R17/F17-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(R17)),NOT(ISNUMBER(F17)),N(H17)=0),"",IF(F17=0,"sem base (mínimo zero)",R17/F17-1))</f>
         <v/>
       </c>
       <c r="T17" s="22" t="n"/>
@@ -1957,7 +1957,7 @@
       <c r="C18" s="24" t="n"/>
       <c r="D18" s="25" t="n"/>
       <c r="E18" s="26">
-        <f>IF(A18="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",(B18+IF(C18="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D18))</f>
+        <f>IF(A18="","",IF(NOT(ISNUMBER((IF(NOT(IF(ISNUMBER(B18),AND(B18&gt;=0),FALSE)),"faltam os minutos",IF(AND(C18&lt;&gt;"Sim",C18&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C18="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B18+IF(C18="Sim",Config!$B$11*Config!$B$12,0))))))),(IF(NOT(IF(ISNUMBER(B18),AND(B18&gt;=0),FALSE)),"faltam os minutos",IF(AND(C18&lt;&gt;"Sim",C18&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C18="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B18+IF(C18="Sim",Config!$B$11*Config!$B$12,0))))),IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D18),AND(D18&gt;=0),FALSE)),"falta o material",(IF(NOT(IF(ISNUMBER(B18),AND(B18&gt;=0),FALSE)),"faltam os minutos",IF(AND(C18&lt;&gt;"Sim",C18&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C18="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B18+IF(C18="Sim",Config!$B$11*Config!$B$12,0)))))/60*Config!$B$7+D18))))</f>
         <v/>
       </c>
       <c r="F18" s="27">
@@ -1975,21 +1975,21 @@
       <c r="L18" s="28" t="n"/>
       <c r="M18" s="28" t="n"/>
       <c r="N18" s="29">
-        <f>IF(OR(A18="",H18=""),"",IF(NOT(ISNUMBER(E18)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(F18)),NOT(ISNUMBER(G18))),"Margens inválidas",IF(H18=0,"Sem cobrança",IF(H18&lt;F18,"Abaixo do mínimo",IF(H18&lt;G18,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
+        <f>IF(OR(A18="",H18=""),"",IF(NOT(ISNUMBER(H18)),"Preço inválido",IF(NOT(ISNUMBER(E18)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F18)),NOT(ISNUMBER(G18))),"Margens inválidas",IF(H18=0,"Sem cobrança",IF(H18&lt;F18,"Abaixo do mínimo",IF(H18&lt;G18,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v/>
       </c>
       <c r="O18" s="30">
-        <f>IF(OR(A18="",NOT(ISNUMBER(F18))),"",SUMPRODUCT((I18:M18&lt;&gt;"")*(I18:M18&gt;0)*(I18:M18*(1-Config!$B$8)&lt;E18)))</f>
+        <f>IF(OR(A18="",NOT(ISNUMBER(F18))),"",IF(SUMPRODUCT(ISTEXT(I18:M18)*1)&gt;0,"tabela com texto",SUMPRODUCT((I18:M18&lt;&gt;"")*(I18:M18&gt;0)*(I18:M18*(1-Config!$B$8)&lt;E18))))</f>
         <v/>
       </c>
       <c r="P18" s="23" t="n"/>
       <c r="Q18" s="28" t="n"/>
       <c r="R18" s="26">
-        <f>IF(OR(A18="",P18="",P18=0),"",Q18/P18)</f>
+        <f>IF(OR(A18="",AND(P18="",Q18="")),"",IF(OR(NOT(ISNUMBER(P18)),NOT(ISNUMBER(Q18))),"volume ou produção faltando",IF(P18=0,"",Q18/P18)))</f>
         <v/>
       </c>
       <c r="S18" s="31">
-        <f>IF(OR(R18="",NOT(ISNUMBER(F18)),N(H18)=0),"",IF(F18=0,"sem base (mínimo zero)",R18/F18-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(R18)),NOT(ISNUMBER(F18)),N(H18)=0),"",IF(F18=0,"sem base (mínimo zero)",R18/F18-1))</f>
         <v/>
       </c>
       <c r="T18" s="22" t="n"/>
@@ -2000,7 +2000,7 @@
       <c r="C19" s="24" t="n"/>
       <c r="D19" s="25" t="n"/>
       <c r="E19" s="26">
-        <f>IF(A19="","",IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",(B19+IF(C19="Sim",Config!$B$11*Config!$B$12,0))/60*Config!$B$7+D19))</f>
+        <f>IF(A19="","",IF(NOT(ISNUMBER((IF(NOT(IF(ISNUMBER(B19),AND(B19&gt;=0),FALSE)),"faltam os minutos",IF(AND(C19&lt;&gt;"Sim",C19&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C19="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B19+IF(C19="Sim",Config!$B$11*Config!$B$12,0))))))),(IF(NOT(IF(ISNUMBER(B19),AND(B19&gt;=0),FALSE)),"faltam os minutos",IF(AND(C19&lt;&gt;"Sim",C19&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C19="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B19+IF(C19="Sim",Config!$B$11*Config!$B$12,0))))),IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D19),AND(D19&gt;=0),FALSE)),"falta o material",(IF(NOT(IF(ISNUMBER(B19),AND(B19&gt;=0),FALSE)),"faltam os minutos",IF(AND(C19&lt;&gt;"Sim",C19&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C19="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B19+IF(C19="Sim",Config!$B$11*Config!$B$12,0)))))/60*Config!$B$7+D19))))</f>
         <v/>
       </c>
       <c r="F19" s="27">
@@ -2018,21 +2018,21 @@
       <c r="L19" s="28" t="n"/>
       <c r="M19" s="28" t="n"/>
       <c r="N19" s="29">
-        <f>IF(OR(A19="",H19=""),"",IF(NOT(ISNUMBER(E19)),"Falta o custo-hora",IF(OR(NOT(ISNUMBER(F19)),NOT(ISNUMBER(G19))),"Margens inválidas",IF(H19=0,"Sem cobrança",IF(H19&lt;F19,"Abaixo do mínimo",IF(H19&lt;G19,"Entre mínimo e alvo","No alvo ou acima"))))))</f>
+        <f>IF(OR(A19="",H19=""),"",IF(NOT(ISNUMBER(H19)),"Preço inválido",IF(NOT(ISNUMBER(E19)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F19)),NOT(ISNUMBER(G19))),"Margens inválidas",IF(H19=0,"Sem cobrança",IF(H19&lt;F19,"Abaixo do mínimo",IF(H19&lt;G19,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v/>
       </c>
       <c r="O19" s="30">
-        <f>IF(OR(A19="",NOT(ISNUMBER(F19))),"",SUMPRODUCT((I19:M19&lt;&gt;"")*(I19:M19&gt;0)*(I19:M19*(1-Config!$B$8)&lt;E19)))</f>
+        <f>IF(OR(A19="",NOT(ISNUMBER(F19))),"",IF(SUMPRODUCT(ISTEXT(I19:M19)*1)&gt;0,"tabela com texto",SUMPRODUCT((I19:M19&lt;&gt;"")*(I19:M19&gt;0)*(I19:M19*(1-Config!$B$8)&lt;E19))))</f>
         <v/>
       </c>
       <c r="P19" s="23" t="n"/>
       <c r="Q19" s="28" t="n"/>
       <c r="R19" s="26">
-        <f>IF(OR(A19="",P19="",P19=0),"",Q19/P19)</f>
+        <f>IF(OR(A19="",AND(P19="",Q19="")),"",IF(OR(NOT(ISNUMBER(P19)),NOT(ISNUMBER(Q19))),"volume ou produção faltando",IF(P19=0,"",Q19/P19)))</f>
         <v/>
       </c>
       <c r="S19" s="31">
-        <f>IF(OR(R19="",NOT(ISNUMBER(F19)),N(H19)=0),"",IF(F19=0,"sem base (mínimo zero)",R19/F19-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(R19)),NOT(ISNUMBER(F19)),N(H19)=0),"",IF(F19=0,"sem base (mínimo zero)",R19/F19-1))</f>
         <v/>
       </c>
       <c r="T19" s="22" t="n"/>
@@ -2119,31 +2119,31 @@
         <v>Consulta</v>
       </c>
       <c r="B27" s="35">
-        <f>IF($A8="","",B8+IF(C8="Sim",Config!$B$11*Config!$B$12,0))</f>
+        <f>IF($A8="","",IF(NOT(IF(ISNUMBER(B8),AND(B8&gt;=0),FALSE)),"faltam os minutos",IF(AND(C8&lt;&gt;"Sim",C8&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C8="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B8+IF(C8="Sim",Config!$B$11*Config!$B$12,0)))))</f>
         <v>38</v>
       </c>
       <c r="C27" s="36">
-        <f>IF(OR($A8="",H8="",$B27=0),"",H8/($B27/60))</f>
+        <f>IF(OR($A8="",H8="",NOT(ISNUMBER(H8)),NOT(ISNUMBER($B27)),N($B27)=0),"",H8/($B27/60))</f>
         <v>600</v>
       </c>
       <c r="D27" s="36">
-        <f>IF(OR($A8="",I8="",$B27=0),"",I8/($B27/60))</f>
+        <f>IF(OR($A8="",I8="",NOT(ISNUMBER(I8)),NOT(ISNUMBER($B27)),N($B27)=0),"",I8/($B27/60))</f>
         <v>189.473684210526</v>
       </c>
       <c r="E27" s="36">
-        <f>IF(OR($A8="",J8="",$B27=0),"",J8/($B27/60))</f>
+        <f>IF(OR($A8="",J8="",NOT(ISNUMBER(J8)),NOT(ISNUMBER($B27)),N($B27)=0),"",J8/($B27/60))</f>
         <v>157.894736842105</v>
       </c>
       <c r="F27" s="36">
-        <f>IF(OR($A8="",K8="",$B27=0),"",K8/($B27/60))</f>
+        <f>IF(OR($A8="",K8="",NOT(ISNUMBER(K8)),NOT(ISNUMBER($B27)),N($B27)=0),"",K8/($B27/60))</f>
         <v>142.105263157895</v>
       </c>
       <c r="G27" s="36">
-        <f>IF(OR($A8="",L8="",$B27=0),"",L8/($B27/60))</f>
+        <f>IF(OR($A8="",L8="",NOT(ISNUMBER(L8)),NOT(ISNUMBER($B27)),N($B27)=0),"",L8/($B27/60))</f>
         <v/>
       </c>
       <c r="H27" s="36">
-        <f>IF(OR($A8="",M8="",$B27=0),"",M8/($B27/60))</f>
+        <f>IF(OR($A8="",M8="",NOT(ISNUMBER(M8)),NOT(ISNUMBER($B27)),N($B27)=0),"",M8/($B27/60))</f>
         <v/>
       </c>
       <c r="I27" s="36">
@@ -2161,31 +2161,31 @@
         <v>Retorno</v>
       </c>
       <c r="B28" s="35">
-        <f>IF($A9="","",B9+IF(C9="Sim",Config!$B$11*Config!$B$12,0))</f>
+        <f>IF($A9="","",IF(NOT(IF(ISNUMBER(B9),AND(B9&gt;=0),FALSE)),"faltam os minutos",IF(AND(C9&lt;&gt;"Sim",C9&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C9="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B9+IF(C9="Sim",Config!$B$11*Config!$B$12,0)))))</f>
         <v>20</v>
       </c>
       <c r="C28" s="36">
-        <f>IF(OR($A9="",H9="",$B28=0),"",H9/($B28/60))</f>
+        <f>IF(OR($A9="",H9="",NOT(ISNUMBER(H9)),NOT(ISNUMBER($B28)),N($B28)=0),"",H9/($B28/60))</f>
         <v>0</v>
       </c>
       <c r="D28" s="36">
-        <f>IF(OR($A9="",I9="",$B28=0),"",I9/($B28/60))</f>
+        <f>IF(OR($A9="",I9="",NOT(ISNUMBER(I9)),NOT(ISNUMBER($B28)),N($B28)=0),"",I9/($B28/60))</f>
         <v>0</v>
       </c>
       <c r="E28" s="36">
-        <f>IF(OR($A9="",J9="",$B28=0),"",J9/($B28/60))</f>
+        <f>IF(OR($A9="",J9="",NOT(ISNUMBER(J9)),NOT(ISNUMBER($B28)),N($B28)=0),"",J9/($B28/60))</f>
         <v>0</v>
       </c>
       <c r="F28" s="36">
-        <f>IF(OR($A9="",K9="",$B28=0),"",K9/($B28/60))</f>
+        <f>IF(OR($A9="",K9="",NOT(ISNUMBER(K9)),NOT(ISNUMBER($B28)),N($B28)=0),"",K9/($B28/60))</f>
         <v>0</v>
       </c>
       <c r="G28" s="36">
-        <f>IF(OR($A9="",L9="",$B28=0),"",L9/($B28/60))</f>
+        <f>IF(OR($A9="",L9="",NOT(ISNUMBER(L9)),NOT(ISNUMBER($B28)),N($B28)=0),"",L9/($B28/60))</f>
         <v/>
       </c>
       <c r="H28" s="36">
-        <f>IF(OR($A9="",M9="",$B28=0),"",M9/($B28/60))</f>
+        <f>IF(OR($A9="",M9="",NOT(ISNUMBER(M9)),NOT(ISNUMBER($B28)),N($B28)=0),"",M9/($B28/60))</f>
         <v/>
       </c>
       <c r="I28" s="36">
@@ -2203,31 +2203,31 @@
         <v>ECG</v>
       </c>
       <c r="B29" s="35">
-        <f>IF($A10="","",B10+IF(C10="Sim",Config!$B$11*Config!$B$12,0))</f>
+        <f>IF($A10="","",IF(NOT(IF(ISNUMBER(B10),AND(B10&gt;=0),FALSE)),"faltam os minutos",IF(AND(C10&lt;&gt;"Sim",C10&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C10="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B10+IF(C10="Sim",Config!$B$11*Config!$B$12,0)))))</f>
         <v>20</v>
       </c>
       <c r="C29" s="36">
-        <f>IF(OR($A10="",H10="",$B29=0),"",H10/($B29/60))</f>
+        <f>IF(OR($A10="",H10="",NOT(ISNUMBER(H10)),NOT(ISNUMBER($B29)),N($B29)=0),"",H10/($B29/60))</f>
         <v>390</v>
       </c>
       <c r="D29" s="36">
-        <f>IF(OR($A10="",I10="",$B29=0),"",I10/($B29/60))</f>
+        <f>IF(OR($A10="",I10="",NOT(ISNUMBER(I10)),NOT(ISNUMBER($B29)),N($B29)=0),"",I10/($B29/60))</f>
         <v>120</v>
       </c>
       <c r="E29" s="36">
-        <f>IF(OR($A10="",J10="",$B29=0),"",J10/($B29/60))</f>
+        <f>IF(OR($A10="",J10="",NOT(ISNUMBER(J10)),NOT(ISNUMBER($B29)),N($B29)=0),"",J10/($B29/60))</f>
         <v>105</v>
       </c>
       <c r="F29" s="36">
-        <f>IF(OR($A10="",K10="",$B29=0),"",K10/($B29/60))</f>
+        <f>IF(OR($A10="",K10="",NOT(ISNUMBER(K10)),NOT(ISNUMBER($B29)),N($B29)=0),"",K10/($B29/60))</f>
         <v>96</v>
       </c>
       <c r="G29" s="36">
-        <f>IF(OR($A10="",L10="",$B29=0),"",L10/($B29/60))</f>
+        <f>IF(OR($A10="",L10="",NOT(ISNUMBER(L10)),NOT(ISNUMBER($B29)),N($B29)=0),"",L10/($B29/60))</f>
         <v/>
       </c>
       <c r="H29" s="36">
-        <f>IF(OR($A10="",M10="",$B29=0),"",M10/($B29/60))</f>
+        <f>IF(OR($A10="",M10="",NOT(ISNUMBER(M10)),NOT(ISNUMBER($B29)),N($B29)=0),"",M10/($B29/60))</f>
         <v/>
       </c>
       <c r="I29" s="36">
@@ -2245,31 +2245,31 @@
         <v>MAPA</v>
       </c>
       <c r="B30" s="35">
-        <f>IF($A11="","",B11+IF(C11="Sim",Config!$B$11*Config!$B$12,0))</f>
+        <f>IF($A11="","",IF(NOT(IF(ISNUMBER(B11),AND(B11&gt;=0),FALSE)),"faltam os minutos",IF(AND(C11&lt;&gt;"Sim",C11&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C11="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B11+IF(C11="Sim",Config!$B$11*Config!$B$12,0)))))</f>
         <v>20</v>
       </c>
       <c r="C30" s="36">
-        <f>IF(OR($A11="",H11="",$B30=0),"",H11/($B30/60))</f>
+        <f>IF(OR($A11="",H11="",NOT(ISNUMBER(H11)),NOT(ISNUMBER($B30)),N($B30)=0),"",H11/($B30/60))</f>
         <v>900</v>
       </c>
       <c r="D30" s="36">
-        <f>IF(OR($A11="",I11="",$B30=0),"",I11/($B30/60))</f>
+        <f>IF(OR($A11="",I11="",NOT(ISNUMBER(I11)),NOT(ISNUMBER($B30)),N($B30)=0),"",I11/($B30/60))</f>
         <v>285</v>
       </c>
       <c r="E30" s="36">
-        <f>IF(OR($A11="",J11="",$B30=0),"",J11/($B30/60))</f>
+        <f>IF(OR($A11="",J11="",NOT(ISNUMBER(J11)),NOT(ISNUMBER($B30)),N($B30)=0),"",J11/($B30/60))</f>
         <v>255</v>
       </c>
       <c r="F30" s="36">
-        <f>IF(OR($A11="",K11="",$B30=0),"",K11/($B30/60))</f>
+        <f>IF(OR($A11="",K11="",NOT(ISNUMBER(K11)),NOT(ISNUMBER($B30)),N($B30)=0),"",K11/($B30/60))</f>
         <v>225</v>
       </c>
       <c r="G30" s="36">
-        <f>IF(OR($A11="",L11="",$B30=0),"",L11/($B30/60))</f>
+        <f>IF(OR($A11="",L11="",NOT(ISNUMBER(L11)),NOT(ISNUMBER($B30)),N($B30)=0),"",L11/($B30/60))</f>
         <v/>
       </c>
       <c r="H30" s="36">
-        <f>IF(OR($A11="",M11="",$B30=0),"",M11/($B30/60))</f>
+        <f>IF(OR($A11="",M11="",NOT(ISNUMBER(M11)),NOT(ISNUMBER($B30)),N($B30)=0),"",M11/($B30/60))</f>
         <v/>
       </c>
       <c r="I30" s="36">
@@ -2287,31 +2287,31 @@
         <v>Holter</v>
       </c>
       <c r="B31" s="35">
-        <f>IF($A12="","",B12+IF(C12="Sim",Config!$B$11*Config!$B$12,0))</f>
+        <f>IF($A12="","",IF(NOT(IF(ISNUMBER(B12),AND(B12&gt;=0),FALSE)),"faltam os minutos",IF(AND(C12&lt;&gt;"Sim",C12&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C12="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B12+IF(C12="Sim",Config!$B$11*Config!$B$12,0)))))</f>
         <v>20</v>
       </c>
       <c r="C31" s="36">
-        <f>IF(OR($A12="",H12="",$B31=0),"",H12/($B31/60))</f>
+        <f>IF(OR($A12="",H12="",NOT(ISNUMBER(H12)),NOT(ISNUMBER($B31)),N($B31)=0),"",H12/($B31/60))</f>
         <v>1050</v>
       </c>
       <c r="D31" s="36">
-        <f>IF(OR($A12="",I12="",$B31=0),"",I12/($B31/60))</f>
+        <f>IF(OR($A12="",I12="",NOT(ISNUMBER(I12)),NOT(ISNUMBER($B31)),N($B31)=0),"",I12/($B31/60))</f>
         <v>315</v>
       </c>
       <c r="E31" s="36">
-        <f>IF(OR($A12="",J12="",$B31=0),"",J12/($B31/60))</f>
+        <f>IF(OR($A12="",J12="",NOT(ISNUMBER(J12)),NOT(ISNUMBER($B31)),N($B31)=0),"",J12/($B31/60))</f>
         <v>285</v>
       </c>
       <c r="F31" s="36">
-        <f>IF(OR($A12="",K12="",$B31=0),"",K12/($B31/60))</f>
+        <f>IF(OR($A12="",K12="",NOT(ISNUMBER(K12)),NOT(ISNUMBER($B31)),N($B31)=0),"",K12/($B31/60))</f>
         <v>255</v>
       </c>
       <c r="G31" s="36">
-        <f>IF(OR($A12="",L12="",$B31=0),"",L12/($B31/60))</f>
+        <f>IF(OR($A12="",L12="",NOT(ISNUMBER(L12)),NOT(ISNUMBER($B31)),N($B31)=0),"",L12/($B31/60))</f>
         <v/>
       </c>
       <c r="H31" s="36">
-        <f>IF(OR($A12="",M12="",$B31=0),"",M12/($B31/60))</f>
+        <f>IF(OR($A12="",M12="",NOT(ISNUMBER(M12)),NOT(ISNUMBER($B31)),N($B31)=0),"",M12/($B31/60))</f>
         <v/>
       </c>
       <c r="I31" s="36">
@@ -2329,31 +2329,31 @@
         <v>Teste ergométrico</v>
       </c>
       <c r="B32" s="35">
-        <f>IF($A13="","",B13+IF(C13="Sim",Config!$B$11*Config!$B$12,0))</f>
+        <f>IF($A13="","",IF(NOT(IF(ISNUMBER(B13),AND(B13&gt;=0),FALSE)),"faltam os minutos",IF(AND(C13&lt;&gt;"Sim",C13&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C13="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B13+IF(C13="Sim",Config!$B$11*Config!$B$12,0)))))</f>
         <v>40</v>
       </c>
       <c r="C32" s="36">
-        <f>IF(OR($A13="",H13="",$B32=0),"",H13/($B32/60))</f>
+        <f>IF(OR($A13="",H13="",NOT(ISNUMBER(H13)),NOT(ISNUMBER($B32)),N($B32)=0),"",H13/($B32/60))</f>
         <v>675</v>
       </c>
       <c r="D32" s="36">
-        <f>IF(OR($A13="",I13="",$B32=0),"",I13/($B32/60))</f>
+        <f>IF(OR($A13="",I13="",NOT(ISNUMBER(I13)),NOT(ISNUMBER($B32)),N($B32)=0),"",I13/($B32/60))</f>
         <v>210</v>
       </c>
       <c r="E32" s="36">
-        <f>IF(OR($A13="",J13="",$B32=0),"",J13/($B32/60))</f>
+        <f>IF(OR($A13="",J13="",NOT(ISNUMBER(J13)),NOT(ISNUMBER($B32)),N($B32)=0),"",J13/($B32/60))</f>
         <v>187.5</v>
       </c>
       <c r="F32" s="36">
-        <f>IF(OR($A13="",K13="",$B32=0),"",K13/($B32/60))</f>
+        <f>IF(OR($A13="",K13="",NOT(ISNUMBER(K13)),NOT(ISNUMBER($B32)),N($B32)=0),"",K13/($B32/60))</f>
         <v>165</v>
       </c>
       <c r="G32" s="36">
-        <f>IF(OR($A13="",L13="",$B32=0),"",L13/($B32/60))</f>
+        <f>IF(OR($A13="",L13="",NOT(ISNUMBER(L13)),NOT(ISNUMBER($B32)),N($B32)=0),"",L13/($B32/60))</f>
         <v/>
       </c>
       <c r="H32" s="36">
-        <f>IF(OR($A13="",M13="",$B32=0),"",M13/($B32/60))</f>
+        <f>IF(OR($A13="",M13="",NOT(ISNUMBER(M13)),NOT(ISNUMBER($B32)),N($B32)=0),"",M13/($B32/60))</f>
         <v/>
       </c>
       <c r="I32" s="36">
@@ -2371,31 +2371,31 @@
         <v>Avaliação endócrina</v>
       </c>
       <c r="B33" s="35">
-        <f>IF($A14="","",B14+IF(C14="Sim",Config!$B$11*Config!$B$12,0))</f>
+        <f>IF($A14="","",IF(NOT(IF(ISNUMBER(B14),AND(B14&gt;=0),FALSE)),"faltam os minutos",IF(AND(C14&lt;&gt;"Sim",C14&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C14="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B14+IF(C14="Sim",Config!$B$11*Config!$B$12,0)))))</f>
         <v>48</v>
       </c>
       <c r="C33" s="36">
-        <f>IF(OR($A14="",H14="",$B33=0),"",H14/($B33/60))</f>
+        <f>IF(OR($A14="",H14="",NOT(ISNUMBER(H14)),NOT(ISNUMBER($B33)),N($B33)=0),"",H14/($B33/60))</f>
         <v>500</v>
       </c>
       <c r="D33" s="36">
-        <f>IF(OR($A14="",I14="",$B33=0),"",I14/($B33/60))</f>
+        <f>IF(OR($A14="",I14="",NOT(ISNUMBER(I14)),NOT(ISNUMBER($B33)),N($B33)=0),"",I14/($B33/60))</f>
         <v>162.5</v>
       </c>
       <c r="E33" s="36">
-        <f>IF(OR($A14="",J14="",$B33=0),"",J14/($B33/60))</f>
+        <f>IF(OR($A14="",J14="",NOT(ISNUMBER(J14)),NOT(ISNUMBER($B33)),N($B33)=0),"",J14/($B33/60))</f>
         <v/>
       </c>
       <c r="F33" s="36">
-        <f>IF(OR($A14="",K14="",$B33=0),"",K14/($B33/60))</f>
+        <f>IF(OR($A14="",K14="",NOT(ISNUMBER(K14)),NOT(ISNUMBER($B33)),N($B33)=0),"",K14/($B33/60))</f>
         <v/>
       </c>
       <c r="G33" s="36">
-        <f>IF(OR($A14="",L14="",$B33=0),"",L14/($B33/60))</f>
+        <f>IF(OR($A14="",L14="",NOT(ISNUMBER(L14)),NOT(ISNUMBER($B33)),N($B33)=0),"",L14/($B33/60))</f>
         <v/>
       </c>
       <c r="H33" s="36">
-        <f>IF(OR($A14="",M14="",$B33=0),"",M14/($B33/60))</f>
+        <f>IF(OR($A14="",M14="",NOT(ISNUMBER(M14)),NOT(ISNUMBER($B33)),N($B33)=0),"",M14/($B33/60))</f>
         <v/>
       </c>
       <c r="I33" s="36">
@@ -2413,31 +2413,31 @@
         <v/>
       </c>
       <c r="B34" s="35">
-        <f>IF($A15="","",B15+IF(C15="Sim",Config!$B$11*Config!$B$12,0))</f>
+        <f>IF($A15="","",IF(NOT(IF(ISNUMBER(B15),AND(B15&gt;=0),FALSE)),"faltam os minutos",IF(AND(C15&lt;&gt;"Sim",C15&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C15="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B15+IF(C15="Sim",Config!$B$11*Config!$B$12,0)))))</f>
         <v/>
       </c>
       <c r="C34" s="36">
-        <f>IF(OR($A15="",H15="",$B34=0),"",H15/($B34/60))</f>
+        <f>IF(OR($A15="",H15="",NOT(ISNUMBER(H15)),NOT(ISNUMBER($B34)),N($B34)=0),"",H15/($B34/60))</f>
         <v/>
       </c>
       <c r="D34" s="36">
-        <f>IF(OR($A15="",I15="",$B34=0),"",I15/($B34/60))</f>
+        <f>IF(OR($A15="",I15="",NOT(ISNUMBER(I15)),NOT(ISNUMBER($B34)),N($B34)=0),"",I15/($B34/60))</f>
         <v/>
       </c>
       <c r="E34" s="36">
-        <f>IF(OR($A15="",J15="",$B34=0),"",J15/($B34/60))</f>
+        <f>IF(OR($A15="",J15="",NOT(ISNUMBER(J15)),NOT(ISNUMBER($B34)),N($B34)=0),"",J15/($B34/60))</f>
         <v/>
       </c>
       <c r="F34" s="36">
-        <f>IF(OR($A15="",K15="",$B34=0),"",K15/($B34/60))</f>
+        <f>IF(OR($A15="",K15="",NOT(ISNUMBER(K15)),NOT(ISNUMBER($B34)),N($B34)=0),"",K15/($B34/60))</f>
         <v/>
       </c>
       <c r="G34" s="36">
-        <f>IF(OR($A15="",L15="",$B34=0),"",L15/($B34/60))</f>
+        <f>IF(OR($A15="",L15="",NOT(ISNUMBER(L15)),NOT(ISNUMBER($B34)),N($B34)=0),"",L15/($B34/60))</f>
         <v/>
       </c>
       <c r="H34" s="36">
-        <f>IF(OR($A15="",M15="",$B34=0),"",M15/($B34/60))</f>
+        <f>IF(OR($A15="",M15="",NOT(ISNUMBER(M15)),NOT(ISNUMBER($B34)),N($B34)=0),"",M15/($B34/60))</f>
         <v/>
       </c>
       <c r="I34" s="36">
@@ -2455,31 +2455,31 @@
         <v/>
       </c>
       <c r="B35" s="35">
-        <f>IF($A16="","",B16+IF(C16="Sim",Config!$B$11*Config!$B$12,0))</f>
+        <f>IF($A16="","",IF(NOT(IF(ISNUMBER(B16),AND(B16&gt;=0),FALSE)),"faltam os minutos",IF(AND(C16&lt;&gt;"Sim",C16&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C16="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B16+IF(C16="Sim",Config!$B$11*Config!$B$12,0)))))</f>
         <v/>
       </c>
       <c r="C35" s="36">
-        <f>IF(OR($A16="",H16="",$B35=0),"",H16/($B35/60))</f>
+        <f>IF(OR($A16="",H16="",NOT(ISNUMBER(H16)),NOT(ISNUMBER($B35)),N($B35)=0),"",H16/($B35/60))</f>
         <v/>
       </c>
       <c r="D35" s="36">
-        <f>IF(OR($A16="",I16="",$B35=0),"",I16/($B35/60))</f>
+        <f>IF(OR($A16="",I16="",NOT(ISNUMBER(I16)),NOT(ISNUMBER($B35)),N($B35)=0),"",I16/($B35/60))</f>
         <v/>
       </c>
       <c r="E35" s="36">
-        <f>IF(OR($A16="",J16="",$B35=0),"",J16/($B35/60))</f>
+        <f>IF(OR($A16="",J16="",NOT(ISNUMBER(J16)),NOT(ISNUMBER($B35)),N($B35)=0),"",J16/($B35/60))</f>
         <v/>
       </c>
       <c r="F35" s="36">
-        <f>IF(OR($A16="",K16="",$B35=0),"",K16/($B35/60))</f>
+        <f>IF(OR($A16="",K16="",NOT(ISNUMBER(K16)),NOT(ISNUMBER($B35)),N($B35)=0),"",K16/($B35/60))</f>
         <v/>
       </c>
       <c r="G35" s="36">
-        <f>IF(OR($A16="",L16="",$B35=0),"",L16/($B35/60))</f>
+        <f>IF(OR($A16="",L16="",NOT(ISNUMBER(L16)),NOT(ISNUMBER($B35)),N($B35)=0),"",L16/($B35/60))</f>
         <v/>
       </c>
       <c r="H35" s="36">
-        <f>IF(OR($A16="",M16="",$B35=0),"",M16/($B35/60))</f>
+        <f>IF(OR($A16="",M16="",NOT(ISNUMBER(M16)),NOT(ISNUMBER($B35)),N($B35)=0),"",M16/($B35/60))</f>
         <v/>
       </c>
       <c r="I35" s="36">
@@ -2497,31 +2497,31 @@
         <v/>
       </c>
       <c r="B36" s="35">
-        <f>IF($A17="","",B17+IF(C17="Sim",Config!$B$11*Config!$B$12,0))</f>
+        <f>IF($A17="","",IF(NOT(IF(ISNUMBER(B17),AND(B17&gt;=0),FALSE)),"faltam os minutos",IF(AND(C17&lt;&gt;"Sim",C17&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C17="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B17+IF(C17="Sim",Config!$B$11*Config!$B$12,0)))))</f>
         <v/>
       </c>
       <c r="C36" s="36">
-        <f>IF(OR($A17="",H17="",$B36=0),"",H17/($B36/60))</f>
+        <f>IF(OR($A17="",H17="",NOT(ISNUMBER(H17)),NOT(ISNUMBER($B36)),N($B36)=0),"",H17/($B36/60))</f>
         <v/>
       </c>
       <c r="D36" s="36">
-        <f>IF(OR($A17="",I17="",$B36=0),"",I17/($B36/60))</f>
+        <f>IF(OR($A17="",I17="",NOT(ISNUMBER(I17)),NOT(ISNUMBER($B36)),N($B36)=0),"",I17/($B36/60))</f>
         <v/>
       </c>
       <c r="E36" s="36">
-        <f>IF(OR($A17="",J17="",$B36=0),"",J17/($B36/60))</f>
+        <f>IF(OR($A17="",J17="",NOT(ISNUMBER(J17)),NOT(ISNUMBER($B36)),N($B36)=0),"",J17/($B36/60))</f>
         <v/>
       </c>
       <c r="F36" s="36">
-        <f>IF(OR($A17="",K17="",$B36=0),"",K17/($B36/60))</f>
+        <f>IF(OR($A17="",K17="",NOT(ISNUMBER(K17)),NOT(ISNUMBER($B36)),N($B36)=0),"",K17/($B36/60))</f>
         <v/>
       </c>
       <c r="G36" s="36">
-        <f>IF(OR($A17="",L17="",$B36=0),"",L17/($B36/60))</f>
+        <f>IF(OR($A17="",L17="",NOT(ISNUMBER(L17)),NOT(ISNUMBER($B36)),N($B36)=0),"",L17/($B36/60))</f>
         <v/>
       </c>
       <c r="H36" s="36">
-        <f>IF(OR($A17="",M17="",$B36=0),"",M17/($B36/60))</f>
+        <f>IF(OR($A17="",M17="",NOT(ISNUMBER(M17)),NOT(ISNUMBER($B36)),N($B36)=0),"",M17/($B36/60))</f>
         <v/>
       </c>
       <c r="I36" s="36">
@@ -2539,31 +2539,31 @@
         <v/>
       </c>
       <c r="B37" s="35">
-        <f>IF($A18="","",B18+IF(C18="Sim",Config!$B$11*Config!$B$12,0))</f>
+        <f>IF($A18="","",IF(NOT(IF(ISNUMBER(B18),AND(B18&gt;=0),FALSE)),"faltam os minutos",IF(AND(C18&lt;&gt;"Sim",C18&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C18="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B18+IF(C18="Sim",Config!$B$11*Config!$B$12,0)))))</f>
         <v/>
       </c>
       <c r="C37" s="36">
-        <f>IF(OR($A18="",H18="",$B37=0),"",H18/($B37/60))</f>
+        <f>IF(OR($A18="",H18="",NOT(ISNUMBER(H18)),NOT(ISNUMBER($B37)),N($B37)=0),"",H18/($B37/60))</f>
         <v/>
       </c>
       <c r="D37" s="36">
-        <f>IF(OR($A18="",I18="",$B37=0),"",I18/($B37/60))</f>
+        <f>IF(OR($A18="",I18="",NOT(ISNUMBER(I18)),NOT(ISNUMBER($B37)),N($B37)=0),"",I18/($B37/60))</f>
         <v/>
       </c>
       <c r="E37" s="36">
-        <f>IF(OR($A18="",J18="",$B37=0),"",J18/($B37/60))</f>
+        <f>IF(OR($A18="",J18="",NOT(ISNUMBER(J18)),NOT(ISNUMBER($B37)),N($B37)=0),"",J18/($B37/60))</f>
         <v/>
       </c>
       <c r="F37" s="36">
-        <f>IF(OR($A18="",K18="",$B37=0),"",K18/($B37/60))</f>
+        <f>IF(OR($A18="",K18="",NOT(ISNUMBER(K18)),NOT(ISNUMBER($B37)),N($B37)=0),"",K18/($B37/60))</f>
         <v/>
       </c>
       <c r="G37" s="36">
-        <f>IF(OR($A18="",L18="",$B37=0),"",L18/($B37/60))</f>
+        <f>IF(OR($A18="",L18="",NOT(ISNUMBER(L18)),NOT(ISNUMBER($B37)),N($B37)=0),"",L18/($B37/60))</f>
         <v/>
       </c>
       <c r="H37" s="36">
-        <f>IF(OR($A18="",M18="",$B37=0),"",M18/($B37/60))</f>
+        <f>IF(OR($A18="",M18="",NOT(ISNUMBER(M18)),NOT(ISNUMBER($B37)),N($B37)=0),"",M18/($B37/60))</f>
         <v/>
       </c>
       <c r="I37" s="36">
@@ -2581,31 +2581,31 @@
         <v/>
       </c>
       <c r="B38" s="35">
-        <f>IF($A19="","",B19+IF(C19="Sim",Config!$B$11*Config!$B$12,0))</f>
+        <f>IF($A19="","",IF(NOT(IF(ISNUMBER(B19),AND(B19&gt;=0),FALSE)),"faltam os minutos",IF(AND(C19&lt;&gt;"Sim",C19&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C19="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B19+IF(C19="Sim",Config!$B$11*Config!$B$12,0)))))</f>
         <v/>
       </c>
       <c r="C38" s="36">
-        <f>IF(OR($A19="",H19="",$B38=0),"",H19/($B38/60))</f>
+        <f>IF(OR($A19="",H19="",NOT(ISNUMBER(H19)),NOT(ISNUMBER($B38)),N($B38)=0),"",H19/($B38/60))</f>
         <v/>
       </c>
       <c r="D38" s="36">
-        <f>IF(OR($A19="",I19="",$B38=0),"",I19/($B38/60))</f>
+        <f>IF(OR($A19="",I19="",NOT(ISNUMBER(I19)),NOT(ISNUMBER($B38)),N($B38)=0),"",I19/($B38/60))</f>
         <v/>
       </c>
       <c r="E38" s="36">
-        <f>IF(OR($A19="",J19="",$B38=0),"",J19/($B38/60))</f>
+        <f>IF(OR($A19="",J19="",NOT(ISNUMBER(J19)),NOT(ISNUMBER($B38)),N($B38)=0),"",J19/($B38/60))</f>
         <v/>
       </c>
       <c r="F38" s="36">
-        <f>IF(OR($A19="",K19="",$B38=0),"",K19/($B38/60))</f>
+        <f>IF(OR($A19="",K19="",NOT(ISNUMBER(K19)),NOT(ISNUMBER($B38)),N($B38)=0),"",K19/($B38/60))</f>
         <v/>
       </c>
       <c r="G38" s="36">
-        <f>IF(OR($A19="",L19="",$B38=0),"",L19/($B38/60))</f>
+        <f>IF(OR($A19="",L19="",NOT(ISNUMBER(L19)),NOT(ISNUMBER($B38)),N($B38)=0),"",L19/($B38/60))</f>
         <v/>
       </c>
       <c r="H38" s="36">
-        <f>IF(OR($A19="",M19="",$B38=0),"",M19/($B38/60))</f>
+        <f>IF(OR($A19="",M19="",NOT(ISNUMBER(M19)),NOT(ISNUMBER($B38)),N($B38)=0),"",M19/($B38/60))</f>
         <v/>
       </c>
       <c r="I38" s="36">
@@ -2649,7 +2649,7 @@
   </mergeCells>
   <conditionalFormatting sqref="N8:N19">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>OR(N8="Abaixo do mínimo",N8="Falta o custo-hora",N8="Margens inválidas")</formula>
+      <formula>OR(N8="Abaixo do mínimo",N8="Falta o custo-hora",N8="Margens inválidas",N8="Faltam dados da linha",N8="Preço inválido")</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1">
       <formula>N8="Entre mínimo e alvo"</formula>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/08-tabela-de-precos.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/08-tabela-de-precos.xlsx
@@ -1235,22 +1235,22 @@
       </c>
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="16" t="str">
-        <f>IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF((SUMPRODUCT(($A$8:$A$19&lt;&gt;"")*(ISNUMBER($F$8:$F$19)=FALSE))+SUMPRODUCT(ISTEXT($H$8:$M$19)*1))&gt;0,(SUMPRODUCT(($A$8:$A$19&lt;&gt;"")*(ISNUMBER($F$8:$F$19)=FALSE))+SUMPRODUCT(ISTEXT($H$8:$M$19)*1))&amp;" linha(s) ou preço(s) incompletos",COUNTIF($N$8:$N$19,"Abaixo do mínimo")&amp;" de "&amp;COUNTA($A$8:$A$19)))</f>
+        <f>IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF((SUMPRODUCT(($A$8:$A$19&lt;&gt;"")*(ISNUMBER($F$8:$F$19)=FALSE))+SUMPRODUCT(ISTEXT($H$8:$M$19)+ISNUMBER($H$8:$M$19)*($H$8:$M$19&lt;0))+SUMPRODUCT(($A$8:$A$19="")*(($B$8:$B$19&lt;&gt;"")+($C$8:$C$19&lt;&gt;"")+($D$8:$D$19&lt;&gt;"")+($H$8:$H$19&lt;&gt;"")+($I$8:$I$19&lt;&gt;"")+($J$8:$J$19&lt;&gt;"")+($K$8:$K$19&lt;&gt;"")+($L$8:$L$19&lt;&gt;"")+($M$8:$M$19&lt;&gt;"")+($P$8:$P$19&lt;&gt;"")+($Q$8:$Q$19&lt;&gt;"")&gt;0)))&gt;0,(SUMPRODUCT(($A$8:$A$19&lt;&gt;"")*(ISNUMBER($F$8:$F$19)=FALSE))+SUMPRODUCT(ISTEXT($H$8:$M$19)+ISNUMBER($H$8:$M$19)*($H$8:$M$19&lt;0))+SUMPRODUCT(($A$8:$A$19="")*(($B$8:$B$19&lt;&gt;"")+($C$8:$C$19&lt;&gt;"")+($D$8:$D$19&lt;&gt;"")+($H$8:$H$19&lt;&gt;"")+($I$8:$I$19&lt;&gt;"")+($J$8:$J$19&lt;&gt;"")+($K$8:$K$19&lt;&gt;"")+($L$8:$L$19&lt;&gt;"")+($M$8:$M$19&lt;&gt;"")+($P$8:$P$19&lt;&gt;"")+($Q$8:$Q$19&lt;&gt;"")&gt;0)))&amp;" linha(s) ou preço(s) incompletos",COUNTIF($N$8:$N$19,"Abaixo do mínimo")&amp;" de "&amp;COUNTA($A$8:$A$19)))</f>
         <v>0 de 7</v>
       </c>
       <c r="D5" s="10" t="n"/>
       <c r="E5" s="17">
-        <f>IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF((SUMPRODUCT(($A$8:$A$19&lt;&gt;"")*(ISNUMBER($F$8:$F$19)=FALSE))+SUMPRODUCT(ISTEXT($H$8:$M$19)*1))&gt;0,(SUMPRODUCT(($A$8:$A$19&lt;&gt;"")*(ISNUMBER($F$8:$F$19)=FALSE))+SUMPRODUCT(ISTEXT($H$8:$M$19)*1))&amp;" linha(s) ou preço(s) incompletos",SUM($O$8:$O$19)))</f>
+        <f>IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF((SUMPRODUCT(($A$8:$A$19&lt;&gt;"")*(ISNUMBER($F$8:$F$19)=FALSE))+SUMPRODUCT(ISTEXT($H$8:$M$19)+ISNUMBER($H$8:$M$19)*($H$8:$M$19&lt;0))+SUMPRODUCT(($A$8:$A$19="")*(($B$8:$B$19&lt;&gt;"")+($C$8:$C$19&lt;&gt;"")+($D$8:$D$19&lt;&gt;"")+($H$8:$H$19&lt;&gt;"")+($I$8:$I$19&lt;&gt;"")+($J$8:$J$19&lt;&gt;"")+($K$8:$K$19&lt;&gt;"")+($L$8:$L$19&lt;&gt;"")+($M$8:$M$19&lt;&gt;"")+($P$8:$P$19&lt;&gt;"")+($Q$8:$Q$19&lt;&gt;"")&gt;0)))&gt;0,(SUMPRODUCT(($A$8:$A$19&lt;&gt;"")*(ISNUMBER($F$8:$F$19)=FALSE))+SUMPRODUCT(ISTEXT($H$8:$M$19)+ISNUMBER($H$8:$M$19)*($H$8:$M$19&lt;0))+SUMPRODUCT(($A$8:$A$19="")*(($B$8:$B$19&lt;&gt;"")+($C$8:$C$19&lt;&gt;"")+($D$8:$D$19&lt;&gt;"")+($H$8:$H$19&lt;&gt;"")+($I$8:$I$19&lt;&gt;"")+($J$8:$J$19&lt;&gt;"")+($K$8:$K$19&lt;&gt;"")+($L$8:$L$19&lt;&gt;"")+($M$8:$M$19&lt;&gt;"")+($P$8:$P$19&lt;&gt;"")+($Q$8:$Q$19&lt;&gt;"")&gt;0)))&amp;" linha(s) ou preço(s) incompletos",SUM($O$8:$O$19)))</f>
         <v>14</v>
       </c>
       <c r="F5" s="10" t="n"/>
       <c r="G5" s="18">
-        <f>IF(SUMPRODUCT(ISTEXT($Q$8:$Q$19)*1)&gt;0,"produção com texto",SUM($Q$8:$Q$19))</f>
+        <f>IF((SUMPRODUCT((($P$8:$P$19&lt;&gt;"")+($Q$8:$Q$19&lt;&gt;"")&gt;0)*((ISNUMBER($P$8:$P$19)=FALSE)+ISNUMBER($P$8:$P$19)*($P$8:$P$19&lt;0)+(ISNUMBER($Q$8:$Q$19)=FALSE)+ISNUMBER($Q$8:$Q$19)*($Q$8:$Q$19&lt;0)&gt;0))+SUMPRODUCT(($A$8:$A$19="")*(($B$8:$B$19&lt;&gt;"")+($C$8:$C$19&lt;&gt;"")+($D$8:$D$19&lt;&gt;"")+($H$8:$H$19&lt;&gt;"")+($I$8:$I$19&lt;&gt;"")+($J$8:$J$19&lt;&gt;"")+($K$8:$K$19&lt;&gt;"")+($L$8:$L$19&lt;&gt;"")+($M$8:$M$19&lt;&gt;"")+($P$8:$P$19&lt;&gt;"")+($Q$8:$Q$19&lt;&gt;"")&gt;0)))&gt;0,"produção incompleta em "&amp;(SUMPRODUCT((($P$8:$P$19&lt;&gt;"")+($Q$8:$Q$19&lt;&gt;"")&gt;0)*((ISNUMBER($P$8:$P$19)=FALSE)+ISNUMBER($P$8:$P$19)*($P$8:$P$19&lt;0)+(ISNUMBER($Q$8:$Q$19)=FALSE)+ISNUMBER($Q$8:$Q$19)*($Q$8:$Q$19&lt;0)&gt;0))+SUMPRODUCT(($A$8:$A$19="")*(($B$8:$B$19&lt;&gt;"")+($C$8:$C$19&lt;&gt;"")+($D$8:$D$19&lt;&gt;"")+($H$8:$H$19&lt;&gt;"")+($I$8:$I$19&lt;&gt;"")+($J$8:$J$19&lt;&gt;"")+($K$8:$K$19&lt;&gt;"")+($L$8:$L$19&lt;&gt;"")+($M$8:$M$19&lt;&gt;"")+($P$8:$P$19&lt;&gt;"")+($Q$8:$Q$19&lt;&gt;"")&gt;0)))&amp;" linha(s)",SUM($Q$8:$Q$19))</f>
         <v>48631</v>
       </c>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="19">
-        <f>IF(SUMPRODUCT((($P$8:$P$19&lt;&gt;"")+($Q$8:$Q$19&lt;&gt;"")&gt;0)*((ISNUMBER($P$8:$P$19)=FALSE)+(ISNUMBER($Q$8:$Q$19)=FALSE)+(ISNUMBER($B$8:$B$19)=FALSE)&gt;0))&gt;0,"volume incompleto em "&amp;SUMPRODUCT((($P$8:$P$19&lt;&gt;"")+($Q$8:$Q$19&lt;&gt;"")&gt;0)*((ISNUMBER($P$8:$P$19)=FALSE)+(ISNUMBER($Q$8:$Q$19)=FALSE)+(ISNUMBER($B$8:$B$19)=FALSE)&gt;0))&amp;" linha(s)",IFERROR(SUM($Q$8:$Q$19)/(SUMPRODUCT($P$8:$P$19,$B$8:$B$19)/60),""))</f>
+        <f>IF((SUMPRODUCT((($P$8:$P$19&lt;&gt;"")+($Q$8:$Q$19&lt;&gt;"")&gt;0)*((ISNUMBER($P$8:$P$19)=FALSE)+ISNUMBER($P$8:$P$19)*($P$8:$P$19&lt;0)+(ISNUMBER($Q$8:$Q$19)=FALSE)+ISNUMBER($Q$8:$Q$19)*($Q$8:$Q$19&lt;0)+(ISNUMBER($B$8:$B$19)=FALSE)+ISNUMBER($B$8:$B$19)*($B$8:$B$19&lt;0)&gt;0))+SUMPRODUCT(($A$8:$A$19="")*(($B$8:$B$19&lt;&gt;"")+($C$8:$C$19&lt;&gt;"")+($D$8:$D$19&lt;&gt;"")+($H$8:$H$19&lt;&gt;"")+($I$8:$I$19&lt;&gt;"")+($J$8:$J$19&lt;&gt;"")+($K$8:$K$19&lt;&gt;"")+($L$8:$L$19&lt;&gt;"")+($M$8:$M$19&lt;&gt;"")+($P$8:$P$19&lt;&gt;"")+($Q$8:$Q$19&lt;&gt;"")&gt;0)))&gt;0,"volume incompleto em "&amp;(SUMPRODUCT((($P$8:$P$19&lt;&gt;"")+($Q$8:$Q$19&lt;&gt;"")&gt;0)*((ISNUMBER($P$8:$P$19)=FALSE)+ISNUMBER($P$8:$P$19)*($P$8:$P$19&lt;0)+(ISNUMBER($Q$8:$Q$19)=FALSE)+ISNUMBER($Q$8:$Q$19)*($Q$8:$Q$19&lt;0)+(ISNUMBER($B$8:$B$19)=FALSE)+ISNUMBER($B$8:$B$19)*($B$8:$B$19&lt;0)&gt;0))+SUMPRODUCT(($A$8:$A$19="")*(($B$8:$B$19&lt;&gt;"")+($C$8:$C$19&lt;&gt;"")+($D$8:$D$19&lt;&gt;"")+($H$8:$H$19&lt;&gt;"")+($I$8:$I$19&lt;&gt;"")+($J$8:$J$19&lt;&gt;"")+($K$8:$K$19&lt;&gt;"")+($L$8:$L$19&lt;&gt;"")+($M$8:$M$19&lt;&gt;"")+($P$8:$P$19&lt;&gt;"")+($Q$8:$Q$19&lt;&gt;"")&gt;0)))&amp;" linha(s)",IFERROR(SUM($Q$8:$Q$19)/(SUMPRODUCT($P$8:$P$19,$B$8:$B$19)/60),""))</f>
         <v>410.966197183099</v>
       </c>
       <c r="J5" s="14" t="n"/>
@@ -1401,11 +1401,11 @@
       <c r="L8" s="28" t="n"/>
       <c r="M8" s="28" t="n"/>
       <c r="N8" s="29" t="str">
-        <f>IF(OR(A8="",H8=""),"",IF(NOT(ISNUMBER(H8)),"Preço inválido",IF(NOT(ISNUMBER(E8)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F8)),NOT(ISNUMBER(G8))),"Margens inválidas",IF(H8=0,"Sem cobrança",IF(H8&lt;F8,"Abaixo do mínimo",IF(H8&lt;G8,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(OR(A8="",H8=""),"",IF(NOT(IF(ISNUMBER(H8),AND(H8&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(E8)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F8)),NOT(ISNUMBER(G8))),"Margens inválidas",IF(H8=0,"Sem cobrança",IF(H8&lt;F8,"Abaixo do mínimo",IF(H8&lt;G8,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="O8" s="30">
-        <f>IF(OR(A8="",NOT(ISNUMBER(F8))),"",IF(SUMPRODUCT(ISTEXT(I8:M8)*1)&gt;0,"tabela com texto",SUMPRODUCT((I8:M8&lt;&gt;"")*(I8:M8&gt;0)*(I8:M8*(1-Config!$B$8)&lt;E8))))</f>
+        <f>IF(OR(A8="",NOT(ISNUMBER(F8))),"",IF(SUMPRODUCT(ISTEXT(I8:M8)+ISNUMBER(I8:M8)*(I8:M8&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I8:M8&lt;&gt;"")*(I8:M8&gt;0)*(I8:M8*(1-Config!$B$8)&lt;E8))))</f>
         <v>3</v>
       </c>
       <c r="P8" s="23" t="n">
@@ -1415,7 +1415,7 @@
         <v>30730</v>
       </c>
       <c r="R8" s="26">
-        <f>IF(OR(A8="",AND(P8="",Q8="")),"",IF(OR(NOT(ISNUMBER(P8)),NOT(ISNUMBER(Q8))),"volume ou produção faltando",IF(P8=0,"",Q8/P8)))</f>
+        <f>IF(OR(A8="",AND(P8="",Q8="")),"",IF(OR(NOT(IF(ISNUMBER(P8),AND(P8&gt;=0),FALSE)),NOT(IF(ISNUMBER(Q8),AND(Q8&gt;=0),FALSE))),"volume ou produção faltando ou negativos",IF(P8=0,"",Q8/P8)))</f>
         <v>236.384615384615</v>
       </c>
       <c r="S8" s="31">
@@ -1468,11 +1468,11 @@
       <c r="L9" s="28" t="n"/>
       <c r="M9" s="28" t="n"/>
       <c r="N9" s="29" t="str">
-        <f>IF(OR(A9="",H9=""),"",IF(NOT(ISNUMBER(H9)),"Preço inválido",IF(NOT(ISNUMBER(E9)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F9)),NOT(ISNUMBER(G9))),"Margens inválidas",IF(H9=0,"Sem cobrança",IF(H9&lt;F9,"Abaixo do mínimo",IF(H9&lt;G9,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(OR(A9="",H9=""),"",IF(NOT(IF(ISNUMBER(H9),AND(H9&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(E9)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F9)),NOT(ISNUMBER(G9))),"Margens inválidas",IF(H9=0,"Sem cobrança",IF(H9&lt;F9,"Abaixo do mínimo",IF(H9&lt;G9,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v>Sem cobrança</v>
       </c>
       <c r="O9" s="30">
-        <f>IF(OR(A9="",NOT(ISNUMBER(F9))),"",IF(SUMPRODUCT(ISTEXT(I9:M9)*1)&gt;0,"tabela com texto",SUMPRODUCT((I9:M9&lt;&gt;"")*(I9:M9&gt;0)*(I9:M9*(1-Config!$B$8)&lt;E9))))</f>
+        <f>IF(OR(A9="",NOT(ISNUMBER(F9))),"",IF(SUMPRODUCT(ISTEXT(I9:M9)+ISNUMBER(I9:M9)*(I9:M9&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I9:M9&lt;&gt;"")*(I9:M9&gt;0)*(I9:M9*(1-Config!$B$8)&lt;E9))))</f>
         <v>0</v>
       </c>
       <c r="P9" s="23" t="n">
@@ -1482,7 +1482,7 @@
         <v>0</v>
       </c>
       <c r="R9" s="26">
-        <f>IF(OR(A9="",AND(P9="",Q9="")),"",IF(OR(NOT(ISNUMBER(P9)),NOT(ISNUMBER(Q9))),"volume ou produção faltando",IF(P9=0,"",Q9/P9)))</f>
+        <f>IF(OR(A9="",AND(P9="",Q9="")),"",IF(OR(NOT(IF(ISNUMBER(P9),AND(P9&gt;=0),FALSE)),NOT(IF(ISNUMBER(Q9),AND(Q9&gt;=0),FALSE))),"volume ou produção faltando ou negativos",IF(P9=0,"",Q9/P9)))</f>
         <v>0</v>
       </c>
       <c r="S9" s="31">
@@ -1535,11 +1535,11 @@
       <c r="L10" s="28" t="n"/>
       <c r="M10" s="28" t="n"/>
       <c r="N10" s="29" t="str">
-        <f>IF(OR(A10="",H10=""),"",IF(NOT(ISNUMBER(H10)),"Preço inválido",IF(NOT(ISNUMBER(E10)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F10)),NOT(ISNUMBER(G10))),"Margens inválidas",IF(H10=0,"Sem cobrança",IF(H10&lt;F10,"Abaixo do mínimo",IF(H10&lt;G10,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(OR(A10="",H10=""),"",IF(NOT(IF(ISNUMBER(H10),AND(H10&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(E10)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F10)),NOT(ISNUMBER(G10))),"Margens inválidas",IF(H10=0,"Sem cobrança",IF(H10&lt;F10,"Abaixo do mínimo",IF(H10&lt;G10,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v>Entre mínimo e alvo</v>
       </c>
       <c r="O10" s="30">
-        <f>IF(OR(A10="",NOT(ISNUMBER(F10))),"",IF(SUMPRODUCT(ISTEXT(I10:M10)*1)&gt;0,"tabela com texto",SUMPRODUCT((I10:M10&lt;&gt;"")*(I10:M10&gt;0)*(I10:M10*(1-Config!$B$8)&lt;E10))))</f>
+        <f>IF(OR(A10="",NOT(ISNUMBER(F10))),"",IF(SUMPRODUCT(ISTEXT(I10:M10)+ISNUMBER(I10:M10)*(I10:M10&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I10:M10&lt;&gt;"")*(I10:M10&gt;0)*(I10:M10*(1-Config!$B$8)&lt;E10))))</f>
         <v>3</v>
       </c>
       <c r="P10" s="23" t="n">
@@ -1549,7 +1549,7 @@
         <v>1416</v>
       </c>
       <c r="R10" s="26">
-        <f>IF(OR(A10="",AND(P10="",Q10="")),"",IF(OR(NOT(ISNUMBER(P10)),NOT(ISNUMBER(Q10))),"volume ou produção faltando",IF(P10=0,"",Q10/P10)))</f>
+        <f>IF(OR(A10="",AND(P10="",Q10="")),"",IF(OR(NOT(IF(ISNUMBER(P10),AND(P10&gt;=0),FALSE)),NOT(IF(ISNUMBER(Q10),AND(Q10&gt;=0),FALSE))),"volume ou produção faltando ou negativos",IF(P10=0,"",Q10/P10)))</f>
         <v>78.6666666666667</v>
       </c>
       <c r="S10" s="31">
@@ -1602,11 +1602,11 @@
       <c r="L11" s="28" t="n"/>
       <c r="M11" s="28" t="n"/>
       <c r="N11" s="29" t="str">
-        <f>IF(OR(A11="",H11=""),"",IF(NOT(ISNUMBER(H11)),"Preço inválido",IF(NOT(ISNUMBER(E11)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F11)),NOT(ISNUMBER(G11))),"Margens inválidas",IF(H11=0,"Sem cobrança",IF(H11&lt;F11,"Abaixo do mínimo",IF(H11&lt;G11,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(OR(A11="",H11=""),"",IF(NOT(IF(ISNUMBER(H11),AND(H11&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(E11)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F11)),NOT(ISNUMBER(G11))),"Margens inválidas",IF(H11=0,"Sem cobrança",IF(H11&lt;F11,"Abaixo do mínimo",IF(H11&lt;G11,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="O11" s="30">
-        <f>IF(OR(A11="",NOT(ISNUMBER(F11))),"",IF(SUMPRODUCT(ISTEXT(I11:M11)*1)&gt;0,"tabela com texto",SUMPRODUCT((I11:M11&lt;&gt;"")*(I11:M11&gt;0)*(I11:M11*(1-Config!$B$8)&lt;E11))))</f>
+        <f>IF(OR(A11="",NOT(ISNUMBER(F11))),"",IF(SUMPRODUCT(ISTEXT(I11:M11)+ISNUMBER(I11:M11)*(I11:M11&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I11:M11&lt;&gt;"")*(I11:M11&gt;0)*(I11:M11*(1-Config!$B$8)&lt;E11))))</f>
         <v>2</v>
       </c>
       <c r="P11" s="23" t="n">
@@ -1616,7 +1616,7 @@
         <v>1345</v>
       </c>
       <c r="R11" s="26">
-        <f>IF(OR(A11="",AND(P11="",Q11="")),"",IF(OR(NOT(ISNUMBER(P11)),NOT(ISNUMBER(Q11))),"volume ou produção faltando",IF(P11=0,"",Q11/P11)))</f>
+        <f>IF(OR(A11="",AND(P11="",Q11="")),"",IF(OR(NOT(IF(ISNUMBER(P11),AND(P11&gt;=0),FALSE)),NOT(IF(ISNUMBER(Q11),AND(Q11&gt;=0),FALSE))),"volume ou produção faltando ou negativos",IF(P11=0,"",Q11/P11)))</f>
         <v>168.125</v>
       </c>
       <c r="S11" s="31">
@@ -1669,11 +1669,11 @@
       <c r="L12" s="28" t="n"/>
       <c r="M12" s="28" t="n"/>
       <c r="N12" s="29" t="str">
-        <f>IF(OR(A12="",H12=""),"",IF(NOT(ISNUMBER(H12)),"Preço inválido",IF(NOT(ISNUMBER(E12)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F12)),NOT(ISNUMBER(G12))),"Margens inválidas",IF(H12=0,"Sem cobrança",IF(H12&lt;F12,"Abaixo do mínimo",IF(H12&lt;G12,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(OR(A12="",H12=""),"",IF(NOT(IF(ISNUMBER(H12),AND(H12&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(E12)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F12)),NOT(ISNUMBER(G12))),"Margens inválidas",IF(H12=0,"Sem cobrança",IF(H12&lt;F12,"Abaixo do mínimo",IF(H12&lt;G12,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="O12" s="30">
-        <f>IF(OR(A12="",NOT(ISNUMBER(F12))),"",IF(SUMPRODUCT(ISTEXT(I12:M12)*1)&gt;0,"tabela com texto",SUMPRODUCT((I12:M12&lt;&gt;"")*(I12:M12&gt;0)*(I12:M12*(1-Config!$B$8)&lt;E12))))</f>
+        <f>IF(OR(A12="",NOT(ISNUMBER(F12))),"",IF(SUMPRODUCT(ISTEXT(I12:M12)+ISNUMBER(I12:M12)*(I12:M12&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I12:M12&lt;&gt;"")*(I12:M12&gt;0)*(I12:M12*(1-Config!$B$8)&lt;E12))))</f>
         <v>2</v>
       </c>
       <c r="P12" s="23" t="n">
@@ -1683,7 +1683,7 @@
         <v>2490</v>
       </c>
       <c r="R12" s="26">
-        <f>IF(OR(A12="",AND(P12="",Q12="")),"",IF(OR(NOT(ISNUMBER(P12)),NOT(ISNUMBER(Q12))),"volume ou produção faltando",IF(P12=0,"",Q12/P12)))</f>
+        <f>IF(OR(A12="",AND(P12="",Q12="")),"",IF(OR(NOT(IF(ISNUMBER(P12),AND(P12&gt;=0),FALSE)),NOT(IF(ISNUMBER(Q12),AND(Q12&gt;=0),FALSE))),"volume ou produção faltando ou negativos",IF(P12=0,"",Q12/P12)))</f>
         <v>249</v>
       </c>
       <c r="S12" s="31">
@@ -1736,11 +1736,11 @@
       <c r="L13" s="28" t="n"/>
       <c r="M13" s="28" t="n"/>
       <c r="N13" s="29" t="str">
-        <f>IF(OR(A13="",H13=""),"",IF(NOT(ISNUMBER(H13)),"Preço inválido",IF(NOT(ISNUMBER(E13)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F13)),NOT(ISNUMBER(G13))),"Margens inválidas",IF(H13=0,"Sem cobrança",IF(H13&lt;F13,"Abaixo do mínimo",IF(H13&lt;G13,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(OR(A13="",H13=""),"",IF(NOT(IF(ISNUMBER(H13),AND(H13&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(E13)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F13)),NOT(ISNUMBER(G13))),"Margens inválidas",IF(H13=0,"Sem cobrança",IF(H13&lt;F13,"Abaixo do mínimo",IF(H13&lt;G13,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="O13" s="30">
-        <f>IF(OR(A13="",NOT(ISNUMBER(F13))),"",IF(SUMPRODUCT(ISTEXT(I13:M13)*1)&gt;0,"tabela com texto",SUMPRODUCT((I13:M13&lt;&gt;"")*(I13:M13&gt;0)*(I13:M13*(1-Config!$B$8)&lt;E13))))</f>
+        <f>IF(OR(A13="",NOT(ISNUMBER(F13))),"",IF(SUMPRODUCT(ISTEXT(I13:M13)+ISNUMBER(I13:M13)*(I13:M13&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I13:M13&lt;&gt;"")*(I13:M13&gt;0)*(I13:M13*(1-Config!$B$8)&lt;E13))))</f>
         <v>3</v>
       </c>
       <c r="P13" s="23" t="n">
@@ -1750,7 +1750,7 @@
         <v>2270</v>
       </c>
       <c r="R13" s="26">
-        <f>IF(OR(A13="",AND(P13="",Q13="")),"",IF(OR(NOT(ISNUMBER(P13)),NOT(ISNUMBER(Q13))),"volume ou produção faltando",IF(P13=0,"",Q13/P13)))</f>
+        <f>IF(OR(A13="",AND(P13="",Q13="")),"",IF(OR(NOT(IF(ISNUMBER(P13),AND(P13&gt;=0),FALSE)),NOT(IF(ISNUMBER(Q13),AND(Q13&gt;=0),FALSE))),"volume ou produção faltando ou negativos",IF(P13=0,"",Q13/P13)))</f>
         <v>283.75</v>
       </c>
       <c r="S13" s="31">
@@ -1799,11 +1799,11 @@
       <c r="L14" s="28" t="n"/>
       <c r="M14" s="28" t="n"/>
       <c r="N14" s="29" t="str">
-        <f>IF(OR(A14="",H14=""),"",IF(NOT(ISNUMBER(H14)),"Preço inválido",IF(NOT(ISNUMBER(E14)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F14)),NOT(ISNUMBER(G14))),"Margens inválidas",IF(H14=0,"Sem cobrança",IF(H14&lt;F14,"Abaixo do mínimo",IF(H14&lt;G14,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(OR(A14="",H14=""),"",IF(NOT(IF(ISNUMBER(H14),AND(H14&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(E14)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F14)),NOT(ISNUMBER(G14))),"Margens inválidas",IF(H14=0,"Sem cobrança",IF(H14&lt;F14,"Abaixo do mínimo",IF(H14&lt;G14,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="O14" s="30">
-        <f>IF(OR(A14="",NOT(ISNUMBER(F14))),"",IF(SUMPRODUCT(ISTEXT(I14:M14)*1)&gt;0,"tabela com texto",SUMPRODUCT((I14:M14&lt;&gt;"")*(I14:M14&gt;0)*(I14:M14*(1-Config!$B$8)&lt;E14))))</f>
+        <f>IF(OR(A14="",NOT(ISNUMBER(F14))),"",IF(SUMPRODUCT(ISTEXT(I14:M14)+ISNUMBER(I14:M14)*(I14:M14&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I14:M14&lt;&gt;"")*(I14:M14&gt;0)*(I14:M14*(1-Config!$B$8)&lt;E14))))</f>
         <v>1</v>
       </c>
       <c r="P14" s="23" t="n">
@@ -1813,7 +1813,7 @@
         <v>10380</v>
       </c>
       <c r="R14" s="26">
-        <f>IF(OR(A14="",AND(P14="",Q14="")),"",IF(OR(NOT(ISNUMBER(P14)),NOT(ISNUMBER(Q14))),"volume ou produção faltando",IF(P14=0,"",Q14/P14)))</f>
+        <f>IF(OR(A14="",AND(P14="",Q14="")),"",IF(OR(NOT(IF(ISNUMBER(P14),AND(P14&gt;=0),FALSE)),NOT(IF(ISNUMBER(Q14),AND(Q14&gt;=0),FALSE))),"volume ou produção faltando ou negativos",IF(P14=0,"",Q14/P14)))</f>
         <v>346</v>
       </c>
       <c r="S14" s="31">
@@ -1846,17 +1846,17 @@
       <c r="L15" s="28" t="n"/>
       <c r="M15" s="28" t="n"/>
       <c r="N15" s="29">
-        <f>IF(OR(A15="",H15=""),"",IF(NOT(ISNUMBER(H15)),"Preço inválido",IF(NOT(ISNUMBER(E15)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F15)),NOT(ISNUMBER(G15))),"Margens inválidas",IF(H15=0,"Sem cobrança",IF(H15&lt;F15,"Abaixo do mínimo",IF(H15&lt;G15,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(OR(A15="",H15=""),"",IF(NOT(IF(ISNUMBER(H15),AND(H15&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(E15)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F15)),NOT(ISNUMBER(G15))),"Margens inválidas",IF(H15=0,"Sem cobrança",IF(H15&lt;F15,"Abaixo do mínimo",IF(H15&lt;G15,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v/>
       </c>
       <c r="O15" s="30">
-        <f>IF(OR(A15="",NOT(ISNUMBER(F15))),"",IF(SUMPRODUCT(ISTEXT(I15:M15)*1)&gt;0,"tabela com texto",SUMPRODUCT((I15:M15&lt;&gt;"")*(I15:M15&gt;0)*(I15:M15*(1-Config!$B$8)&lt;E15))))</f>
+        <f>IF(OR(A15="",NOT(ISNUMBER(F15))),"",IF(SUMPRODUCT(ISTEXT(I15:M15)+ISNUMBER(I15:M15)*(I15:M15&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I15:M15&lt;&gt;"")*(I15:M15&gt;0)*(I15:M15*(1-Config!$B$8)&lt;E15))))</f>
         <v/>
       </c>
       <c r="P15" s="23" t="n"/>
       <c r="Q15" s="28" t="n"/>
       <c r="R15" s="26">
-        <f>IF(OR(A15="",AND(P15="",Q15="")),"",IF(OR(NOT(ISNUMBER(P15)),NOT(ISNUMBER(Q15))),"volume ou produção faltando",IF(P15=0,"",Q15/P15)))</f>
+        <f>IF(OR(A15="",AND(P15="",Q15="")),"",IF(OR(NOT(IF(ISNUMBER(P15),AND(P15&gt;=0),FALSE)),NOT(IF(ISNUMBER(Q15),AND(Q15&gt;=0),FALSE))),"volume ou produção faltando ou negativos",IF(P15=0,"",Q15/P15)))</f>
         <v/>
       </c>
       <c r="S15" s="31">
@@ -1889,17 +1889,17 @@
       <c r="L16" s="28" t="n"/>
       <c r="M16" s="28" t="n"/>
       <c r="N16" s="29">
-        <f>IF(OR(A16="",H16=""),"",IF(NOT(ISNUMBER(H16)),"Preço inválido",IF(NOT(ISNUMBER(E16)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F16)),NOT(ISNUMBER(G16))),"Margens inválidas",IF(H16=0,"Sem cobrança",IF(H16&lt;F16,"Abaixo do mínimo",IF(H16&lt;G16,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(OR(A16="",H16=""),"",IF(NOT(IF(ISNUMBER(H16),AND(H16&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(E16)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F16)),NOT(ISNUMBER(G16))),"Margens inválidas",IF(H16=0,"Sem cobrança",IF(H16&lt;F16,"Abaixo do mínimo",IF(H16&lt;G16,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v/>
       </c>
       <c r="O16" s="30">
-        <f>IF(OR(A16="",NOT(ISNUMBER(F16))),"",IF(SUMPRODUCT(ISTEXT(I16:M16)*1)&gt;0,"tabela com texto",SUMPRODUCT((I16:M16&lt;&gt;"")*(I16:M16&gt;0)*(I16:M16*(1-Config!$B$8)&lt;E16))))</f>
+        <f>IF(OR(A16="",NOT(ISNUMBER(F16))),"",IF(SUMPRODUCT(ISTEXT(I16:M16)+ISNUMBER(I16:M16)*(I16:M16&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I16:M16&lt;&gt;"")*(I16:M16&gt;0)*(I16:M16*(1-Config!$B$8)&lt;E16))))</f>
         <v/>
       </c>
       <c r="P16" s="23" t="n"/>
       <c r="Q16" s="28" t="n"/>
       <c r="R16" s="26">
-        <f>IF(OR(A16="",AND(P16="",Q16="")),"",IF(OR(NOT(ISNUMBER(P16)),NOT(ISNUMBER(Q16))),"volume ou produção faltando",IF(P16=0,"",Q16/P16)))</f>
+        <f>IF(OR(A16="",AND(P16="",Q16="")),"",IF(OR(NOT(IF(ISNUMBER(P16),AND(P16&gt;=0),FALSE)),NOT(IF(ISNUMBER(Q16),AND(Q16&gt;=0),FALSE))),"volume ou produção faltando ou negativos",IF(P16=0,"",Q16/P16)))</f>
         <v/>
       </c>
       <c r="S16" s="31">
@@ -1932,17 +1932,17 @@
       <c r="L17" s="28" t="n"/>
       <c r="M17" s="28" t="n"/>
       <c r="N17" s="29">
-        <f>IF(OR(A17="",H17=""),"",IF(NOT(ISNUMBER(H17)),"Preço inválido",IF(NOT(ISNUMBER(E17)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F17)),NOT(ISNUMBER(G17))),"Margens inválidas",IF(H17=0,"Sem cobrança",IF(H17&lt;F17,"Abaixo do mínimo",IF(H17&lt;G17,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(OR(A17="",H17=""),"",IF(NOT(IF(ISNUMBER(H17),AND(H17&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(E17)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F17)),NOT(ISNUMBER(G17))),"Margens inválidas",IF(H17=0,"Sem cobrança",IF(H17&lt;F17,"Abaixo do mínimo",IF(H17&lt;G17,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v/>
       </c>
       <c r="O17" s="30">
-        <f>IF(OR(A17="",NOT(ISNUMBER(F17))),"",IF(SUMPRODUCT(ISTEXT(I17:M17)*1)&gt;0,"tabela com texto",SUMPRODUCT((I17:M17&lt;&gt;"")*(I17:M17&gt;0)*(I17:M17*(1-Config!$B$8)&lt;E17))))</f>
+        <f>IF(OR(A17="",NOT(ISNUMBER(F17))),"",IF(SUMPRODUCT(ISTEXT(I17:M17)+ISNUMBER(I17:M17)*(I17:M17&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I17:M17&lt;&gt;"")*(I17:M17&gt;0)*(I17:M17*(1-Config!$B$8)&lt;E17))))</f>
         <v/>
       </c>
       <c r="P17" s="23" t="n"/>
       <c r="Q17" s="28" t="n"/>
       <c r="R17" s="26">
-        <f>IF(OR(A17="",AND(P17="",Q17="")),"",IF(OR(NOT(ISNUMBER(P17)),NOT(ISNUMBER(Q17))),"volume ou produção faltando",IF(P17=0,"",Q17/P17)))</f>
+        <f>IF(OR(A17="",AND(P17="",Q17="")),"",IF(OR(NOT(IF(ISNUMBER(P17),AND(P17&gt;=0),FALSE)),NOT(IF(ISNUMBER(Q17),AND(Q17&gt;=0),FALSE))),"volume ou produção faltando ou negativos",IF(P17=0,"",Q17/P17)))</f>
         <v/>
       </c>
       <c r="S17" s="31">
@@ -1975,17 +1975,17 @@
       <c r="L18" s="28" t="n"/>
       <c r="M18" s="28" t="n"/>
       <c r="N18" s="29">
-        <f>IF(OR(A18="",H18=""),"",IF(NOT(ISNUMBER(H18)),"Preço inválido",IF(NOT(ISNUMBER(E18)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F18)),NOT(ISNUMBER(G18))),"Margens inválidas",IF(H18=0,"Sem cobrança",IF(H18&lt;F18,"Abaixo do mínimo",IF(H18&lt;G18,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(OR(A18="",H18=""),"",IF(NOT(IF(ISNUMBER(H18),AND(H18&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(E18)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F18)),NOT(ISNUMBER(G18))),"Margens inválidas",IF(H18=0,"Sem cobrança",IF(H18&lt;F18,"Abaixo do mínimo",IF(H18&lt;G18,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v/>
       </c>
       <c r="O18" s="30">
-        <f>IF(OR(A18="",NOT(ISNUMBER(F18))),"",IF(SUMPRODUCT(ISTEXT(I18:M18)*1)&gt;0,"tabela com texto",SUMPRODUCT((I18:M18&lt;&gt;"")*(I18:M18&gt;0)*(I18:M18*(1-Config!$B$8)&lt;E18))))</f>
+        <f>IF(OR(A18="",NOT(ISNUMBER(F18))),"",IF(SUMPRODUCT(ISTEXT(I18:M18)+ISNUMBER(I18:M18)*(I18:M18&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I18:M18&lt;&gt;"")*(I18:M18&gt;0)*(I18:M18*(1-Config!$B$8)&lt;E18))))</f>
         <v/>
       </c>
       <c r="P18" s="23" t="n"/>
       <c r="Q18" s="28" t="n"/>
       <c r="R18" s="26">
-        <f>IF(OR(A18="",AND(P18="",Q18="")),"",IF(OR(NOT(ISNUMBER(P18)),NOT(ISNUMBER(Q18))),"volume ou produção faltando",IF(P18=0,"",Q18/P18)))</f>
+        <f>IF(OR(A18="",AND(P18="",Q18="")),"",IF(OR(NOT(IF(ISNUMBER(P18),AND(P18&gt;=0),FALSE)),NOT(IF(ISNUMBER(Q18),AND(Q18&gt;=0),FALSE))),"volume ou produção faltando ou negativos",IF(P18=0,"",Q18/P18)))</f>
         <v/>
       </c>
       <c r="S18" s="31">
@@ -2018,17 +2018,17 @@
       <c r="L19" s="28" t="n"/>
       <c r="M19" s="28" t="n"/>
       <c r="N19" s="29">
-        <f>IF(OR(A19="",H19=""),"",IF(NOT(ISNUMBER(H19)),"Preço inválido",IF(NOT(ISNUMBER(E19)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F19)),NOT(ISNUMBER(G19))),"Margens inválidas",IF(H19=0,"Sem cobrança",IF(H19&lt;F19,"Abaixo do mínimo",IF(H19&lt;G19,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(OR(A19="",H19=""),"",IF(NOT(IF(ISNUMBER(H19),AND(H19&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(E19)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F19)),NOT(ISNUMBER(G19))),"Margens inválidas",IF(H19=0,"Sem cobrança",IF(H19&lt;F19,"Abaixo do mínimo",IF(H19&lt;G19,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
         <v/>
       </c>
       <c r="O19" s="30">
-        <f>IF(OR(A19="",NOT(ISNUMBER(F19))),"",IF(SUMPRODUCT(ISTEXT(I19:M19)*1)&gt;0,"tabela com texto",SUMPRODUCT((I19:M19&lt;&gt;"")*(I19:M19&gt;0)*(I19:M19*(1-Config!$B$8)&lt;E19))))</f>
+        <f>IF(OR(A19="",NOT(ISNUMBER(F19))),"",IF(SUMPRODUCT(ISTEXT(I19:M19)+ISNUMBER(I19:M19)*(I19:M19&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I19:M19&lt;&gt;"")*(I19:M19&gt;0)*(I19:M19*(1-Config!$B$8)&lt;E19))))</f>
         <v/>
       </c>
       <c r="P19" s="23" t="n"/>
       <c r="Q19" s="28" t="n"/>
       <c r="R19" s="26">
-        <f>IF(OR(A19="",AND(P19="",Q19="")),"",IF(OR(NOT(ISNUMBER(P19)),NOT(ISNUMBER(Q19))),"volume ou produção faltando",IF(P19=0,"",Q19/P19)))</f>
+        <f>IF(OR(A19="",AND(P19="",Q19="")),"",IF(OR(NOT(IF(ISNUMBER(P19),AND(P19&gt;=0),FALSE)),NOT(IF(ISNUMBER(Q19),AND(Q19&gt;=0),FALSE))),"volume ou produção faltando ou negativos",IF(P19=0,"",Q19/P19)))</f>
         <v/>
       </c>
       <c r="S19" s="31">
@@ -2123,27 +2123,27 @@
         <v>38</v>
       </c>
       <c r="C27" s="36">
-        <f>IF(OR($A8="",H8="",NOT(ISNUMBER(H8)),NOT(ISNUMBER($B27)),N($B27)=0),"",H8/($B27/60))</f>
+        <f>IF(OR($A8="",H8="",NOT(IF(ISNUMBER(H8),AND(H8&gt;=0),FALSE)),NOT(ISNUMBER($B27)),N($B27)=0),"",H8/($B27/60))</f>
         <v>600</v>
       </c>
       <c r="D27" s="36">
-        <f>IF(OR($A8="",I8="",NOT(ISNUMBER(I8)),NOT(ISNUMBER($B27)),N($B27)=0),"",I8/($B27/60))</f>
+        <f>IF(OR($A8="",I8="",NOT(IF(ISNUMBER(I8),AND(I8&gt;=0),FALSE)),NOT(ISNUMBER($B27)),N($B27)=0),"",I8/($B27/60))</f>
         <v>189.473684210526</v>
       </c>
       <c r="E27" s="36">
-        <f>IF(OR($A8="",J8="",NOT(ISNUMBER(J8)),NOT(ISNUMBER($B27)),N($B27)=0),"",J8/($B27/60))</f>
+        <f>IF(OR($A8="",J8="",NOT(IF(ISNUMBER(J8),AND(J8&gt;=0),FALSE)),NOT(ISNUMBER($B27)),N($B27)=0),"",J8/($B27/60))</f>
         <v>157.894736842105</v>
       </c>
       <c r="F27" s="36">
-        <f>IF(OR($A8="",K8="",NOT(ISNUMBER(K8)),NOT(ISNUMBER($B27)),N($B27)=0),"",K8/($B27/60))</f>
+        <f>IF(OR($A8="",K8="",NOT(IF(ISNUMBER(K8),AND(K8&gt;=0),FALSE)),NOT(ISNUMBER($B27)),N($B27)=0),"",K8/($B27/60))</f>
         <v>142.105263157895</v>
       </c>
       <c r="G27" s="36">
-        <f>IF(OR($A8="",L8="",NOT(ISNUMBER(L8)),NOT(ISNUMBER($B27)),N($B27)=0),"",L8/($B27/60))</f>
+        <f>IF(OR($A8="",L8="",NOT(IF(ISNUMBER(L8),AND(L8&gt;=0),FALSE)),NOT(ISNUMBER($B27)),N($B27)=0),"",L8/($B27/60))</f>
         <v/>
       </c>
       <c r="H27" s="36">
-        <f>IF(OR($A8="",M8="",NOT(ISNUMBER(M8)),NOT(ISNUMBER($B27)),N($B27)=0),"",M8/($B27/60))</f>
+        <f>IF(OR($A8="",M8="",NOT(IF(ISNUMBER(M8),AND(M8&gt;=0),FALSE)),NOT(ISNUMBER($B27)),N($B27)=0),"",M8/($B27/60))</f>
         <v/>
       </c>
       <c r="I27" s="36">
@@ -2165,27 +2165,27 @@
         <v>20</v>
       </c>
       <c r="C28" s="36">
-        <f>IF(OR($A9="",H9="",NOT(ISNUMBER(H9)),NOT(ISNUMBER($B28)),N($B28)=0),"",H9/($B28/60))</f>
+        <f>IF(OR($A9="",H9="",NOT(IF(ISNUMBER(H9),AND(H9&gt;=0),FALSE)),NOT(ISNUMBER($B28)),N($B28)=0),"",H9/($B28/60))</f>
         <v>0</v>
       </c>
       <c r="D28" s="36">
-        <f>IF(OR($A9="",I9="",NOT(ISNUMBER(I9)),NOT(ISNUMBER($B28)),N($B28)=0),"",I9/($B28/60))</f>
+        <f>IF(OR($A9="",I9="",NOT(IF(ISNUMBER(I9),AND(I9&gt;=0),FALSE)),NOT(ISNUMBER($B28)),N($B28)=0),"",I9/($B28/60))</f>
         <v>0</v>
       </c>
       <c r="E28" s="36">
-        <f>IF(OR($A9="",J9="",NOT(ISNUMBER(J9)),NOT(ISNUMBER($B28)),N($B28)=0),"",J9/($B28/60))</f>
+        <f>IF(OR($A9="",J9="",NOT(IF(ISNUMBER(J9),AND(J9&gt;=0),FALSE)),NOT(ISNUMBER($B28)),N($B28)=0),"",J9/($B28/60))</f>
         <v>0</v>
       </c>
       <c r="F28" s="36">
-        <f>IF(OR($A9="",K9="",NOT(ISNUMBER(K9)),NOT(ISNUMBER($B28)),N($B28)=0),"",K9/($B28/60))</f>
+        <f>IF(OR($A9="",K9="",NOT(IF(ISNUMBER(K9),AND(K9&gt;=0),FALSE)),NOT(ISNUMBER($B28)),N($B28)=0),"",K9/($B28/60))</f>
         <v>0</v>
       </c>
       <c r="G28" s="36">
-        <f>IF(OR($A9="",L9="",NOT(ISNUMBER(L9)),NOT(ISNUMBER($B28)),N($B28)=0),"",L9/($B28/60))</f>
+        <f>IF(OR($A9="",L9="",NOT(IF(ISNUMBER(L9),AND(L9&gt;=0),FALSE)),NOT(ISNUMBER($B28)),N($B28)=0),"",L9/($B28/60))</f>
         <v/>
       </c>
       <c r="H28" s="36">
-        <f>IF(OR($A9="",M9="",NOT(ISNUMBER(M9)),NOT(ISNUMBER($B28)),N($B28)=0),"",M9/($B28/60))</f>
+        <f>IF(OR($A9="",M9="",NOT(IF(ISNUMBER(M9),AND(M9&gt;=0),FALSE)),NOT(ISNUMBER($B28)),N($B28)=0),"",M9/($B28/60))</f>
         <v/>
       </c>
       <c r="I28" s="36">
@@ -2207,27 +2207,27 @@
         <v>20</v>
       </c>
       <c r="C29" s="36">
-        <f>IF(OR($A10="",H10="",NOT(ISNUMBER(H10)),NOT(ISNUMBER($B29)),N($B29)=0),"",H10/($B29/60))</f>
+        <f>IF(OR($A10="",H10="",NOT(IF(ISNUMBER(H10),AND(H10&gt;=0),FALSE)),NOT(ISNUMBER($B29)),N($B29)=0),"",H10/($B29/60))</f>
         <v>390</v>
       </c>
       <c r="D29" s="36">
-        <f>IF(OR($A10="",I10="",NOT(ISNUMBER(I10)),NOT(ISNUMBER($B29)),N($B29)=0),"",I10/($B29/60))</f>
+        <f>IF(OR($A10="",I10="",NOT(IF(ISNUMBER(I10),AND(I10&gt;=0),FALSE)),NOT(ISNUMBER($B29)),N($B29)=0),"",I10/($B29/60))</f>
         <v>120</v>
       </c>
       <c r="E29" s="36">
-        <f>IF(OR($A10="",J10="",NOT(ISNUMBER(J10)),NOT(ISNUMBER($B29)),N($B29)=0),"",J10/($B29/60))</f>
+        <f>IF(OR($A10="",J10="",NOT(IF(ISNUMBER(J10),AND(J10&gt;=0),FALSE)),NOT(ISNUMBER($B29)),N($B29)=0),"",J10/($B29/60))</f>
         <v>105</v>
       </c>
       <c r="F29" s="36">
-        <f>IF(OR($A10="",K10="",NOT(ISNUMBER(K10)),NOT(ISNUMBER($B29)),N($B29)=0),"",K10/($B29/60))</f>
+        <f>IF(OR($A10="",K10="",NOT(IF(ISNUMBER(K10),AND(K10&gt;=0),FALSE)),NOT(ISNUMBER($B29)),N($B29)=0),"",K10/($B29/60))</f>
         <v>96</v>
       </c>
       <c r="G29" s="36">
-        <f>IF(OR($A10="",L10="",NOT(ISNUMBER(L10)),NOT(ISNUMBER($B29)),N($B29)=0),"",L10/($B29/60))</f>
+        <f>IF(OR($A10="",L10="",NOT(IF(ISNUMBER(L10),AND(L10&gt;=0),FALSE)),NOT(ISNUMBER($B29)),N($B29)=0),"",L10/($B29/60))</f>
         <v/>
       </c>
       <c r="H29" s="36">
-        <f>IF(OR($A10="",M10="",NOT(ISNUMBER(M10)),NOT(ISNUMBER($B29)),N($B29)=0),"",M10/($B29/60))</f>
+        <f>IF(OR($A10="",M10="",NOT(IF(ISNUMBER(M10),AND(M10&gt;=0),FALSE)),NOT(ISNUMBER($B29)),N($B29)=0),"",M10/($B29/60))</f>
         <v/>
       </c>
       <c r="I29" s="36">
@@ -2249,27 +2249,27 @@
         <v>20</v>
       </c>
       <c r="C30" s="36">
-        <f>IF(OR($A11="",H11="",NOT(ISNUMBER(H11)),NOT(ISNUMBER($B30)),N($B30)=0),"",H11/($B30/60))</f>
+        <f>IF(OR($A11="",H11="",NOT(IF(ISNUMBER(H11),AND(H11&gt;=0),FALSE)),NOT(ISNUMBER($B30)),N($B30)=0),"",H11/($B30/60))</f>
         <v>900</v>
       </c>
       <c r="D30" s="36">
-        <f>IF(OR($A11="",I11="",NOT(ISNUMBER(I11)),NOT(ISNUMBER($B30)),N($B30)=0),"",I11/($B30/60))</f>
+        <f>IF(OR($A11="",I11="",NOT(IF(ISNUMBER(I11),AND(I11&gt;=0),FALSE)),NOT(ISNUMBER($B30)),N($B30)=0),"",I11/($B30/60))</f>
         <v>285</v>
       </c>
       <c r="E30" s="36">
-        <f>IF(OR($A11="",J11="",NOT(ISNUMBER(J11)),NOT(ISNUMBER($B30)),N($B30)=0),"",J11/($B30/60))</f>
+        <f>IF(OR($A11="",J11="",NOT(IF(ISNUMBER(J11),AND(J11&gt;=0),FALSE)),NOT(ISNUMBER($B30)),N($B30)=0),"",J11/($B30/60))</f>
         <v>255</v>
       </c>
       <c r="F30" s="36">
-        <f>IF(OR($A11="",K11="",NOT(ISNUMBER(K11)),NOT(ISNUMBER($B30)),N($B30)=0),"",K11/($B30/60))</f>
+        <f>IF(OR($A11="",K11="",NOT(IF(ISNUMBER(K11),AND(K11&gt;=0),FALSE)),NOT(ISNUMBER($B30)),N($B30)=0),"",K11/($B30/60))</f>
         <v>225</v>
       </c>
       <c r="G30" s="36">
-        <f>IF(OR($A11="",L11="",NOT(ISNUMBER(L11)),NOT(ISNUMBER($B30)),N($B30)=0),"",L11/($B30/60))</f>
+        <f>IF(OR($A11="",L11="",NOT(IF(ISNUMBER(L11),AND(L11&gt;=0),FALSE)),NOT(ISNUMBER($B30)),N($B30)=0),"",L11/($B30/60))</f>
         <v/>
       </c>
       <c r="H30" s="36">
-        <f>IF(OR($A11="",M11="",NOT(ISNUMBER(M11)),NOT(ISNUMBER($B30)),N($B30)=0),"",M11/($B30/60))</f>
+        <f>IF(OR($A11="",M11="",NOT(IF(ISNUMBER(M11),AND(M11&gt;=0),FALSE)),NOT(ISNUMBER($B30)),N($B30)=0),"",M11/($B30/60))</f>
         <v/>
       </c>
       <c r="I30" s="36">
@@ -2291,27 +2291,27 @@
         <v>20</v>
       </c>
       <c r="C31" s="36">
-        <f>IF(OR($A12="",H12="",NOT(ISNUMBER(H12)),NOT(ISNUMBER($B31)),N($B31)=0),"",H12/($B31/60))</f>
+        <f>IF(OR($A12="",H12="",NOT(IF(ISNUMBER(H12),AND(H12&gt;=0),FALSE)),NOT(ISNUMBER($B31)),N($B31)=0),"",H12/($B31/60))</f>
         <v>1050</v>
       </c>
       <c r="D31" s="36">
-        <f>IF(OR($A12="",I12="",NOT(ISNUMBER(I12)),NOT(ISNUMBER($B31)),N($B31)=0),"",I12/($B31/60))</f>
+        <f>IF(OR($A12="",I12="",NOT(IF(ISNUMBER(I12),AND(I12&gt;=0),FALSE)),NOT(ISNUMBER($B31)),N($B31)=0),"",I12/($B31/60))</f>
         <v>315</v>
       </c>
       <c r="E31" s="36">
-        <f>IF(OR($A12="",J12="",NOT(ISNUMBER(J12)),NOT(ISNUMBER($B31)),N($B31)=0),"",J12/($B31/60))</f>
+        <f>IF(OR($A12="",J12="",NOT(IF(ISNUMBER(J12),AND(J12&gt;=0),FALSE)),NOT(ISNUMBER($B31)),N($B31)=0),"",J12/($B31/60))</f>
         <v>285</v>
       </c>
       <c r="F31" s="36">
-        <f>IF(OR($A12="",K12="",NOT(ISNUMBER(K12)),NOT(ISNUMBER($B31)),N($B31)=0),"",K12/($B31/60))</f>
+        <f>IF(OR($A12="",K12="",NOT(IF(ISNUMBER(K12),AND(K12&gt;=0),FALSE)),NOT(ISNUMBER($B31)),N($B31)=0),"",K12/($B31/60))</f>
         <v>255</v>
       </c>
       <c r="G31" s="36">
-        <f>IF(OR($A12="",L12="",NOT(ISNUMBER(L12)),NOT(ISNUMBER($B31)),N($B31)=0),"",L12/($B31/60))</f>
+        <f>IF(OR($A12="",L12="",NOT(IF(ISNUMBER(L12),AND(L12&gt;=0),FALSE)),NOT(ISNUMBER($B31)),N($B31)=0),"",L12/($B31/60))</f>
         <v/>
       </c>
       <c r="H31" s="36">
-        <f>IF(OR($A12="",M12="",NOT(ISNUMBER(M12)),NOT(ISNUMBER($B31)),N($B31)=0),"",M12/($B31/60))</f>
+        <f>IF(OR($A12="",M12="",NOT(IF(ISNUMBER(M12),AND(M12&gt;=0),FALSE)),NOT(ISNUMBER($B31)),N($B31)=0),"",M12/($B31/60))</f>
         <v/>
       </c>
       <c r="I31" s="36">
@@ -2333,27 +2333,27 @@
         <v>40</v>
       </c>
       <c r="C32" s="36">
-        <f>IF(OR($A13="",H13="",NOT(ISNUMBER(H13)),NOT(ISNUMBER($B32)),N($B32)=0),"",H13/($B32/60))</f>
+        <f>IF(OR($A13="",H13="",NOT(IF(ISNUMBER(H13),AND(H13&gt;=0),FALSE)),NOT(ISNUMBER($B32)),N($B32)=0),"",H13/($B32/60))</f>
         <v>675</v>
       </c>
       <c r="D32" s="36">
-        <f>IF(OR($A13="",I13="",NOT(ISNUMBER(I13)),NOT(ISNUMBER($B32)),N($B32)=0),"",I13/($B32/60))</f>
+        <f>IF(OR($A13="",I13="",NOT(IF(ISNUMBER(I13),AND(I13&gt;=0),FALSE)),NOT(ISNUMBER($B32)),N($B32)=0),"",I13/($B32/60))</f>
         <v>210</v>
       </c>
       <c r="E32" s="36">
-        <f>IF(OR($A13="",J13="",NOT(ISNUMBER(J13)),NOT(ISNUMBER($B32)),N($B32)=0),"",J13/($B32/60))</f>
+        <f>IF(OR($A13="",J13="",NOT(IF(ISNUMBER(J13),AND(J13&gt;=0),FALSE)),NOT(ISNUMBER($B32)),N($B32)=0),"",J13/($B32/60))</f>
         <v>187.5</v>
       </c>
       <c r="F32" s="36">
-        <f>IF(OR($A13="",K13="",NOT(ISNUMBER(K13)),NOT(ISNUMBER($B32)),N($B32)=0),"",K13/($B32/60))</f>
+        <f>IF(OR($A13="",K13="",NOT(IF(ISNUMBER(K13),AND(K13&gt;=0),FALSE)),NOT(ISNUMBER($B32)),N($B32)=0),"",K13/($B32/60))</f>
         <v>165</v>
       </c>
       <c r="G32" s="36">
-        <f>IF(OR($A13="",L13="",NOT(ISNUMBER(L13)),NOT(ISNUMBER($B32)),N($B32)=0),"",L13/($B32/60))</f>
+        <f>IF(OR($A13="",L13="",NOT(IF(ISNUMBER(L13),AND(L13&gt;=0),FALSE)),NOT(ISNUMBER($B32)),N($B32)=0),"",L13/($B32/60))</f>
         <v/>
       </c>
       <c r="H32" s="36">
-        <f>IF(OR($A13="",M13="",NOT(ISNUMBER(M13)),NOT(ISNUMBER($B32)),N($B32)=0),"",M13/($B32/60))</f>
+        <f>IF(OR($A13="",M13="",NOT(IF(ISNUMBER(M13),AND(M13&gt;=0),FALSE)),NOT(ISNUMBER($B32)),N($B32)=0),"",M13/($B32/60))</f>
         <v/>
       </c>
       <c r="I32" s="36">
@@ -2375,27 +2375,27 @@
         <v>48</v>
       </c>
       <c r="C33" s="36">
-        <f>IF(OR($A14="",H14="",NOT(ISNUMBER(H14)),NOT(ISNUMBER($B33)),N($B33)=0),"",H14/($B33/60))</f>
+        <f>IF(OR($A14="",H14="",NOT(IF(ISNUMBER(H14),AND(H14&gt;=0),FALSE)),NOT(ISNUMBER($B33)),N($B33)=0),"",H14/($B33/60))</f>
         <v>500</v>
       </c>
       <c r="D33" s="36">
-        <f>IF(OR($A14="",I14="",NOT(ISNUMBER(I14)),NOT(ISNUMBER($B33)),N($B33)=0),"",I14/($B33/60))</f>
+        <f>IF(OR($A14="",I14="",NOT(IF(ISNUMBER(I14),AND(I14&gt;=0),FALSE)),NOT(ISNUMBER($B33)),N($B33)=0),"",I14/($B33/60))</f>
         <v>162.5</v>
       </c>
       <c r="E33" s="36">
-        <f>IF(OR($A14="",J14="",NOT(ISNUMBER(J14)),NOT(ISNUMBER($B33)),N($B33)=0),"",J14/($B33/60))</f>
+        <f>IF(OR($A14="",J14="",NOT(IF(ISNUMBER(J14),AND(J14&gt;=0),FALSE)),NOT(ISNUMBER($B33)),N($B33)=0),"",J14/($B33/60))</f>
         <v/>
       </c>
       <c r="F33" s="36">
-        <f>IF(OR($A14="",K14="",NOT(ISNUMBER(K14)),NOT(ISNUMBER($B33)),N($B33)=0),"",K14/($B33/60))</f>
+        <f>IF(OR($A14="",K14="",NOT(IF(ISNUMBER(K14),AND(K14&gt;=0),FALSE)),NOT(ISNUMBER($B33)),N($B33)=0),"",K14/($B33/60))</f>
         <v/>
       </c>
       <c r="G33" s="36">
-        <f>IF(OR($A14="",L14="",NOT(ISNUMBER(L14)),NOT(ISNUMBER($B33)),N($B33)=0),"",L14/($B33/60))</f>
+        <f>IF(OR($A14="",L14="",NOT(IF(ISNUMBER(L14),AND(L14&gt;=0),FALSE)),NOT(ISNUMBER($B33)),N($B33)=0),"",L14/($B33/60))</f>
         <v/>
       </c>
       <c r="H33" s="36">
-        <f>IF(OR($A14="",M14="",NOT(ISNUMBER(M14)),NOT(ISNUMBER($B33)),N($B33)=0),"",M14/($B33/60))</f>
+        <f>IF(OR($A14="",M14="",NOT(IF(ISNUMBER(M14),AND(M14&gt;=0),FALSE)),NOT(ISNUMBER($B33)),N($B33)=0),"",M14/($B33/60))</f>
         <v/>
       </c>
       <c r="I33" s="36">
@@ -2417,27 +2417,27 @@
         <v/>
       </c>
       <c r="C34" s="36">
-        <f>IF(OR($A15="",H15="",NOT(ISNUMBER(H15)),NOT(ISNUMBER($B34)),N($B34)=0),"",H15/($B34/60))</f>
+        <f>IF(OR($A15="",H15="",NOT(IF(ISNUMBER(H15),AND(H15&gt;=0),FALSE)),NOT(ISNUMBER($B34)),N($B34)=0),"",H15/($B34/60))</f>
         <v/>
       </c>
       <c r="D34" s="36">
-        <f>IF(OR($A15="",I15="",NOT(ISNUMBER(I15)),NOT(ISNUMBER($B34)),N($B34)=0),"",I15/($B34/60))</f>
+        <f>IF(OR($A15="",I15="",NOT(IF(ISNUMBER(I15),AND(I15&gt;=0),FALSE)),NOT(ISNUMBER($B34)),N($B34)=0),"",I15/($B34/60))</f>
         <v/>
       </c>
       <c r="E34" s="36">
-        <f>IF(OR($A15="",J15="",NOT(ISNUMBER(J15)),NOT(ISNUMBER($B34)),N($B34)=0),"",J15/($B34/60))</f>
+        <f>IF(OR($A15="",J15="",NOT(IF(ISNUMBER(J15),AND(J15&gt;=0),FALSE)),NOT(ISNUMBER($B34)),N($B34)=0),"",J15/($B34/60))</f>
         <v/>
       </c>
       <c r="F34" s="36">
-        <f>IF(OR($A15="",K15="",NOT(ISNUMBER(K15)),NOT(ISNUMBER($B34)),N($B34)=0),"",K15/($B34/60))</f>
+        <f>IF(OR($A15="",K15="",NOT(IF(ISNUMBER(K15),AND(K15&gt;=0),FALSE)),NOT(ISNUMBER($B34)),N($B34)=0),"",K15/($B34/60))</f>
         <v/>
       </c>
       <c r="G34" s="36">
-        <f>IF(OR($A15="",L15="",NOT(ISNUMBER(L15)),NOT(ISNUMBER($B34)),N($B34)=0),"",L15/($B34/60))</f>
+        <f>IF(OR($A15="",L15="",NOT(IF(ISNUMBER(L15),AND(L15&gt;=0),FALSE)),NOT(ISNUMBER($B34)),N($B34)=0),"",L15/($B34/60))</f>
         <v/>
       </c>
       <c r="H34" s="36">
-        <f>IF(OR($A15="",M15="",NOT(ISNUMBER(M15)),NOT(ISNUMBER($B34)),N($B34)=0),"",M15/($B34/60))</f>
+        <f>IF(OR($A15="",M15="",NOT(IF(ISNUMBER(M15),AND(M15&gt;=0),FALSE)),NOT(ISNUMBER($B34)),N($B34)=0),"",M15/($B34/60))</f>
         <v/>
       </c>
       <c r="I34" s="36">
@@ -2459,27 +2459,27 @@
         <v/>
       </c>
       <c r="C35" s="36">
-        <f>IF(OR($A16="",H16="",NOT(ISNUMBER(H16)),NOT(ISNUMBER($B35)),N($B35)=0),"",H16/($B35/60))</f>
+        <f>IF(OR($A16="",H16="",NOT(IF(ISNUMBER(H16),AND(H16&gt;=0),FALSE)),NOT(ISNUMBER($B35)),N($B35)=0),"",H16/($B35/60))</f>
         <v/>
       </c>
       <c r="D35" s="36">
-        <f>IF(OR($A16="",I16="",NOT(ISNUMBER(I16)),NOT(ISNUMBER($B35)),N($B35)=0),"",I16/($B35/60))</f>
+        <f>IF(OR($A16="",I16="",NOT(IF(ISNUMBER(I16),AND(I16&gt;=0),FALSE)),NOT(ISNUMBER($B35)),N($B35)=0),"",I16/($B35/60))</f>
         <v/>
       </c>
       <c r="E35" s="36">
-        <f>IF(OR($A16="",J16="",NOT(ISNUMBER(J16)),NOT(ISNUMBER($B35)),N($B35)=0),"",J16/($B35/60))</f>
+        <f>IF(OR($A16="",J16="",NOT(IF(ISNUMBER(J16),AND(J16&gt;=0),FALSE)),NOT(ISNUMBER($B35)),N($B35)=0),"",J16/($B35/60))</f>
         <v/>
       </c>
       <c r="F35" s="36">
-        <f>IF(OR($A16="",K16="",NOT(ISNUMBER(K16)),NOT(ISNUMBER($B35)),N($B35)=0),"",K16/($B35/60))</f>
+        <f>IF(OR($A16="",K16="",NOT(IF(ISNUMBER(K16),AND(K16&gt;=0),FALSE)),NOT(ISNUMBER($B35)),N($B35)=0),"",K16/($B35/60))</f>
         <v/>
       </c>
       <c r="G35" s="36">
-        <f>IF(OR($A16="",L16="",NOT(ISNUMBER(L16)),NOT(ISNUMBER($B35)),N($B35)=0),"",L16/($B35/60))</f>
+        <f>IF(OR($A16="",L16="",NOT(IF(ISNUMBER(L16),AND(L16&gt;=0),FALSE)),NOT(ISNUMBER($B35)),N($B35)=0),"",L16/($B35/60))</f>
         <v/>
       </c>
       <c r="H35" s="36">
-        <f>IF(OR($A16="",M16="",NOT(ISNUMBER(M16)),NOT(ISNUMBER($B35)),N($B35)=0),"",M16/($B35/60))</f>
+        <f>IF(OR($A16="",M16="",NOT(IF(ISNUMBER(M16),AND(M16&gt;=0),FALSE)),NOT(ISNUMBER($B35)),N($B35)=0),"",M16/($B35/60))</f>
         <v/>
       </c>
       <c r="I35" s="36">
@@ -2501,27 +2501,27 @@
         <v/>
       </c>
       <c r="C36" s="36">
-        <f>IF(OR($A17="",H17="",NOT(ISNUMBER(H17)),NOT(ISNUMBER($B36)),N($B36)=0),"",H17/($B36/60))</f>
+        <f>IF(OR($A17="",H17="",NOT(IF(ISNUMBER(H17),AND(H17&gt;=0),FALSE)),NOT(ISNUMBER($B36)),N($B36)=0),"",H17/($B36/60))</f>
         <v/>
       </c>
       <c r="D36" s="36">
-        <f>IF(OR($A17="",I17="",NOT(ISNUMBER(I17)),NOT(ISNUMBER($B36)),N($B36)=0),"",I17/($B36/60))</f>
+        <f>IF(OR($A17="",I17="",NOT(IF(ISNUMBER(I17),AND(I17&gt;=0),FALSE)),NOT(ISNUMBER($B36)),N($B36)=0),"",I17/($B36/60))</f>
         <v/>
       </c>
       <c r="E36" s="36">
-        <f>IF(OR($A17="",J17="",NOT(ISNUMBER(J17)),NOT(ISNUMBER($B36)),N($B36)=0),"",J17/($B36/60))</f>
+        <f>IF(OR($A17="",J17="",NOT(IF(ISNUMBER(J17),AND(J17&gt;=0),FALSE)),NOT(ISNUMBER($B36)),N($B36)=0),"",J17/($B36/60))</f>
         <v/>
       </c>
       <c r="F36" s="36">
-        <f>IF(OR($A17="",K17="",NOT(ISNUMBER(K17)),NOT(ISNUMBER($B36)),N($B36)=0),"",K17/($B36/60))</f>
+        <f>IF(OR($A17="",K17="",NOT(IF(ISNUMBER(K17),AND(K17&gt;=0),FALSE)),NOT(ISNUMBER($B36)),N($B36)=0),"",K17/($B36/60))</f>
         <v/>
       </c>
       <c r="G36" s="36">
-        <f>IF(OR($A17="",L17="",NOT(ISNUMBER(L17)),NOT(ISNUMBER($B36)),N($B36)=0),"",L17/($B36/60))</f>
+        <f>IF(OR($A17="",L17="",NOT(IF(ISNUMBER(L17),AND(L17&gt;=0),FALSE)),NOT(ISNUMBER($B36)),N($B36)=0),"",L17/($B36/60))</f>
         <v/>
       </c>
       <c r="H36" s="36">
-        <f>IF(OR($A17="",M17="",NOT(ISNUMBER(M17)),NOT(ISNUMBER($B36)),N($B36)=0),"",M17/($B36/60))</f>
+        <f>IF(OR($A17="",M17="",NOT(IF(ISNUMBER(M17),AND(M17&gt;=0),FALSE)),NOT(ISNUMBER($B36)),N($B36)=0),"",M17/($B36/60))</f>
         <v/>
       </c>
       <c r="I36" s="36">
@@ -2543,27 +2543,27 @@
         <v/>
       </c>
       <c r="C37" s="36">
-        <f>IF(OR($A18="",H18="",NOT(ISNUMBER(H18)),NOT(ISNUMBER($B37)),N($B37)=0),"",H18/($B37/60))</f>
+        <f>IF(OR($A18="",H18="",NOT(IF(ISNUMBER(H18),AND(H18&gt;=0),FALSE)),NOT(ISNUMBER($B37)),N($B37)=0),"",H18/($B37/60))</f>
         <v/>
       </c>
       <c r="D37" s="36">
-        <f>IF(OR($A18="",I18="",NOT(ISNUMBER(I18)),NOT(ISNUMBER($B37)),N($B37)=0),"",I18/($B37/60))</f>
+        <f>IF(OR($A18="",I18="",NOT(IF(ISNUMBER(I18),AND(I18&gt;=0),FALSE)),NOT(ISNUMBER($B37)),N($B37)=0),"",I18/($B37/60))</f>
         <v/>
       </c>
       <c r="E37" s="36">
-        <f>IF(OR($A18="",J18="",NOT(ISNUMBER(J18)),NOT(ISNUMBER($B37)),N($B37)=0),"",J18/($B37/60))</f>
+        <f>IF(OR($A18="",J18="",NOT(IF(ISNUMBER(J18),AND(J18&gt;=0),FALSE)),NOT(ISNUMBER($B37)),N($B37)=0),"",J18/($B37/60))</f>
         <v/>
       </c>
       <c r="F37" s="36">
-        <f>IF(OR($A18="",K18="",NOT(ISNUMBER(K18)),NOT(ISNUMBER($B37)),N($B37)=0),"",K18/($B37/60))</f>
+        <f>IF(OR($A18="",K18="",NOT(IF(ISNUMBER(K18),AND(K18&gt;=0),FALSE)),NOT(ISNUMBER($B37)),N($B37)=0),"",K18/($B37/60))</f>
         <v/>
       </c>
       <c r="G37" s="36">
-        <f>IF(OR($A18="",L18="",NOT(ISNUMBER(L18)),NOT(ISNUMBER($B37)),N($B37)=0),"",L18/($B37/60))</f>
+        <f>IF(OR($A18="",L18="",NOT(IF(ISNUMBER(L18),AND(L18&gt;=0),FALSE)),NOT(ISNUMBER($B37)),N($B37)=0),"",L18/($B37/60))</f>
         <v/>
       </c>
       <c r="H37" s="36">
-        <f>IF(OR($A18="",M18="",NOT(ISNUMBER(M18)),NOT(ISNUMBER($B37)),N($B37)=0),"",M18/($B37/60))</f>
+        <f>IF(OR($A18="",M18="",NOT(IF(ISNUMBER(M18),AND(M18&gt;=0),FALSE)),NOT(ISNUMBER($B37)),N($B37)=0),"",M18/($B37/60))</f>
         <v/>
       </c>
       <c r="I37" s="36">
@@ -2585,27 +2585,27 @@
         <v/>
       </c>
       <c r="C38" s="36">
-        <f>IF(OR($A19="",H19="",NOT(ISNUMBER(H19)),NOT(ISNUMBER($B38)),N($B38)=0),"",H19/($B38/60))</f>
+        <f>IF(OR($A19="",H19="",NOT(IF(ISNUMBER(H19),AND(H19&gt;=0),FALSE)),NOT(ISNUMBER($B38)),N($B38)=0),"",H19/($B38/60))</f>
         <v/>
       </c>
       <c r="D38" s="36">
-        <f>IF(OR($A19="",I19="",NOT(ISNUMBER(I19)),NOT(ISNUMBER($B38)),N($B38)=0),"",I19/($B38/60))</f>
+        <f>IF(OR($A19="",I19="",NOT(IF(ISNUMBER(I19),AND(I19&gt;=0),FALSE)),NOT(ISNUMBER($B38)),N($B38)=0),"",I19/($B38/60))</f>
         <v/>
       </c>
       <c r="E38" s="36">
-        <f>IF(OR($A19="",J19="",NOT(ISNUMBER(J19)),NOT(ISNUMBER($B38)),N($B38)=0),"",J19/($B38/60))</f>
+        <f>IF(OR($A19="",J19="",NOT(IF(ISNUMBER(J19),AND(J19&gt;=0),FALSE)),NOT(ISNUMBER($B38)),N($B38)=0),"",J19/($B38/60))</f>
         <v/>
       </c>
       <c r="F38" s="36">
-        <f>IF(OR($A19="",K19="",NOT(ISNUMBER(K19)),NOT(ISNUMBER($B38)),N($B38)=0),"",K19/($B38/60))</f>
+        <f>IF(OR($A19="",K19="",NOT(IF(ISNUMBER(K19),AND(K19&gt;=0),FALSE)),NOT(ISNUMBER($B38)),N($B38)=0),"",K19/($B38/60))</f>
         <v/>
       </c>
       <c r="G38" s="36">
-        <f>IF(OR($A19="",L19="",NOT(ISNUMBER(L19)),NOT(ISNUMBER($B38)),N($B38)=0),"",L19/($B38/60))</f>
+        <f>IF(OR($A19="",L19="",NOT(IF(ISNUMBER(L19),AND(L19&gt;=0),FALSE)),NOT(ISNUMBER($B38)),N($B38)=0),"",L19/($B38/60))</f>
         <v/>
       </c>
       <c r="H38" s="36">
-        <f>IF(OR($A19="",M19="",NOT(ISNUMBER(M19)),NOT(ISNUMBER($B38)),N($B38)=0),"",M19/($B38/60))</f>
+        <f>IF(OR($A19="",M19="",NOT(IF(ISNUMBER(M19),AND(M19&gt;=0),FALSE)),NOT(ISNUMBER($B38)),N($B38)=0),"",M19/($B38/60))</f>
         <v/>
       </c>
       <c r="I38" s="36">

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/08-tabela-de-precos.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/08-tabela-de-precos.xlsx
@@ -1235,12 +1235,12 @@
       </c>
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="16" t="str">
-        <f>IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF((SUMPRODUCT(($A$8:$A$19&lt;&gt;"")*(ISNUMBER($F$8:$F$19)=FALSE))+SUMPRODUCT(ISTEXT($H$8:$M$19)+ISNUMBER($H$8:$M$19)*($H$8:$M$19&lt;0))+SUMPRODUCT(($A$8:$A$19="")*(($B$8:$B$19&lt;&gt;"")+($C$8:$C$19&lt;&gt;"")+($D$8:$D$19&lt;&gt;"")+($H$8:$H$19&lt;&gt;"")+($I$8:$I$19&lt;&gt;"")+($J$8:$J$19&lt;&gt;"")+($K$8:$K$19&lt;&gt;"")+($L$8:$L$19&lt;&gt;"")+($M$8:$M$19&lt;&gt;"")+($P$8:$P$19&lt;&gt;"")+($Q$8:$Q$19&lt;&gt;"")&gt;0)))&gt;0,(SUMPRODUCT(($A$8:$A$19&lt;&gt;"")*(ISNUMBER($F$8:$F$19)=FALSE))+SUMPRODUCT(ISTEXT($H$8:$M$19)+ISNUMBER($H$8:$M$19)*($H$8:$M$19&lt;0))+SUMPRODUCT(($A$8:$A$19="")*(($B$8:$B$19&lt;&gt;"")+($C$8:$C$19&lt;&gt;"")+($D$8:$D$19&lt;&gt;"")+($H$8:$H$19&lt;&gt;"")+($I$8:$I$19&lt;&gt;"")+($J$8:$J$19&lt;&gt;"")+($K$8:$K$19&lt;&gt;"")+($L$8:$L$19&lt;&gt;"")+($M$8:$M$19&lt;&gt;"")+($P$8:$P$19&lt;&gt;"")+($Q$8:$Q$19&lt;&gt;"")&gt;0)))&amp;" linha(s) ou preço(s) incompletos",COUNTIF($N$8:$N$19,"Abaixo do mínimo")&amp;" de "&amp;COUNTA($A$8:$A$19)))</f>
+        <f>IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF((SUMPRODUCT(($A$8:$A$19&lt;&gt;"")*(ISNUMBER($F$8:$F$19)=FALSE))+SUMPRODUCT(($A$8:$A$19&lt;&gt;"")*($H$8:$H$19=""))+SUMPRODUCT(ISTEXT($H$8:$M$19)+ISNUMBER($H$8:$M$19)*($H$8:$M$19&lt;0))+SUMPRODUCT(($A$8:$A$19="")*(($B$8:$B$19&lt;&gt;"")+($C$8:$C$19&lt;&gt;"")+($D$8:$D$19&lt;&gt;"")+($H$8:$H$19&lt;&gt;"")+($I$8:$I$19&lt;&gt;"")+($J$8:$J$19&lt;&gt;"")+($K$8:$K$19&lt;&gt;"")+($L$8:$L$19&lt;&gt;"")+($M$8:$M$19&lt;&gt;"")+($P$8:$P$19&lt;&gt;"")+($Q$8:$Q$19&lt;&gt;"")&gt;0)))&gt;0,(SUMPRODUCT(($A$8:$A$19&lt;&gt;"")*(ISNUMBER($F$8:$F$19)=FALSE))+SUMPRODUCT(($A$8:$A$19&lt;&gt;"")*($H$8:$H$19=""))+SUMPRODUCT(ISTEXT($H$8:$M$19)+ISNUMBER($H$8:$M$19)*($H$8:$M$19&lt;0))+SUMPRODUCT(($A$8:$A$19="")*(($B$8:$B$19&lt;&gt;"")+($C$8:$C$19&lt;&gt;"")+($D$8:$D$19&lt;&gt;"")+($H$8:$H$19&lt;&gt;"")+($I$8:$I$19&lt;&gt;"")+($J$8:$J$19&lt;&gt;"")+($K$8:$K$19&lt;&gt;"")+($L$8:$L$19&lt;&gt;"")+($M$8:$M$19&lt;&gt;"")+($P$8:$P$19&lt;&gt;"")+($Q$8:$Q$19&lt;&gt;"")&gt;0)))&amp;" linha(s) ou preço(s) incompletos",COUNTIF($N$8:$N$19,"Abaixo do mínimo")&amp;" de "&amp;COUNTA($A$8:$A$19)))</f>
         <v>0 de 7</v>
       </c>
       <c r="D5" s="10" t="n"/>
       <c r="E5" s="17">
-        <f>IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF((SUMPRODUCT(($A$8:$A$19&lt;&gt;"")*(ISNUMBER($F$8:$F$19)=FALSE))+SUMPRODUCT(ISTEXT($H$8:$M$19)+ISNUMBER($H$8:$M$19)*($H$8:$M$19&lt;0))+SUMPRODUCT(($A$8:$A$19="")*(($B$8:$B$19&lt;&gt;"")+($C$8:$C$19&lt;&gt;"")+($D$8:$D$19&lt;&gt;"")+($H$8:$H$19&lt;&gt;"")+($I$8:$I$19&lt;&gt;"")+($J$8:$J$19&lt;&gt;"")+($K$8:$K$19&lt;&gt;"")+($L$8:$L$19&lt;&gt;"")+($M$8:$M$19&lt;&gt;"")+($P$8:$P$19&lt;&gt;"")+($Q$8:$Q$19&lt;&gt;"")&gt;0)))&gt;0,(SUMPRODUCT(($A$8:$A$19&lt;&gt;"")*(ISNUMBER($F$8:$F$19)=FALSE))+SUMPRODUCT(ISTEXT($H$8:$M$19)+ISNUMBER($H$8:$M$19)*($H$8:$M$19&lt;0))+SUMPRODUCT(($A$8:$A$19="")*(($B$8:$B$19&lt;&gt;"")+($C$8:$C$19&lt;&gt;"")+($D$8:$D$19&lt;&gt;"")+($H$8:$H$19&lt;&gt;"")+($I$8:$I$19&lt;&gt;"")+($J$8:$J$19&lt;&gt;"")+($K$8:$K$19&lt;&gt;"")+($L$8:$L$19&lt;&gt;"")+($M$8:$M$19&lt;&gt;"")+($P$8:$P$19&lt;&gt;"")+($Q$8:$Q$19&lt;&gt;"")&gt;0)))&amp;" linha(s) ou preço(s) incompletos",SUM($O$8:$O$19)))</f>
+        <f>IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF((SUMPRODUCT(($A$8:$A$19&lt;&gt;"")*(ISNUMBER($F$8:$F$19)=FALSE))+SUMPRODUCT(($A$8:$A$19&lt;&gt;"")*($H$8:$H$19=""))+SUMPRODUCT(ISTEXT($H$8:$M$19)+ISNUMBER($H$8:$M$19)*($H$8:$M$19&lt;0))+SUMPRODUCT(($A$8:$A$19="")*(($B$8:$B$19&lt;&gt;"")+($C$8:$C$19&lt;&gt;"")+($D$8:$D$19&lt;&gt;"")+($H$8:$H$19&lt;&gt;"")+($I$8:$I$19&lt;&gt;"")+($J$8:$J$19&lt;&gt;"")+($K$8:$K$19&lt;&gt;"")+($L$8:$L$19&lt;&gt;"")+($M$8:$M$19&lt;&gt;"")+($P$8:$P$19&lt;&gt;"")+($Q$8:$Q$19&lt;&gt;"")&gt;0)))&gt;0,(SUMPRODUCT(($A$8:$A$19&lt;&gt;"")*(ISNUMBER($F$8:$F$19)=FALSE))+SUMPRODUCT(($A$8:$A$19&lt;&gt;"")*($H$8:$H$19=""))+SUMPRODUCT(ISTEXT($H$8:$M$19)+ISNUMBER($H$8:$M$19)*($H$8:$M$19&lt;0))+SUMPRODUCT(($A$8:$A$19="")*(($B$8:$B$19&lt;&gt;"")+($C$8:$C$19&lt;&gt;"")+($D$8:$D$19&lt;&gt;"")+($H$8:$H$19&lt;&gt;"")+($I$8:$I$19&lt;&gt;"")+($J$8:$J$19&lt;&gt;"")+($K$8:$K$19&lt;&gt;"")+($L$8:$L$19&lt;&gt;"")+($M$8:$M$19&lt;&gt;"")+($P$8:$P$19&lt;&gt;"")+($Q$8:$Q$19&lt;&gt;"")&gt;0)))&amp;" linha(s) ou preço(s) incompletos",SUM($O$8:$O$19)))</f>
         <v>14</v>
       </c>
       <c r="F5" s="10" t="n"/>
@@ -1375,7 +1375,7 @@
         <v>4</v>
       </c>
       <c r="E8" s="26">
-        <f>IF(A8="","",IF(NOT(ISNUMBER((IF(NOT(IF(ISNUMBER(B8),AND(B8&gt;=0),FALSE)),"faltam os minutos",IF(AND(C8&lt;&gt;"Sim",C8&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C8="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B8+IF(C8="Sim",Config!$B$11*Config!$B$12,0))))))),(IF(NOT(IF(ISNUMBER(B8),AND(B8&gt;=0),FALSE)),"faltam os minutos",IF(AND(C8&lt;&gt;"Sim",C8&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C8="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B8+IF(C8="Sim",Config!$B$11*Config!$B$12,0))))),IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D8),AND(D8&gt;=0),FALSE)),"falta o material",(IF(NOT(IF(ISNUMBER(B8),AND(B8&gt;=0),FALSE)),"faltam os minutos",IF(AND(C8&lt;&gt;"Sim",C8&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C8="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B8+IF(C8="Sim",Config!$B$11*Config!$B$12,0)))))/60*Config!$B$7+D8))))</f>
+        <f>IF(A8="","",IF(NOT(ISNUMBER((IF(NOT(IF(ISNUMBER(B8),AND(B8&gt;=0),FALSE)),"faltam os minutos",IF(AND(C8&lt;&gt;"Sim",C8&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C8="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B8+IF(C8="Sim",Config!$B$11*Config!$B$12,0))))))),(IF(NOT(IF(ISNUMBER(B8),AND(B8&gt;=0),FALSE)),"faltam os minutos",IF(AND(C8&lt;&gt;"Sim",C8&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C8="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B8+IF(C8="Sim",Config!$B$11*Config!$B$12,0))))),IF(NOT(IF(ISNUMBER(Config!$B$7),AND(Config!$B$7&gt;=0),FALSE)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D8),AND(D8&gt;=0),FALSE)),"falta o material",(IF(NOT(IF(ISNUMBER(B8),AND(B8&gt;=0),FALSE)),"faltam os minutos",IF(AND(C8&lt;&gt;"Sim",C8&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C8="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B8+IF(C8="Sim",Config!$B$11*Config!$B$12,0)))))/60*Config!$B$7+D8))))</f>
         <v>130.666666666667</v>
       </c>
       <c r="F8" s="27">
@@ -1401,11 +1401,11 @@
       <c r="L8" s="28" t="n"/>
       <c r="M8" s="28" t="n"/>
       <c r="N8" s="29" t="str">
-        <f>IF(OR(A8="",H8=""),"",IF(NOT(IF(ISNUMBER(H8),AND(H8&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(E8)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F8)),NOT(ISNUMBER(G8))),"Margens inválidas",IF(H8=0,"Sem cobrança",IF(H8&lt;F8,"Abaixo do mínimo",IF(H8&lt;G8,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(A8="","",IF(H8="","Falta o preço particular",IF(NOT(IF(ISNUMBER(H8),AND(H8&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(E8)),IF(IF(ISNUMBER(Config!$B$7),Config!$B$7&gt;=0,FALSE),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F8)),NOT(ISNUMBER(G8))),"Margens inválidas",IF(H8=0,"Sem cobrança",IF(H8&lt;F8,"Abaixo do mínimo",IF(H8&lt;G8,"Entre mínimo e alvo","No alvo ou acima"))))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="O8" s="30">
-        <f>IF(OR(A8="",NOT(ISNUMBER(F8))),"",IF(SUMPRODUCT(ISTEXT(I8:M8)+ISNUMBER(I8:M8)*(I8:M8&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I8:M8&lt;&gt;"")*(I8:M8&gt;0)*(I8:M8*(1-Config!$B$8)&lt;E8))))</f>
+        <f>IF(OR(A8="",NOT(ISNUMBER(F8))),"",IF(SUMPRODUCT(ISTEXT(I8:M8)+ISNUMBER(I8:M8)*(I8:M8&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I8:M8&lt;&gt;"")*ISNUMBER(I8:M8)*(((I8:M8)&gt;0)+(N(H8)&gt;0)&gt;0)*(I8:M8*(1-Config!$B$8)&lt;E8))))</f>
         <v>3</v>
       </c>
       <c r="P8" s="23" t="n">
@@ -1442,7 +1442,7 @@
         <v>2</v>
       </c>
       <c r="E9" s="26">
-        <f>IF(A9="","",IF(NOT(ISNUMBER((IF(NOT(IF(ISNUMBER(B9),AND(B9&gt;=0),FALSE)),"faltam os minutos",IF(AND(C9&lt;&gt;"Sim",C9&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C9="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B9+IF(C9="Sim",Config!$B$11*Config!$B$12,0))))))),(IF(NOT(IF(ISNUMBER(B9),AND(B9&gt;=0),FALSE)),"faltam os minutos",IF(AND(C9&lt;&gt;"Sim",C9&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C9="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B9+IF(C9="Sim",Config!$B$11*Config!$B$12,0))))),IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D9),AND(D9&gt;=0),FALSE)),"falta o material",(IF(NOT(IF(ISNUMBER(B9),AND(B9&gt;=0),FALSE)),"faltam os minutos",IF(AND(C9&lt;&gt;"Sim",C9&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C9="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B9+IF(C9="Sim",Config!$B$11*Config!$B$12,0)))))/60*Config!$B$7+D9))))</f>
+        <f>IF(A9="","",IF(NOT(ISNUMBER((IF(NOT(IF(ISNUMBER(B9),AND(B9&gt;=0),FALSE)),"faltam os minutos",IF(AND(C9&lt;&gt;"Sim",C9&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C9="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B9+IF(C9="Sim",Config!$B$11*Config!$B$12,0))))))),(IF(NOT(IF(ISNUMBER(B9),AND(B9&gt;=0),FALSE)),"faltam os minutos",IF(AND(C9&lt;&gt;"Sim",C9&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C9="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B9+IF(C9="Sim",Config!$B$11*Config!$B$12,0))))),IF(NOT(IF(ISNUMBER(Config!$B$7),AND(Config!$B$7&gt;=0),FALSE)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D9),AND(D9&gt;=0),FALSE)),"falta o material",(IF(NOT(IF(ISNUMBER(B9),AND(B9&gt;=0),FALSE)),"faltam os minutos",IF(AND(C9&lt;&gt;"Sim",C9&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C9="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B9+IF(C9="Sim",Config!$B$11*Config!$B$12,0)))))/60*Config!$B$7+D9))))</f>
         <v>68.6666666666667</v>
       </c>
       <c r="F9" s="27">
@@ -1468,11 +1468,11 @@
       <c r="L9" s="28" t="n"/>
       <c r="M9" s="28" t="n"/>
       <c r="N9" s="29" t="str">
-        <f>IF(OR(A9="",H9=""),"",IF(NOT(IF(ISNUMBER(H9),AND(H9&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(E9)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F9)),NOT(ISNUMBER(G9))),"Margens inválidas",IF(H9=0,"Sem cobrança",IF(H9&lt;F9,"Abaixo do mínimo",IF(H9&lt;G9,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(A9="","",IF(H9="","Falta o preço particular",IF(NOT(IF(ISNUMBER(H9),AND(H9&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(E9)),IF(IF(ISNUMBER(Config!$B$7),Config!$B$7&gt;=0,FALSE),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F9)),NOT(ISNUMBER(G9))),"Margens inválidas",IF(H9=0,"Sem cobrança",IF(H9&lt;F9,"Abaixo do mínimo",IF(H9&lt;G9,"Entre mínimo e alvo","No alvo ou acima"))))))))</f>
         <v>Sem cobrança</v>
       </c>
       <c r="O9" s="30">
-        <f>IF(OR(A9="",NOT(ISNUMBER(F9))),"",IF(SUMPRODUCT(ISTEXT(I9:M9)+ISNUMBER(I9:M9)*(I9:M9&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I9:M9&lt;&gt;"")*(I9:M9&gt;0)*(I9:M9*(1-Config!$B$8)&lt;E9))))</f>
+        <f>IF(OR(A9="",NOT(ISNUMBER(F9))),"",IF(SUMPRODUCT(ISTEXT(I9:M9)+ISNUMBER(I9:M9)*(I9:M9&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I9:M9&lt;&gt;"")*ISNUMBER(I9:M9)*(((I9:M9)&gt;0)+(N(H9)&gt;0)&gt;0)*(I9:M9*(1-Config!$B$8)&lt;E9))))</f>
         <v>0</v>
       </c>
       <c r="P9" s="23" t="n">
@@ -1509,7 +1509,7 @@
         <v>8</v>
       </c>
       <c r="E10" s="26">
-        <f>IF(A10="","",IF(NOT(ISNUMBER((IF(NOT(IF(ISNUMBER(B10),AND(B10&gt;=0),FALSE)),"faltam os minutos",IF(AND(C10&lt;&gt;"Sim",C10&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C10="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B10+IF(C10="Sim",Config!$B$11*Config!$B$12,0))))))),(IF(NOT(IF(ISNUMBER(B10),AND(B10&gt;=0),FALSE)),"faltam os minutos",IF(AND(C10&lt;&gt;"Sim",C10&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C10="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B10+IF(C10="Sim",Config!$B$11*Config!$B$12,0))))),IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D10),AND(D10&gt;=0),FALSE)),"falta o material",(IF(NOT(IF(ISNUMBER(B10),AND(B10&gt;=0),FALSE)),"faltam os minutos",IF(AND(C10&lt;&gt;"Sim",C10&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C10="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B10+IF(C10="Sim",Config!$B$11*Config!$B$12,0)))))/60*Config!$B$7+D10))))</f>
+        <f>IF(A10="","",IF(NOT(ISNUMBER((IF(NOT(IF(ISNUMBER(B10),AND(B10&gt;=0),FALSE)),"faltam os minutos",IF(AND(C10&lt;&gt;"Sim",C10&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C10="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B10+IF(C10="Sim",Config!$B$11*Config!$B$12,0))))))),(IF(NOT(IF(ISNUMBER(B10),AND(B10&gt;=0),FALSE)),"faltam os minutos",IF(AND(C10&lt;&gt;"Sim",C10&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C10="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B10+IF(C10="Sim",Config!$B$11*Config!$B$12,0))))),IF(NOT(IF(ISNUMBER(Config!$B$7),AND(Config!$B$7&gt;=0),FALSE)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D10),AND(D10&gt;=0),FALSE)),"falta o material",(IF(NOT(IF(ISNUMBER(B10),AND(B10&gt;=0),FALSE)),"faltam os minutos",IF(AND(C10&lt;&gt;"Sim",C10&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C10="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B10+IF(C10="Sim",Config!$B$11*Config!$B$12,0)))))/60*Config!$B$7+D10))))</f>
         <v>74.6666666666667</v>
       </c>
       <c r="F10" s="27">
@@ -1535,11 +1535,11 @@
       <c r="L10" s="28" t="n"/>
       <c r="M10" s="28" t="n"/>
       <c r="N10" s="29" t="str">
-        <f>IF(OR(A10="",H10=""),"",IF(NOT(IF(ISNUMBER(H10),AND(H10&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(E10)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F10)),NOT(ISNUMBER(G10))),"Margens inválidas",IF(H10=0,"Sem cobrança",IF(H10&lt;F10,"Abaixo do mínimo",IF(H10&lt;G10,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(A10="","",IF(H10="","Falta o preço particular",IF(NOT(IF(ISNUMBER(H10),AND(H10&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(E10)),IF(IF(ISNUMBER(Config!$B$7),Config!$B$7&gt;=0,FALSE),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F10)),NOT(ISNUMBER(G10))),"Margens inválidas",IF(H10=0,"Sem cobrança",IF(H10&lt;F10,"Abaixo do mínimo",IF(H10&lt;G10,"Entre mínimo e alvo","No alvo ou acima"))))))))</f>
         <v>Entre mínimo e alvo</v>
       </c>
       <c r="O10" s="30">
-        <f>IF(OR(A10="",NOT(ISNUMBER(F10))),"",IF(SUMPRODUCT(ISTEXT(I10:M10)+ISNUMBER(I10:M10)*(I10:M10&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I10:M10&lt;&gt;"")*(I10:M10&gt;0)*(I10:M10*(1-Config!$B$8)&lt;E10))))</f>
+        <f>IF(OR(A10="",NOT(ISNUMBER(F10))),"",IF(SUMPRODUCT(ISTEXT(I10:M10)+ISNUMBER(I10:M10)*(I10:M10&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I10:M10&lt;&gt;"")*ISNUMBER(I10:M10)*(((I10:M10)&gt;0)+(N(H10)&gt;0)&gt;0)*(I10:M10*(1-Config!$B$8)&lt;E10))))</f>
         <v>3</v>
       </c>
       <c r="P10" s="23" t="n">
@@ -1576,7 +1576,7 @@
         <v>15</v>
       </c>
       <c r="E11" s="26">
-        <f>IF(A11="","",IF(NOT(ISNUMBER((IF(NOT(IF(ISNUMBER(B11),AND(B11&gt;=0),FALSE)),"faltam os minutos",IF(AND(C11&lt;&gt;"Sim",C11&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C11="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B11+IF(C11="Sim",Config!$B$11*Config!$B$12,0))))))),(IF(NOT(IF(ISNUMBER(B11),AND(B11&gt;=0),FALSE)),"faltam os minutos",IF(AND(C11&lt;&gt;"Sim",C11&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C11="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B11+IF(C11="Sim",Config!$B$11*Config!$B$12,0))))),IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D11),AND(D11&gt;=0),FALSE)),"falta o material",(IF(NOT(IF(ISNUMBER(B11),AND(B11&gt;=0),FALSE)),"faltam os minutos",IF(AND(C11&lt;&gt;"Sim",C11&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C11="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B11+IF(C11="Sim",Config!$B$11*Config!$B$12,0)))))/60*Config!$B$7+D11))))</f>
+        <f>IF(A11="","",IF(NOT(ISNUMBER((IF(NOT(IF(ISNUMBER(B11),AND(B11&gt;=0),FALSE)),"faltam os minutos",IF(AND(C11&lt;&gt;"Sim",C11&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C11="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B11+IF(C11="Sim",Config!$B$11*Config!$B$12,0))))))),(IF(NOT(IF(ISNUMBER(B11),AND(B11&gt;=0),FALSE)),"faltam os minutos",IF(AND(C11&lt;&gt;"Sim",C11&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C11="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B11+IF(C11="Sim",Config!$B$11*Config!$B$12,0))))),IF(NOT(IF(ISNUMBER(Config!$B$7),AND(Config!$B$7&gt;=0),FALSE)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D11),AND(D11&gt;=0),FALSE)),"falta o material",(IF(NOT(IF(ISNUMBER(B11),AND(B11&gt;=0),FALSE)),"faltam os minutos",IF(AND(C11&lt;&gt;"Sim",C11&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C11="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B11+IF(C11="Sim",Config!$B$11*Config!$B$12,0)))))/60*Config!$B$7+D11))))</f>
         <v>81.6666666666667</v>
       </c>
       <c r="F11" s="27">
@@ -1602,11 +1602,11 @@
       <c r="L11" s="28" t="n"/>
       <c r="M11" s="28" t="n"/>
       <c r="N11" s="29" t="str">
-        <f>IF(OR(A11="",H11=""),"",IF(NOT(IF(ISNUMBER(H11),AND(H11&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(E11)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F11)),NOT(ISNUMBER(G11))),"Margens inválidas",IF(H11=0,"Sem cobrança",IF(H11&lt;F11,"Abaixo do mínimo",IF(H11&lt;G11,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(A11="","",IF(H11="","Falta o preço particular",IF(NOT(IF(ISNUMBER(H11),AND(H11&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(E11)),IF(IF(ISNUMBER(Config!$B$7),Config!$B$7&gt;=0,FALSE),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F11)),NOT(ISNUMBER(G11))),"Margens inválidas",IF(H11=0,"Sem cobrança",IF(H11&lt;F11,"Abaixo do mínimo",IF(H11&lt;G11,"Entre mínimo e alvo","No alvo ou acima"))))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="O11" s="30">
-        <f>IF(OR(A11="",NOT(ISNUMBER(F11))),"",IF(SUMPRODUCT(ISTEXT(I11:M11)+ISNUMBER(I11:M11)*(I11:M11&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I11:M11&lt;&gt;"")*(I11:M11&gt;0)*(I11:M11*(1-Config!$B$8)&lt;E11))))</f>
+        <f>IF(OR(A11="",NOT(ISNUMBER(F11))),"",IF(SUMPRODUCT(ISTEXT(I11:M11)+ISNUMBER(I11:M11)*(I11:M11&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I11:M11&lt;&gt;"")*ISNUMBER(I11:M11)*(((I11:M11)&gt;0)+(N(H11)&gt;0)&gt;0)*(I11:M11*(1-Config!$B$8)&lt;E11))))</f>
         <v>2</v>
       </c>
       <c r="P11" s="23" t="n">
@@ -1643,7 +1643,7 @@
         <v>18</v>
       </c>
       <c r="E12" s="26">
-        <f>IF(A12="","",IF(NOT(ISNUMBER((IF(NOT(IF(ISNUMBER(B12),AND(B12&gt;=0),FALSE)),"faltam os minutos",IF(AND(C12&lt;&gt;"Sim",C12&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C12="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B12+IF(C12="Sim",Config!$B$11*Config!$B$12,0))))))),(IF(NOT(IF(ISNUMBER(B12),AND(B12&gt;=0),FALSE)),"faltam os minutos",IF(AND(C12&lt;&gt;"Sim",C12&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C12="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B12+IF(C12="Sim",Config!$B$11*Config!$B$12,0))))),IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D12),AND(D12&gt;=0),FALSE)),"falta o material",(IF(NOT(IF(ISNUMBER(B12),AND(B12&gt;=0),FALSE)),"faltam os minutos",IF(AND(C12&lt;&gt;"Sim",C12&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C12="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B12+IF(C12="Sim",Config!$B$11*Config!$B$12,0)))))/60*Config!$B$7+D12))))</f>
+        <f>IF(A12="","",IF(NOT(ISNUMBER((IF(NOT(IF(ISNUMBER(B12),AND(B12&gt;=0),FALSE)),"faltam os minutos",IF(AND(C12&lt;&gt;"Sim",C12&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C12="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B12+IF(C12="Sim",Config!$B$11*Config!$B$12,0))))))),(IF(NOT(IF(ISNUMBER(B12),AND(B12&gt;=0),FALSE)),"faltam os minutos",IF(AND(C12&lt;&gt;"Sim",C12&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C12="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B12+IF(C12="Sim",Config!$B$11*Config!$B$12,0))))),IF(NOT(IF(ISNUMBER(Config!$B$7),AND(Config!$B$7&gt;=0),FALSE)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D12),AND(D12&gt;=0),FALSE)),"falta o material",(IF(NOT(IF(ISNUMBER(B12),AND(B12&gt;=0),FALSE)),"faltam os minutos",IF(AND(C12&lt;&gt;"Sim",C12&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C12="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B12+IF(C12="Sim",Config!$B$11*Config!$B$12,0)))))/60*Config!$B$7+D12))))</f>
         <v>84.6666666666667</v>
       </c>
       <c r="F12" s="27">
@@ -1669,11 +1669,11 @@
       <c r="L12" s="28" t="n"/>
       <c r="M12" s="28" t="n"/>
       <c r="N12" s="29" t="str">
-        <f>IF(OR(A12="",H12=""),"",IF(NOT(IF(ISNUMBER(H12),AND(H12&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(E12)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F12)),NOT(ISNUMBER(G12))),"Margens inválidas",IF(H12=0,"Sem cobrança",IF(H12&lt;F12,"Abaixo do mínimo",IF(H12&lt;G12,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(A12="","",IF(H12="","Falta o preço particular",IF(NOT(IF(ISNUMBER(H12),AND(H12&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(E12)),IF(IF(ISNUMBER(Config!$B$7),Config!$B$7&gt;=0,FALSE),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F12)),NOT(ISNUMBER(G12))),"Margens inválidas",IF(H12=0,"Sem cobrança",IF(H12&lt;F12,"Abaixo do mínimo",IF(H12&lt;G12,"Entre mínimo e alvo","No alvo ou acima"))))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="O12" s="30">
-        <f>IF(OR(A12="",NOT(ISNUMBER(F12))),"",IF(SUMPRODUCT(ISTEXT(I12:M12)+ISNUMBER(I12:M12)*(I12:M12&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I12:M12&lt;&gt;"")*(I12:M12&gt;0)*(I12:M12*(1-Config!$B$8)&lt;E12))))</f>
+        <f>IF(OR(A12="",NOT(ISNUMBER(F12))),"",IF(SUMPRODUCT(ISTEXT(I12:M12)+ISNUMBER(I12:M12)*(I12:M12&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I12:M12&lt;&gt;"")*ISNUMBER(I12:M12)*(((I12:M12)&gt;0)+(N(H12)&gt;0)&gt;0)*(I12:M12*(1-Config!$B$8)&lt;E12))))</f>
         <v>2</v>
       </c>
       <c r="P12" s="23" t="n">
@@ -1710,7 +1710,7 @@
         <v>25</v>
       </c>
       <c r="E13" s="26">
-        <f>IF(A13="","",IF(NOT(ISNUMBER((IF(NOT(IF(ISNUMBER(B13),AND(B13&gt;=0),FALSE)),"faltam os minutos",IF(AND(C13&lt;&gt;"Sim",C13&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C13="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B13+IF(C13="Sim",Config!$B$11*Config!$B$12,0))))))),(IF(NOT(IF(ISNUMBER(B13),AND(B13&gt;=0),FALSE)),"faltam os minutos",IF(AND(C13&lt;&gt;"Sim",C13&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C13="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B13+IF(C13="Sim",Config!$B$11*Config!$B$12,0))))),IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D13),AND(D13&gt;=0),FALSE)),"falta o material",(IF(NOT(IF(ISNUMBER(B13),AND(B13&gt;=0),FALSE)),"faltam os minutos",IF(AND(C13&lt;&gt;"Sim",C13&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C13="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B13+IF(C13="Sim",Config!$B$11*Config!$B$12,0)))))/60*Config!$B$7+D13))))</f>
+        <f>IF(A13="","",IF(NOT(ISNUMBER((IF(NOT(IF(ISNUMBER(B13),AND(B13&gt;=0),FALSE)),"faltam os minutos",IF(AND(C13&lt;&gt;"Sim",C13&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C13="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B13+IF(C13="Sim",Config!$B$11*Config!$B$12,0))))))),(IF(NOT(IF(ISNUMBER(B13),AND(B13&gt;=0),FALSE)),"faltam os minutos",IF(AND(C13&lt;&gt;"Sim",C13&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C13="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B13+IF(C13="Sim",Config!$B$11*Config!$B$12,0))))),IF(NOT(IF(ISNUMBER(Config!$B$7),AND(Config!$B$7&gt;=0),FALSE)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D13),AND(D13&gt;=0),FALSE)),"falta o material",(IF(NOT(IF(ISNUMBER(B13),AND(B13&gt;=0),FALSE)),"faltam os minutos",IF(AND(C13&lt;&gt;"Sim",C13&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C13="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B13+IF(C13="Sim",Config!$B$11*Config!$B$12,0)))))/60*Config!$B$7+D13))))</f>
         <v>158.333333333333</v>
       </c>
       <c r="F13" s="27">
@@ -1736,11 +1736,11 @@
       <c r="L13" s="28" t="n"/>
       <c r="M13" s="28" t="n"/>
       <c r="N13" s="29" t="str">
-        <f>IF(OR(A13="",H13=""),"",IF(NOT(IF(ISNUMBER(H13),AND(H13&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(E13)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F13)),NOT(ISNUMBER(G13))),"Margens inválidas",IF(H13=0,"Sem cobrança",IF(H13&lt;F13,"Abaixo do mínimo",IF(H13&lt;G13,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(A13="","",IF(H13="","Falta o preço particular",IF(NOT(IF(ISNUMBER(H13),AND(H13&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(E13)),IF(IF(ISNUMBER(Config!$B$7),Config!$B$7&gt;=0,FALSE),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F13)),NOT(ISNUMBER(G13))),"Margens inválidas",IF(H13=0,"Sem cobrança",IF(H13&lt;F13,"Abaixo do mínimo",IF(H13&lt;G13,"Entre mínimo e alvo","No alvo ou acima"))))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="O13" s="30">
-        <f>IF(OR(A13="",NOT(ISNUMBER(F13))),"",IF(SUMPRODUCT(ISTEXT(I13:M13)+ISNUMBER(I13:M13)*(I13:M13&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I13:M13&lt;&gt;"")*(I13:M13&gt;0)*(I13:M13*(1-Config!$B$8)&lt;E13))))</f>
+        <f>IF(OR(A13="",NOT(ISNUMBER(F13))),"",IF(SUMPRODUCT(ISTEXT(I13:M13)+ISNUMBER(I13:M13)*(I13:M13&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I13:M13&lt;&gt;"")*ISNUMBER(I13:M13)*(((I13:M13)&gt;0)+(N(H13)&gt;0)&gt;0)*(I13:M13*(1-Config!$B$8)&lt;E13))))</f>
         <v>3</v>
       </c>
       <c r="P13" s="23" t="n">
@@ -1777,7 +1777,7 @@
         <v>4</v>
       </c>
       <c r="E14" s="26">
-        <f>IF(A14="","",IF(NOT(ISNUMBER((IF(NOT(IF(ISNUMBER(B14),AND(B14&gt;=0),FALSE)),"faltam os minutos",IF(AND(C14&lt;&gt;"Sim",C14&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C14="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B14+IF(C14="Sim",Config!$B$11*Config!$B$12,0))))))),(IF(NOT(IF(ISNUMBER(B14),AND(B14&gt;=0),FALSE)),"faltam os minutos",IF(AND(C14&lt;&gt;"Sim",C14&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C14="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B14+IF(C14="Sim",Config!$B$11*Config!$B$12,0))))),IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D14),AND(D14&gt;=0),FALSE)),"falta o material",(IF(NOT(IF(ISNUMBER(B14),AND(B14&gt;=0),FALSE)),"faltam os minutos",IF(AND(C14&lt;&gt;"Sim",C14&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C14="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B14+IF(C14="Sim",Config!$B$11*Config!$B$12,0)))))/60*Config!$B$7+D14))))</f>
+        <f>IF(A14="","",IF(NOT(ISNUMBER((IF(NOT(IF(ISNUMBER(B14),AND(B14&gt;=0),FALSE)),"faltam os minutos",IF(AND(C14&lt;&gt;"Sim",C14&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C14="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B14+IF(C14="Sim",Config!$B$11*Config!$B$12,0))))))),(IF(NOT(IF(ISNUMBER(B14),AND(B14&gt;=0),FALSE)),"faltam os minutos",IF(AND(C14&lt;&gt;"Sim",C14&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C14="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B14+IF(C14="Sim",Config!$B$11*Config!$B$12,0))))),IF(NOT(IF(ISNUMBER(Config!$B$7),AND(Config!$B$7&gt;=0),FALSE)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D14),AND(D14&gt;=0),FALSE)),"falta o material",(IF(NOT(IF(ISNUMBER(B14),AND(B14&gt;=0),FALSE)),"faltam os minutos",IF(AND(C14&lt;&gt;"Sim",C14&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C14="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B14+IF(C14="Sim",Config!$B$11*Config!$B$12,0)))))/60*Config!$B$7+D14))))</f>
         <v>164</v>
       </c>
       <c r="F14" s="27">
@@ -1799,11 +1799,11 @@
       <c r="L14" s="28" t="n"/>
       <c r="M14" s="28" t="n"/>
       <c r="N14" s="29" t="str">
-        <f>IF(OR(A14="",H14=""),"",IF(NOT(IF(ISNUMBER(H14),AND(H14&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(E14)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F14)),NOT(ISNUMBER(G14))),"Margens inválidas",IF(H14=0,"Sem cobrança",IF(H14&lt;F14,"Abaixo do mínimo",IF(H14&lt;G14,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(A14="","",IF(H14="","Falta o preço particular",IF(NOT(IF(ISNUMBER(H14),AND(H14&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(E14)),IF(IF(ISNUMBER(Config!$B$7),Config!$B$7&gt;=0,FALSE),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F14)),NOT(ISNUMBER(G14))),"Margens inválidas",IF(H14=0,"Sem cobrança",IF(H14&lt;F14,"Abaixo do mínimo",IF(H14&lt;G14,"Entre mínimo e alvo","No alvo ou acima"))))))))</f>
         <v>No alvo ou acima</v>
       </c>
       <c r="O14" s="30">
-        <f>IF(OR(A14="",NOT(ISNUMBER(F14))),"",IF(SUMPRODUCT(ISTEXT(I14:M14)+ISNUMBER(I14:M14)*(I14:M14&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I14:M14&lt;&gt;"")*(I14:M14&gt;0)*(I14:M14*(1-Config!$B$8)&lt;E14))))</f>
+        <f>IF(OR(A14="",NOT(ISNUMBER(F14))),"",IF(SUMPRODUCT(ISTEXT(I14:M14)+ISNUMBER(I14:M14)*(I14:M14&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I14:M14&lt;&gt;"")*ISNUMBER(I14:M14)*(((I14:M14)&gt;0)+(N(H14)&gt;0)&gt;0)*(I14:M14*(1-Config!$B$8)&lt;E14))))</f>
         <v>1</v>
       </c>
       <c r="P14" s="23" t="n">
@@ -1828,7 +1828,7 @@
       <c r="C15" s="24" t="n"/>
       <c r="D15" s="25" t="n"/>
       <c r="E15" s="26">
-        <f>IF(A15="","",IF(NOT(ISNUMBER((IF(NOT(IF(ISNUMBER(B15),AND(B15&gt;=0),FALSE)),"faltam os minutos",IF(AND(C15&lt;&gt;"Sim",C15&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C15="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B15+IF(C15="Sim",Config!$B$11*Config!$B$12,0))))))),(IF(NOT(IF(ISNUMBER(B15),AND(B15&gt;=0),FALSE)),"faltam os minutos",IF(AND(C15&lt;&gt;"Sim",C15&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C15="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B15+IF(C15="Sim",Config!$B$11*Config!$B$12,0))))),IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D15),AND(D15&gt;=0),FALSE)),"falta o material",(IF(NOT(IF(ISNUMBER(B15),AND(B15&gt;=0),FALSE)),"faltam os minutos",IF(AND(C15&lt;&gt;"Sim",C15&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C15="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B15+IF(C15="Sim",Config!$B$11*Config!$B$12,0)))))/60*Config!$B$7+D15))))</f>
+        <f>IF(A15="","",IF(NOT(ISNUMBER((IF(NOT(IF(ISNUMBER(B15),AND(B15&gt;=0),FALSE)),"faltam os minutos",IF(AND(C15&lt;&gt;"Sim",C15&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C15="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B15+IF(C15="Sim",Config!$B$11*Config!$B$12,0))))))),(IF(NOT(IF(ISNUMBER(B15),AND(B15&gt;=0),FALSE)),"faltam os minutos",IF(AND(C15&lt;&gt;"Sim",C15&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C15="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B15+IF(C15="Sim",Config!$B$11*Config!$B$12,0))))),IF(NOT(IF(ISNUMBER(Config!$B$7),AND(Config!$B$7&gt;=0),FALSE)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D15),AND(D15&gt;=0),FALSE)),"falta o material",(IF(NOT(IF(ISNUMBER(B15),AND(B15&gt;=0),FALSE)),"faltam os minutos",IF(AND(C15&lt;&gt;"Sim",C15&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C15="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B15+IF(C15="Sim",Config!$B$11*Config!$B$12,0)))))/60*Config!$B$7+D15))))</f>
         <v/>
       </c>
       <c r="F15" s="27">
@@ -1846,11 +1846,11 @@
       <c r="L15" s="28" t="n"/>
       <c r="M15" s="28" t="n"/>
       <c r="N15" s="29">
-        <f>IF(OR(A15="",H15=""),"",IF(NOT(IF(ISNUMBER(H15),AND(H15&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(E15)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F15)),NOT(ISNUMBER(G15))),"Margens inválidas",IF(H15=0,"Sem cobrança",IF(H15&lt;F15,"Abaixo do mínimo",IF(H15&lt;G15,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(A15="","",IF(H15="","Falta o preço particular",IF(NOT(IF(ISNUMBER(H15),AND(H15&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(E15)),IF(IF(ISNUMBER(Config!$B$7),Config!$B$7&gt;=0,FALSE),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F15)),NOT(ISNUMBER(G15))),"Margens inválidas",IF(H15=0,"Sem cobrança",IF(H15&lt;F15,"Abaixo do mínimo",IF(H15&lt;G15,"Entre mínimo e alvo","No alvo ou acima"))))))))</f>
         <v/>
       </c>
       <c r="O15" s="30">
-        <f>IF(OR(A15="",NOT(ISNUMBER(F15))),"",IF(SUMPRODUCT(ISTEXT(I15:M15)+ISNUMBER(I15:M15)*(I15:M15&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I15:M15&lt;&gt;"")*(I15:M15&gt;0)*(I15:M15*(1-Config!$B$8)&lt;E15))))</f>
+        <f>IF(OR(A15="",NOT(ISNUMBER(F15))),"",IF(SUMPRODUCT(ISTEXT(I15:M15)+ISNUMBER(I15:M15)*(I15:M15&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I15:M15&lt;&gt;"")*ISNUMBER(I15:M15)*(((I15:M15)&gt;0)+(N(H15)&gt;0)&gt;0)*(I15:M15*(1-Config!$B$8)&lt;E15))))</f>
         <v/>
       </c>
       <c r="P15" s="23" t="n"/>
@@ -1871,7 +1871,7 @@
       <c r="C16" s="24" t="n"/>
       <c r="D16" s="25" t="n"/>
       <c r="E16" s="26">
-        <f>IF(A16="","",IF(NOT(ISNUMBER((IF(NOT(IF(ISNUMBER(B16),AND(B16&gt;=0),FALSE)),"faltam os minutos",IF(AND(C16&lt;&gt;"Sim",C16&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C16="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B16+IF(C16="Sim",Config!$B$11*Config!$B$12,0))))))),(IF(NOT(IF(ISNUMBER(B16),AND(B16&gt;=0),FALSE)),"faltam os minutos",IF(AND(C16&lt;&gt;"Sim",C16&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C16="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B16+IF(C16="Sim",Config!$B$11*Config!$B$12,0))))),IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D16),AND(D16&gt;=0),FALSE)),"falta o material",(IF(NOT(IF(ISNUMBER(B16),AND(B16&gt;=0),FALSE)),"faltam os minutos",IF(AND(C16&lt;&gt;"Sim",C16&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C16="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B16+IF(C16="Sim",Config!$B$11*Config!$B$12,0)))))/60*Config!$B$7+D16))))</f>
+        <f>IF(A16="","",IF(NOT(ISNUMBER((IF(NOT(IF(ISNUMBER(B16),AND(B16&gt;=0),FALSE)),"faltam os minutos",IF(AND(C16&lt;&gt;"Sim",C16&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C16="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B16+IF(C16="Sim",Config!$B$11*Config!$B$12,0))))))),(IF(NOT(IF(ISNUMBER(B16),AND(B16&gt;=0),FALSE)),"faltam os minutos",IF(AND(C16&lt;&gt;"Sim",C16&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C16="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B16+IF(C16="Sim",Config!$B$11*Config!$B$12,0))))),IF(NOT(IF(ISNUMBER(Config!$B$7),AND(Config!$B$7&gt;=0),FALSE)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D16),AND(D16&gt;=0),FALSE)),"falta o material",(IF(NOT(IF(ISNUMBER(B16),AND(B16&gt;=0),FALSE)),"faltam os minutos",IF(AND(C16&lt;&gt;"Sim",C16&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C16="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B16+IF(C16="Sim",Config!$B$11*Config!$B$12,0)))))/60*Config!$B$7+D16))))</f>
         <v/>
       </c>
       <c r="F16" s="27">
@@ -1889,11 +1889,11 @@
       <c r="L16" s="28" t="n"/>
       <c r="M16" s="28" t="n"/>
       <c r="N16" s="29">
-        <f>IF(OR(A16="",H16=""),"",IF(NOT(IF(ISNUMBER(H16),AND(H16&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(E16)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F16)),NOT(ISNUMBER(G16))),"Margens inválidas",IF(H16=0,"Sem cobrança",IF(H16&lt;F16,"Abaixo do mínimo",IF(H16&lt;G16,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(A16="","",IF(H16="","Falta o preço particular",IF(NOT(IF(ISNUMBER(H16),AND(H16&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(E16)),IF(IF(ISNUMBER(Config!$B$7),Config!$B$7&gt;=0,FALSE),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F16)),NOT(ISNUMBER(G16))),"Margens inválidas",IF(H16=0,"Sem cobrança",IF(H16&lt;F16,"Abaixo do mínimo",IF(H16&lt;G16,"Entre mínimo e alvo","No alvo ou acima"))))))))</f>
         <v/>
       </c>
       <c r="O16" s="30">
-        <f>IF(OR(A16="",NOT(ISNUMBER(F16))),"",IF(SUMPRODUCT(ISTEXT(I16:M16)+ISNUMBER(I16:M16)*(I16:M16&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I16:M16&lt;&gt;"")*(I16:M16&gt;0)*(I16:M16*(1-Config!$B$8)&lt;E16))))</f>
+        <f>IF(OR(A16="",NOT(ISNUMBER(F16))),"",IF(SUMPRODUCT(ISTEXT(I16:M16)+ISNUMBER(I16:M16)*(I16:M16&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I16:M16&lt;&gt;"")*ISNUMBER(I16:M16)*(((I16:M16)&gt;0)+(N(H16)&gt;0)&gt;0)*(I16:M16*(1-Config!$B$8)&lt;E16))))</f>
         <v/>
       </c>
       <c r="P16" s="23" t="n"/>
@@ -1914,7 +1914,7 @@
       <c r="C17" s="24" t="n"/>
       <c r="D17" s="25" t="n"/>
       <c r="E17" s="26">
-        <f>IF(A17="","",IF(NOT(ISNUMBER((IF(NOT(IF(ISNUMBER(B17),AND(B17&gt;=0),FALSE)),"faltam os minutos",IF(AND(C17&lt;&gt;"Sim",C17&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C17="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B17+IF(C17="Sim",Config!$B$11*Config!$B$12,0))))))),(IF(NOT(IF(ISNUMBER(B17),AND(B17&gt;=0),FALSE)),"faltam os minutos",IF(AND(C17&lt;&gt;"Sim",C17&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C17="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B17+IF(C17="Sim",Config!$B$11*Config!$B$12,0))))),IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D17),AND(D17&gt;=0),FALSE)),"falta o material",(IF(NOT(IF(ISNUMBER(B17),AND(B17&gt;=0),FALSE)),"faltam os minutos",IF(AND(C17&lt;&gt;"Sim",C17&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C17="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B17+IF(C17="Sim",Config!$B$11*Config!$B$12,0)))))/60*Config!$B$7+D17))))</f>
+        <f>IF(A17="","",IF(NOT(ISNUMBER((IF(NOT(IF(ISNUMBER(B17),AND(B17&gt;=0),FALSE)),"faltam os minutos",IF(AND(C17&lt;&gt;"Sim",C17&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C17="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B17+IF(C17="Sim",Config!$B$11*Config!$B$12,0))))))),(IF(NOT(IF(ISNUMBER(B17),AND(B17&gt;=0),FALSE)),"faltam os minutos",IF(AND(C17&lt;&gt;"Sim",C17&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C17="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B17+IF(C17="Sim",Config!$B$11*Config!$B$12,0))))),IF(NOT(IF(ISNUMBER(Config!$B$7),AND(Config!$B$7&gt;=0),FALSE)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D17),AND(D17&gt;=0),FALSE)),"falta o material",(IF(NOT(IF(ISNUMBER(B17),AND(B17&gt;=0),FALSE)),"faltam os minutos",IF(AND(C17&lt;&gt;"Sim",C17&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C17="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B17+IF(C17="Sim",Config!$B$11*Config!$B$12,0)))))/60*Config!$B$7+D17))))</f>
         <v/>
       </c>
       <c r="F17" s="27">
@@ -1932,11 +1932,11 @@
       <c r="L17" s="28" t="n"/>
       <c r="M17" s="28" t="n"/>
       <c r="N17" s="29">
-        <f>IF(OR(A17="",H17=""),"",IF(NOT(IF(ISNUMBER(H17),AND(H17&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(E17)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F17)),NOT(ISNUMBER(G17))),"Margens inválidas",IF(H17=0,"Sem cobrança",IF(H17&lt;F17,"Abaixo do mínimo",IF(H17&lt;G17,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(A17="","",IF(H17="","Falta o preço particular",IF(NOT(IF(ISNUMBER(H17),AND(H17&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(E17)),IF(IF(ISNUMBER(Config!$B$7),Config!$B$7&gt;=0,FALSE),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F17)),NOT(ISNUMBER(G17))),"Margens inválidas",IF(H17=0,"Sem cobrança",IF(H17&lt;F17,"Abaixo do mínimo",IF(H17&lt;G17,"Entre mínimo e alvo","No alvo ou acima"))))))))</f>
         <v/>
       </c>
       <c r="O17" s="30">
-        <f>IF(OR(A17="",NOT(ISNUMBER(F17))),"",IF(SUMPRODUCT(ISTEXT(I17:M17)+ISNUMBER(I17:M17)*(I17:M17&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I17:M17&lt;&gt;"")*(I17:M17&gt;0)*(I17:M17*(1-Config!$B$8)&lt;E17))))</f>
+        <f>IF(OR(A17="",NOT(ISNUMBER(F17))),"",IF(SUMPRODUCT(ISTEXT(I17:M17)+ISNUMBER(I17:M17)*(I17:M17&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I17:M17&lt;&gt;"")*ISNUMBER(I17:M17)*(((I17:M17)&gt;0)+(N(H17)&gt;0)&gt;0)*(I17:M17*(1-Config!$B$8)&lt;E17))))</f>
         <v/>
       </c>
       <c r="P17" s="23" t="n"/>
@@ -1957,7 +1957,7 @@
       <c r="C18" s="24" t="n"/>
       <c r="D18" s="25" t="n"/>
       <c r="E18" s="26">
-        <f>IF(A18="","",IF(NOT(ISNUMBER((IF(NOT(IF(ISNUMBER(B18),AND(B18&gt;=0),FALSE)),"faltam os minutos",IF(AND(C18&lt;&gt;"Sim",C18&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C18="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B18+IF(C18="Sim",Config!$B$11*Config!$B$12,0))))))),(IF(NOT(IF(ISNUMBER(B18),AND(B18&gt;=0),FALSE)),"faltam os minutos",IF(AND(C18&lt;&gt;"Sim",C18&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C18="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B18+IF(C18="Sim",Config!$B$11*Config!$B$12,0))))),IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D18),AND(D18&gt;=0),FALSE)),"falta o material",(IF(NOT(IF(ISNUMBER(B18),AND(B18&gt;=0),FALSE)),"faltam os minutos",IF(AND(C18&lt;&gt;"Sim",C18&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C18="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B18+IF(C18="Sim",Config!$B$11*Config!$B$12,0)))))/60*Config!$B$7+D18))))</f>
+        <f>IF(A18="","",IF(NOT(ISNUMBER((IF(NOT(IF(ISNUMBER(B18),AND(B18&gt;=0),FALSE)),"faltam os minutos",IF(AND(C18&lt;&gt;"Sim",C18&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C18="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B18+IF(C18="Sim",Config!$B$11*Config!$B$12,0))))))),(IF(NOT(IF(ISNUMBER(B18),AND(B18&gt;=0),FALSE)),"faltam os minutos",IF(AND(C18&lt;&gt;"Sim",C18&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C18="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B18+IF(C18="Sim",Config!$B$11*Config!$B$12,0))))),IF(NOT(IF(ISNUMBER(Config!$B$7),AND(Config!$B$7&gt;=0),FALSE)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D18),AND(D18&gt;=0),FALSE)),"falta o material",(IF(NOT(IF(ISNUMBER(B18),AND(B18&gt;=0),FALSE)),"faltam os minutos",IF(AND(C18&lt;&gt;"Sim",C18&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C18="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B18+IF(C18="Sim",Config!$B$11*Config!$B$12,0)))))/60*Config!$B$7+D18))))</f>
         <v/>
       </c>
       <c r="F18" s="27">
@@ -1975,11 +1975,11 @@
       <c r="L18" s="28" t="n"/>
       <c r="M18" s="28" t="n"/>
       <c r="N18" s="29">
-        <f>IF(OR(A18="",H18=""),"",IF(NOT(IF(ISNUMBER(H18),AND(H18&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(E18)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F18)),NOT(ISNUMBER(G18))),"Margens inválidas",IF(H18=0,"Sem cobrança",IF(H18&lt;F18,"Abaixo do mínimo",IF(H18&lt;G18,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(A18="","",IF(H18="","Falta o preço particular",IF(NOT(IF(ISNUMBER(H18),AND(H18&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(E18)),IF(IF(ISNUMBER(Config!$B$7),Config!$B$7&gt;=0,FALSE),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F18)),NOT(ISNUMBER(G18))),"Margens inválidas",IF(H18=0,"Sem cobrança",IF(H18&lt;F18,"Abaixo do mínimo",IF(H18&lt;G18,"Entre mínimo e alvo","No alvo ou acima"))))))))</f>
         <v/>
       </c>
       <c r="O18" s="30">
-        <f>IF(OR(A18="",NOT(ISNUMBER(F18))),"",IF(SUMPRODUCT(ISTEXT(I18:M18)+ISNUMBER(I18:M18)*(I18:M18&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I18:M18&lt;&gt;"")*(I18:M18&gt;0)*(I18:M18*(1-Config!$B$8)&lt;E18))))</f>
+        <f>IF(OR(A18="",NOT(ISNUMBER(F18))),"",IF(SUMPRODUCT(ISTEXT(I18:M18)+ISNUMBER(I18:M18)*(I18:M18&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I18:M18&lt;&gt;"")*ISNUMBER(I18:M18)*(((I18:M18)&gt;0)+(N(H18)&gt;0)&gt;0)*(I18:M18*(1-Config!$B$8)&lt;E18))))</f>
         <v/>
       </c>
       <c r="P18" s="23" t="n"/>
@@ -2000,7 +2000,7 @@
       <c r="C19" s="24" t="n"/>
       <c r="D19" s="25" t="n"/>
       <c r="E19" s="26">
-        <f>IF(A19="","",IF(NOT(ISNUMBER((IF(NOT(IF(ISNUMBER(B19),AND(B19&gt;=0),FALSE)),"faltam os minutos",IF(AND(C19&lt;&gt;"Sim",C19&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C19="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B19+IF(C19="Sim",Config!$B$11*Config!$B$12,0))))))),(IF(NOT(IF(ISNUMBER(B19),AND(B19&gt;=0),FALSE)),"faltam os minutos",IF(AND(C19&lt;&gt;"Sim",C19&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C19="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B19+IF(C19="Sim",Config!$B$11*Config!$B$12,0))))),IF(NOT(ISNUMBER(Config!$B$7)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D19),AND(D19&gt;=0),FALSE)),"falta o material",(IF(NOT(IF(ISNUMBER(B19),AND(B19&gt;=0),FALSE)),"faltam os minutos",IF(AND(C19&lt;&gt;"Sim",C19&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C19="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B19+IF(C19="Sim",Config!$B$11*Config!$B$12,0)))))/60*Config!$B$7+D19))))</f>
+        <f>IF(A19="","",IF(NOT(ISNUMBER((IF(NOT(IF(ISNUMBER(B19),AND(B19&gt;=0),FALSE)),"faltam os minutos",IF(AND(C19&lt;&gt;"Sim",C19&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C19="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B19+IF(C19="Sim",Config!$B$11*Config!$B$12,0))))))),(IF(NOT(IF(ISNUMBER(B19),AND(B19&gt;=0),FALSE)),"faltam os minutos",IF(AND(C19&lt;&gt;"Sim",C19&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C19="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B19+IF(C19="Sim",Config!$B$11*Config!$B$12,0))))),IF(NOT(IF(ISNUMBER(Config!$B$7),AND(Config!$B$7&gt;=0),FALSE)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(D19),AND(D19&gt;=0),FALSE)),"falta o material",(IF(NOT(IF(ISNUMBER(B19),AND(B19&gt;=0),FALSE)),"faltam os minutos",IF(AND(C19&lt;&gt;"Sim",C19&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(C19="Sim",NOT(AND(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE)))),"falta o retorno em Config",B19+IF(C19="Sim",Config!$B$11*Config!$B$12,0)))))/60*Config!$B$7+D19))))</f>
         <v/>
       </c>
       <c r="F19" s="27">
@@ -2018,11 +2018,11 @@
       <c r="L19" s="28" t="n"/>
       <c r="M19" s="28" t="n"/>
       <c r="N19" s="29">
-        <f>IF(OR(A19="",H19=""),"",IF(NOT(IF(ISNUMBER(H19),AND(H19&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(E19)),IF(ISNUMBER(Config!$B$7),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F19)),NOT(ISNUMBER(G19))),"Margens inválidas",IF(H19=0,"Sem cobrança",IF(H19&lt;F19,"Abaixo do mínimo",IF(H19&lt;G19,"Entre mínimo e alvo","No alvo ou acima")))))))</f>
+        <f>IF(A19="","",IF(H19="","Falta o preço particular",IF(NOT(IF(ISNUMBER(H19),AND(H19&gt;=0),FALSE)),"Preço inválido",IF(NOT(ISNUMBER(E19)),IF(IF(ISNUMBER(Config!$B$7),Config!$B$7&gt;=0,FALSE),"Faltam dados da linha","Falta o custo-hora"),IF(OR(NOT(ISNUMBER(F19)),NOT(ISNUMBER(G19))),"Margens inválidas",IF(H19=0,"Sem cobrança",IF(H19&lt;F19,"Abaixo do mínimo",IF(H19&lt;G19,"Entre mínimo e alvo","No alvo ou acima"))))))))</f>
         <v/>
       </c>
       <c r="O19" s="30">
-        <f>IF(OR(A19="",NOT(ISNUMBER(F19))),"",IF(SUMPRODUCT(ISTEXT(I19:M19)+ISNUMBER(I19:M19)*(I19:M19&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I19:M19&lt;&gt;"")*(I19:M19&gt;0)*(I19:M19*(1-Config!$B$8)&lt;E19))))</f>
+        <f>IF(OR(A19="",NOT(ISNUMBER(F19))),"",IF(SUMPRODUCT(ISTEXT(I19:M19)+ISNUMBER(I19:M19)*(I19:M19&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I19:M19&lt;&gt;"")*ISNUMBER(I19:M19)*(((I19:M19)&gt;0)+(N(H19)&gt;0)&gt;0)*(I19:M19*(1-Config!$B$8)&lt;E19))))</f>
         <v/>
       </c>
       <c r="P19" s="23" t="n"/>
@@ -2041,7 +2041,7 @@
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="32" t="inlineStr">
         <is>
-          <t>Custo cheio, preço mínimo e preço alvo: a mesma conta da planilha 06 (tempo com retorno × custo-hora + material; ÷ (1 − impostos − margem)). Tabela de convênio em vermelho: depois dos impostos não cobre o custo cheio (margem negativa) — é a mesma conta e o mesmo número do KPI "Tabelas de convênio abaixo do custo cheio + imposto" e do Resumo da planilha 06. Amarela: cobre o custo, mas não a margem mínima.</t>
+          <t>Custo cheio, preço mínimo e preço alvo: a mesma conta da planilha 06 (tempo com retorno × custo-hora + material; ÷ (1 − impostos − margem)). Tabela de convênio em vermelho: depois dos impostos não cobre o custo cheio (margem negativa) — é a mesma conta e o mesmo número do KPI "Tabelas de convênio abaixo do custo cheio + imposto" e do Resumo da planilha 06. Tabela 0 em procedimento cobrado conta (o convênio não paga o custo); no retorno, com particular 0 também, não conta. Amarela: cobre o custo, mas não a margem mínima.</t>
         </is>
       </c>
     </row>
@@ -2649,7 +2649,7 @@
   </mergeCells>
   <conditionalFormatting sqref="N8:N19">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>OR(N8="Abaixo do mínimo",N8="Falta o custo-hora",N8="Margens inválidas",N8="Faltam dados da linha",N8="Preço inválido")</formula>
+      <formula>OR(N8="Abaixo do mínimo",N8="Falta o custo-hora",N8="Margens inválidas",N8="Faltam dados da linha",N8="Preço inválido",N8="Falta o preço particular")</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1">
       <formula>N8="Entre mínimo e alvo"</formula>
@@ -2663,7 +2663,7 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="I8:M19">
     <cfRule type="expression" priority="4" dxfId="4">
-      <formula>AND(ISNUMBER(I8),I8&gt;0,ISNUMBER($F8),I8*(1-INDIRECT("Config!$B$8"))&lt;$E8)</formula>
+      <formula>AND(ISNUMBER(I8),OR(I8&gt;0,N($H8)&gt;0),ISNUMBER($F8),I8*(1-INDIRECT("Config!$B$8"))&lt;$E8)</formula>
     </cfRule>
     <cfRule type="expression" priority="5" dxfId="1">
       <formula>AND(ISNUMBER(I8),ISNUMBER($F8),I8*(1-INDIRECT("Config!$B$8"))&gt;=$E8,I8&lt;$F8)</formula>
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="B13" s="27">
-        <f>IF(NOT(ISNUMBER(B7)),"falta o custo-hora",IF(B15&lt;&gt;"Sim","margens inválidas (Config)",B7/(1-B8-B9)))</f>
+        <f>IF(NOT(IF(ISNUMBER(B7),B7&gt;=0,FALSE)),"falta o custo-hora",IF(B15&lt;&gt;"Sim","margens inválidas (Config)",B7/(1-B8-B9)))</f>
         <v>338.983050847458</v>
       </c>
       <c r="C13" s="37" t="inlineStr">
@@ -2867,7 +2867,7 @@
         </is>
       </c>
       <c r="B14" s="27">
-        <f>IF(NOT(ISNUMBER(B7)),"falta o custo-hora",IF(B15&lt;&gt;"Sim","margens inválidas (Config)",B7/(1-B8-B10)))</f>
+        <f>IF(NOT(IF(ISNUMBER(B7),B7&gt;=0,FALSE)),"falta o custo-hora",IF(B15&lt;&gt;"Sim","margens inválidas (Config)",B7/(1-B8-B10)))</f>
         <v>454.545454545455</v>
       </c>
       <c r="C14" s="37" t="inlineStr">
@@ -2963,7 +2963,7 @@
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentual" error="Impostos entre 0 % e 99 %, e impostos + margem alvo abaixo de 100 %." type="custom">
       <formula1>=IF(ISNUMBER(B8),AND(B8&gt;=0,B8&lt;1,B8+N(B10)&lt;1),FALSE)</formula1>
     </dataValidation>
@@ -2973,6 +2973,9 @@
     <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentual" error="Margem alvo entre a margem mínima e 99 %, e impostos + margem alvo abaixo de 100 %." type="custom">
       <formula1>=IF(ISNUMBER(B10),AND(B10&gt;=N(B9),B10&lt;1,N(B8)+B10&lt;1),FALSE)</formula1>
     </dataValidation>
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Custo-hora" error="Número maior ou igual a zero." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/08-tabela-de-precos.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/08-tabela-de-precos.xlsx
@@ -1419,7 +1419,7 @@
         <v>236.384615384615</v>
       </c>
       <c r="S8" s="31">
-        <f>IF(OR(NOT(ISNUMBER(R8)),NOT(ISNUMBER(F8)),N(H8)=0),"",IF(F8=0,"sem base (mínimo zero)",R8/F8-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(R8)),NOT(ISNUMBER(F8)),NOT(IF(ISNUMBER(H8),H8&gt;0,FALSE))),"",IF(F8=0,"sem base (mínimo zero)",R8/F8-1))</f>
         <v>0.0673489010989012</v>
       </c>
       <c r="T8" s="22" t="n"/>
@@ -1486,7 +1486,7 @@
         <v>0</v>
       </c>
       <c r="S9" s="31">
-        <f>IF(OR(NOT(ISNUMBER(R9)),NOT(ISNUMBER(F9)),N(H9)=0),"",IF(F9=0,"sem base (mínimo zero)",R9/F9-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(R9)),NOT(ISNUMBER(F9)),NOT(IF(ISNUMBER(H9),H9&gt;0,FALSE))),"",IF(F9=0,"sem base (mínimo zero)",R9/F9-1))</f>
         <v/>
       </c>
       <c r="T9" s="22" t="n"/>
@@ -1553,7 +1553,7 @@
         <v>78.6666666666667</v>
       </c>
       <c r="S10" s="31">
-        <f>IF(OR(NOT(ISNUMBER(R10)),NOT(ISNUMBER(F10)),N(H10)=0),"",IF(F10=0,"sem base (mínimo zero)",R10/F10-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(R10)),NOT(ISNUMBER(F10)),NOT(IF(ISNUMBER(H10),H10&gt;0,FALSE))),"",IF(F10=0,"sem base (mínimo zero)",R10/F10-1))</f>
         <v>-0.378392857142857</v>
       </c>
       <c r="T10" s="22" t="n"/>
@@ -1620,7 +1620,7 @@
         <v>168.125</v>
       </c>
       <c r="S11" s="31">
-        <f>IF(OR(NOT(ISNUMBER(R11)),NOT(ISNUMBER(F11)),N(H11)=0),"",IF(F11=0,"sem base (mínimo zero)",R11/F11-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(R11)),NOT(ISNUMBER(F11)),NOT(IF(ISNUMBER(H11),H11&gt;0,FALSE))),"",IF(F11=0,"sem base (mínimo zero)",R11/F11-1))</f>
         <v>0.214617346938776</v>
       </c>
       <c r="T11" s="22" t="n"/>
@@ -1687,7 +1687,7 @@
         <v>249</v>
       </c>
       <c r="S12" s="31">
-        <f>IF(OR(NOT(ISNUMBER(R12)),NOT(ISNUMBER(F12)),N(H12)=0),"",IF(F12=0,"sem base (mínimo zero)",R12/F12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(R12)),NOT(ISNUMBER(F12)),NOT(IF(ISNUMBER(H12),H12&gt;0,FALSE))),"",IF(F12=0,"sem base (mínimo zero)",R12/F12-1))</f>
         <v>0.735157480314961</v>
       </c>
       <c r="T12" s="22" t="n"/>
@@ -1754,7 +1754,7 @@
         <v>283.75</v>
       </c>
       <c r="S13" s="31">
-        <f>IF(OR(NOT(ISNUMBER(R13)),NOT(ISNUMBER(F13)),N(H13)=0),"",IF(F13=0,"sem base (mínimo zero)",R13/F13-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(R13)),NOT(ISNUMBER(F13)),NOT(IF(ISNUMBER(H13),H13&gt;0,FALSE))),"",IF(F13=0,"sem base (mínimo zero)",R13/F13-1))</f>
         <v>0.0573421052631582</v>
       </c>
       <c r="T13" s="22" t="n"/>
@@ -1817,7 +1817,7 @@
         <v>346</v>
       </c>
       <c r="S14" s="31">
-        <f>IF(OR(NOT(ISNUMBER(R14)),NOT(ISNUMBER(F14)),N(H14)=0),"",IF(F14=0,"sem base (mínimo zero)",R14/F14-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(R14)),NOT(ISNUMBER(F14)),NOT(IF(ISNUMBER(H14),H14&gt;0,FALSE))),"",IF(F14=0,"sem base (mínimo zero)",R14/F14-1))</f>
         <v>0.244756097560976</v>
       </c>
       <c r="T14" s="22" t="n"/>
@@ -1860,7 +1860,7 @@
         <v/>
       </c>
       <c r="S15" s="31">
-        <f>IF(OR(NOT(ISNUMBER(R15)),NOT(ISNUMBER(F15)),N(H15)=0),"",IF(F15=0,"sem base (mínimo zero)",R15/F15-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(R15)),NOT(ISNUMBER(F15)),NOT(IF(ISNUMBER(H15),H15&gt;0,FALSE))),"",IF(F15=0,"sem base (mínimo zero)",R15/F15-1))</f>
         <v/>
       </c>
       <c r="T15" s="22" t="n"/>
@@ -1903,7 +1903,7 @@
         <v/>
       </c>
       <c r="S16" s="31">
-        <f>IF(OR(NOT(ISNUMBER(R16)),NOT(ISNUMBER(F16)),N(H16)=0),"",IF(F16=0,"sem base (mínimo zero)",R16/F16-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(R16)),NOT(ISNUMBER(F16)),NOT(IF(ISNUMBER(H16),H16&gt;0,FALSE))),"",IF(F16=0,"sem base (mínimo zero)",R16/F16-1))</f>
         <v/>
       </c>
       <c r="T16" s="22" t="n"/>
@@ -1946,7 +1946,7 @@
         <v/>
       </c>
       <c r="S17" s="31">
-        <f>IF(OR(NOT(ISNUMBER(R17)),NOT(ISNUMBER(F17)),N(H17)=0),"",IF(F17=0,"sem base (mínimo zero)",R17/F17-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(R17)),NOT(ISNUMBER(F17)),NOT(IF(ISNUMBER(H17),H17&gt;0,FALSE))),"",IF(F17=0,"sem base (mínimo zero)",R17/F17-1))</f>
         <v/>
       </c>
       <c r="T17" s="22" t="n"/>
@@ -1989,7 +1989,7 @@
         <v/>
       </c>
       <c r="S18" s="31">
-        <f>IF(OR(NOT(ISNUMBER(R18)),NOT(ISNUMBER(F18)),N(H18)=0),"",IF(F18=0,"sem base (mínimo zero)",R18/F18-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(R18)),NOT(ISNUMBER(F18)),NOT(IF(ISNUMBER(H18),H18&gt;0,FALSE))),"",IF(F18=0,"sem base (mínimo zero)",R18/F18-1))</f>
         <v/>
       </c>
       <c r="T18" s="22" t="n"/>
@@ -2032,7 +2032,7 @@
         <v/>
       </c>
       <c r="S19" s="31">
-        <f>IF(OR(NOT(ISNUMBER(R19)),NOT(ISNUMBER(F19)),N(H19)=0),"",IF(F19=0,"sem base (mínimo zero)",R19/F19-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(R19)),NOT(ISNUMBER(F19)),NOT(IF(ISNUMBER(H19),H19&gt;0,FALSE))),"",IF(F19=0,"sem base (mínimo zero)",R19/F19-1))</f>
         <v/>
       </c>
       <c r="T19" s="22" t="n"/>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/08-tabela-de-precos.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/08-tabela-de-precos.xlsx
@@ -1405,7 +1405,7 @@
         <v>No alvo ou acima</v>
       </c>
       <c r="O8" s="30">
-        <f>IF(OR(A8="",NOT(ISNUMBER(F8))),"",IF(SUMPRODUCT(ISTEXT(I8:M8)+ISNUMBER(I8:M8)*(I8:M8&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I8:M8&lt;&gt;"")*ISNUMBER(I8:M8)*(((I8:M8)&gt;0)+(N(H8)&gt;0)&gt;0)*(I8:M8*(1-Config!$B$8)&lt;E8))))</f>
+        <f>IF(OR(A8="",NOT(ISNUMBER(F8))),"",IF(SUMPRODUCT(ISTEXT(I8:M8)+ISNUMBER(I8:M8)*(I8:M8&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I8:M8&lt;&gt;"")*ISNUMBER(I8:M8)*(((I8:M8)&gt;0)+(TRIM(A8)&lt;&gt;"Retorno")&gt;0)*(I8:M8*(1-Config!$B$8)&lt;E8))))</f>
         <v>3</v>
       </c>
       <c r="P8" s="23" t="n">
@@ -1472,7 +1472,7 @@
         <v>Sem cobrança</v>
       </c>
       <c r="O9" s="30">
-        <f>IF(OR(A9="",NOT(ISNUMBER(F9))),"",IF(SUMPRODUCT(ISTEXT(I9:M9)+ISNUMBER(I9:M9)*(I9:M9&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I9:M9&lt;&gt;"")*ISNUMBER(I9:M9)*(((I9:M9)&gt;0)+(N(H9)&gt;0)&gt;0)*(I9:M9*(1-Config!$B$8)&lt;E9))))</f>
+        <f>IF(OR(A9="",NOT(ISNUMBER(F9))),"",IF(SUMPRODUCT(ISTEXT(I9:M9)+ISNUMBER(I9:M9)*(I9:M9&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I9:M9&lt;&gt;"")*ISNUMBER(I9:M9)*(((I9:M9)&gt;0)+(TRIM(A9)&lt;&gt;"Retorno")&gt;0)*(I9:M9*(1-Config!$B$8)&lt;E9))))</f>
         <v>0</v>
       </c>
       <c r="P9" s="23" t="n">
@@ -1539,7 +1539,7 @@
         <v>Entre mínimo e alvo</v>
       </c>
       <c r="O10" s="30">
-        <f>IF(OR(A10="",NOT(ISNUMBER(F10))),"",IF(SUMPRODUCT(ISTEXT(I10:M10)+ISNUMBER(I10:M10)*(I10:M10&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I10:M10&lt;&gt;"")*ISNUMBER(I10:M10)*(((I10:M10)&gt;0)+(N(H10)&gt;0)&gt;0)*(I10:M10*(1-Config!$B$8)&lt;E10))))</f>
+        <f>IF(OR(A10="",NOT(ISNUMBER(F10))),"",IF(SUMPRODUCT(ISTEXT(I10:M10)+ISNUMBER(I10:M10)*(I10:M10&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I10:M10&lt;&gt;"")*ISNUMBER(I10:M10)*(((I10:M10)&gt;0)+(TRIM(A10)&lt;&gt;"Retorno")&gt;0)*(I10:M10*(1-Config!$B$8)&lt;E10))))</f>
         <v>3</v>
       </c>
       <c r="P10" s="23" t="n">
@@ -1606,7 +1606,7 @@
         <v>No alvo ou acima</v>
       </c>
       <c r="O11" s="30">
-        <f>IF(OR(A11="",NOT(ISNUMBER(F11))),"",IF(SUMPRODUCT(ISTEXT(I11:M11)+ISNUMBER(I11:M11)*(I11:M11&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I11:M11&lt;&gt;"")*ISNUMBER(I11:M11)*(((I11:M11)&gt;0)+(N(H11)&gt;0)&gt;0)*(I11:M11*(1-Config!$B$8)&lt;E11))))</f>
+        <f>IF(OR(A11="",NOT(ISNUMBER(F11))),"",IF(SUMPRODUCT(ISTEXT(I11:M11)+ISNUMBER(I11:M11)*(I11:M11&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I11:M11&lt;&gt;"")*ISNUMBER(I11:M11)*(((I11:M11)&gt;0)+(TRIM(A11)&lt;&gt;"Retorno")&gt;0)*(I11:M11*(1-Config!$B$8)&lt;E11))))</f>
         <v>2</v>
       </c>
       <c r="P11" s="23" t="n">
@@ -1673,7 +1673,7 @@
         <v>No alvo ou acima</v>
       </c>
       <c r="O12" s="30">
-        <f>IF(OR(A12="",NOT(ISNUMBER(F12))),"",IF(SUMPRODUCT(ISTEXT(I12:M12)+ISNUMBER(I12:M12)*(I12:M12&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I12:M12&lt;&gt;"")*ISNUMBER(I12:M12)*(((I12:M12)&gt;0)+(N(H12)&gt;0)&gt;0)*(I12:M12*(1-Config!$B$8)&lt;E12))))</f>
+        <f>IF(OR(A12="",NOT(ISNUMBER(F12))),"",IF(SUMPRODUCT(ISTEXT(I12:M12)+ISNUMBER(I12:M12)*(I12:M12&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I12:M12&lt;&gt;"")*ISNUMBER(I12:M12)*(((I12:M12)&gt;0)+(TRIM(A12)&lt;&gt;"Retorno")&gt;0)*(I12:M12*(1-Config!$B$8)&lt;E12))))</f>
         <v>2</v>
       </c>
       <c r="P12" s="23" t="n">
@@ -1740,7 +1740,7 @@
         <v>No alvo ou acima</v>
       </c>
       <c r="O13" s="30">
-        <f>IF(OR(A13="",NOT(ISNUMBER(F13))),"",IF(SUMPRODUCT(ISTEXT(I13:M13)+ISNUMBER(I13:M13)*(I13:M13&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I13:M13&lt;&gt;"")*ISNUMBER(I13:M13)*(((I13:M13)&gt;0)+(N(H13)&gt;0)&gt;0)*(I13:M13*(1-Config!$B$8)&lt;E13))))</f>
+        <f>IF(OR(A13="",NOT(ISNUMBER(F13))),"",IF(SUMPRODUCT(ISTEXT(I13:M13)+ISNUMBER(I13:M13)*(I13:M13&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I13:M13&lt;&gt;"")*ISNUMBER(I13:M13)*(((I13:M13)&gt;0)+(TRIM(A13)&lt;&gt;"Retorno")&gt;0)*(I13:M13*(1-Config!$B$8)&lt;E13))))</f>
         <v>3</v>
       </c>
       <c r="P13" s="23" t="n">
@@ -1803,7 +1803,7 @@
         <v>No alvo ou acima</v>
       </c>
       <c r="O14" s="30">
-        <f>IF(OR(A14="",NOT(ISNUMBER(F14))),"",IF(SUMPRODUCT(ISTEXT(I14:M14)+ISNUMBER(I14:M14)*(I14:M14&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I14:M14&lt;&gt;"")*ISNUMBER(I14:M14)*(((I14:M14)&gt;0)+(N(H14)&gt;0)&gt;0)*(I14:M14*(1-Config!$B$8)&lt;E14))))</f>
+        <f>IF(OR(A14="",NOT(ISNUMBER(F14))),"",IF(SUMPRODUCT(ISTEXT(I14:M14)+ISNUMBER(I14:M14)*(I14:M14&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I14:M14&lt;&gt;"")*ISNUMBER(I14:M14)*(((I14:M14)&gt;0)+(TRIM(A14)&lt;&gt;"Retorno")&gt;0)*(I14:M14*(1-Config!$B$8)&lt;E14))))</f>
         <v>1</v>
       </c>
       <c r="P14" s="23" t="n">
@@ -1850,7 +1850,7 @@
         <v/>
       </c>
       <c r="O15" s="30">
-        <f>IF(OR(A15="",NOT(ISNUMBER(F15))),"",IF(SUMPRODUCT(ISTEXT(I15:M15)+ISNUMBER(I15:M15)*(I15:M15&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I15:M15&lt;&gt;"")*ISNUMBER(I15:M15)*(((I15:M15)&gt;0)+(N(H15)&gt;0)&gt;0)*(I15:M15*(1-Config!$B$8)&lt;E15))))</f>
+        <f>IF(OR(A15="",NOT(ISNUMBER(F15))),"",IF(SUMPRODUCT(ISTEXT(I15:M15)+ISNUMBER(I15:M15)*(I15:M15&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I15:M15&lt;&gt;"")*ISNUMBER(I15:M15)*(((I15:M15)&gt;0)+(TRIM(A15)&lt;&gt;"Retorno")&gt;0)*(I15:M15*(1-Config!$B$8)&lt;E15))))</f>
         <v/>
       </c>
       <c r="P15" s="23" t="n"/>
@@ -1893,7 +1893,7 @@
         <v/>
       </c>
       <c r="O16" s="30">
-        <f>IF(OR(A16="",NOT(ISNUMBER(F16))),"",IF(SUMPRODUCT(ISTEXT(I16:M16)+ISNUMBER(I16:M16)*(I16:M16&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I16:M16&lt;&gt;"")*ISNUMBER(I16:M16)*(((I16:M16)&gt;0)+(N(H16)&gt;0)&gt;0)*(I16:M16*(1-Config!$B$8)&lt;E16))))</f>
+        <f>IF(OR(A16="",NOT(ISNUMBER(F16))),"",IF(SUMPRODUCT(ISTEXT(I16:M16)+ISNUMBER(I16:M16)*(I16:M16&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I16:M16&lt;&gt;"")*ISNUMBER(I16:M16)*(((I16:M16)&gt;0)+(TRIM(A16)&lt;&gt;"Retorno")&gt;0)*(I16:M16*(1-Config!$B$8)&lt;E16))))</f>
         <v/>
       </c>
       <c r="P16" s="23" t="n"/>
@@ -1936,7 +1936,7 @@
         <v/>
       </c>
       <c r="O17" s="30">
-        <f>IF(OR(A17="",NOT(ISNUMBER(F17))),"",IF(SUMPRODUCT(ISTEXT(I17:M17)+ISNUMBER(I17:M17)*(I17:M17&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I17:M17&lt;&gt;"")*ISNUMBER(I17:M17)*(((I17:M17)&gt;0)+(N(H17)&gt;0)&gt;0)*(I17:M17*(1-Config!$B$8)&lt;E17))))</f>
+        <f>IF(OR(A17="",NOT(ISNUMBER(F17))),"",IF(SUMPRODUCT(ISTEXT(I17:M17)+ISNUMBER(I17:M17)*(I17:M17&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I17:M17&lt;&gt;"")*ISNUMBER(I17:M17)*(((I17:M17)&gt;0)+(TRIM(A17)&lt;&gt;"Retorno")&gt;0)*(I17:M17*(1-Config!$B$8)&lt;E17))))</f>
         <v/>
       </c>
       <c r="P17" s="23" t="n"/>
@@ -1979,7 +1979,7 @@
         <v/>
       </c>
       <c r="O18" s="30">
-        <f>IF(OR(A18="",NOT(ISNUMBER(F18))),"",IF(SUMPRODUCT(ISTEXT(I18:M18)+ISNUMBER(I18:M18)*(I18:M18&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I18:M18&lt;&gt;"")*ISNUMBER(I18:M18)*(((I18:M18)&gt;0)+(N(H18)&gt;0)&gt;0)*(I18:M18*(1-Config!$B$8)&lt;E18))))</f>
+        <f>IF(OR(A18="",NOT(ISNUMBER(F18))),"",IF(SUMPRODUCT(ISTEXT(I18:M18)+ISNUMBER(I18:M18)*(I18:M18&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I18:M18&lt;&gt;"")*ISNUMBER(I18:M18)*(((I18:M18)&gt;0)+(TRIM(A18)&lt;&gt;"Retorno")&gt;0)*(I18:M18*(1-Config!$B$8)&lt;E18))))</f>
         <v/>
       </c>
       <c r="P18" s="23" t="n"/>
@@ -2022,7 +2022,7 @@
         <v/>
       </c>
       <c r="O19" s="30">
-        <f>IF(OR(A19="",NOT(ISNUMBER(F19))),"",IF(SUMPRODUCT(ISTEXT(I19:M19)+ISNUMBER(I19:M19)*(I19:M19&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I19:M19&lt;&gt;"")*ISNUMBER(I19:M19)*(((I19:M19)&gt;0)+(N(H19)&gt;0)&gt;0)*(I19:M19*(1-Config!$B$8)&lt;E19))))</f>
+        <f>IF(OR(A19="",NOT(ISNUMBER(F19))),"",IF(SUMPRODUCT(ISTEXT(I19:M19)+ISNUMBER(I19:M19)*(I19:M19&lt;0))&gt;0,"tabela inválida (texto ou negativo)",SUMPRODUCT((I19:M19&lt;&gt;"")*ISNUMBER(I19:M19)*(((I19:M19)&gt;0)+(TRIM(A19)&lt;&gt;"Retorno")&gt;0)*(I19:M19*(1-Config!$B$8)&lt;E19))))</f>
         <v/>
       </c>
       <c r="P19" s="23" t="n"/>
@@ -2041,7 +2041,7 @@
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="32" t="inlineStr">
         <is>
-          <t>Custo cheio, preço mínimo e preço alvo: a mesma conta da planilha 06 (tempo com retorno × custo-hora + material; ÷ (1 − impostos − margem)). Tabela de convênio em vermelho: depois dos impostos não cobre o custo cheio (margem negativa) — é a mesma conta e o mesmo número do KPI "Tabelas de convênio abaixo do custo cheio + imposto" e do Resumo da planilha 06. Tabela 0 em procedimento cobrado conta (o convênio não paga o custo); no retorno, com particular 0 também, não conta. Amarela: cobre o custo, mas não a margem mínima.</t>
+          <t>Custo cheio, preço mínimo e preço alvo: a mesma conta da planilha 06 (tempo com retorno × custo-hora + material; ÷ (1 − impostos − margem)). Tabela de convênio em vermelho: depois dos impostos não cobre o custo cheio (margem negativa) — é a mesma conta e o mesmo número do KPI "Tabelas de convênio abaixo do custo cheio + imposto" e do Resumo da planilha 06. Tabela 0 conta (o convênio não paga o custo), inclusive em procedimento sem cobrança no particular; só não conta na linha chamada Retorno, cujo tempo já está no custo da consulta. Amarela: cobre o custo, mas não a margem mínima.</t>
         </is>
       </c>
     </row>
@@ -2663,10 +2663,10 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="I8:M19">
     <cfRule type="expression" priority="4" dxfId="4">
-      <formula>AND(ISNUMBER(I8),OR(I8&gt;0,N($H8)&gt;0),ISNUMBER($F8),I8*(1-INDIRECT("Config!$B$8"))&lt;$E8)</formula>
+      <formula>IF(AND(ISNUMBER(I8),ISNUMBER($E8),ISNUMBER($F8)),AND(OR(I8&gt;0,TRIM($A8)&lt;&gt;"Retorno"),I8*(1-INDIRECT("Config!$B$8"))&lt;$E8),FALSE)</formula>
     </cfRule>
     <cfRule type="expression" priority="5" dxfId="1">
-      <formula>AND(ISNUMBER(I8),ISNUMBER($F8),I8*(1-INDIRECT("Config!$B$8"))&gt;=$E8,I8&lt;$F8)</formula>
+      <formula>IF(AND(ISNUMBER(I8),ISNUMBER($E8),ISNUMBER($F8)),AND(I8*(1-INDIRECT("Config!$B$8"))&gt;=$E8,I8&lt;$F8),FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O8:O19">
